--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -24392,16 +24392,18 @@
       <c r="A749" s="7" t="s">
         <v>925</v>
       </c>
-      <c r="B749" s="8" t="s">
-        <v>926</v>
+      <c r="B749" s="8" t="inlineStr">
+        <is>
+          <t>1F300</t>
+        </is>
       </c>
       <c r="C749" s="7" t="n">
         <f aca="false">HEX2DEC(B749)</f>
-        <v>58112</v>
+        <v>127744</v>
       </c>
       <c r="D749" s="9" t="str">
         <f aca="false">DEC2HEX(C749,4)</f>
-        <v>E300</v>
+        <v>1F300</v>
       </c>
       <c r="E749" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C749)</f>
@@ -24409,7 +24411,7 @@
       </c>
       <c r="F749" s="7" t="n">
         <f aca="false">C749-C748</f>
-        <v>45572</v>
+        <v>115204</v>
       </c>
       <c r="G749" s="16" t="s">
         <v>927</v>
@@ -24419,16 +24421,18 @@
       <c r="A750" s="7" t="s">
         <v>928</v>
       </c>
-      <c r="B750" s="8" t="s">
-        <v>929</v>
+      <c r="B750" s="8" t="inlineStr">
+        <is>
+          <t>1F310</t>
+        </is>
       </c>
       <c r="C750" s="7" t="n">
         <f aca="false">HEX2DEC(B750)</f>
-        <v>58128</v>
+        <v>127760</v>
       </c>
       <c r="D750" s="9" t="str">
         <f aca="false">DEC2HEX(C750,4)</f>
-        <v>E310</v>
+        <v>1F310</v>
       </c>
       <c r="E750" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C750)</f>
@@ -24444,16 +24448,18 @@
       <c r="A751" s="7" t="s">
         <v>930</v>
       </c>
-      <c r="B751" s="8" t="s">
-        <v>931</v>
+      <c r="B751" s="8" t="inlineStr">
+        <is>
+          <t>1F311</t>
+        </is>
       </c>
       <c r="C751" s="7" t="n">
         <f aca="false">HEX2DEC(B751)</f>
-        <v>58129</v>
+        <v>127761</v>
       </c>
       <c r="D751" s="9" t="str">
         <f aca="false">DEC2HEX(C751,4)</f>
-        <v>E311</v>
+        <v>1F311</v>
       </c>
       <c r="E751" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C751)</f>
@@ -24469,16 +24475,18 @@
       <c r="A752" s="7" t="s">
         <v>932</v>
       </c>
-      <c r="B752" s="8" t="s">
-        <v>933</v>
+      <c r="B752" s="8" t="inlineStr">
+        <is>
+          <t>1F315</t>
+        </is>
       </c>
       <c r="C752" s="7" t="n">
         <f aca="false">HEX2DEC(B752)</f>
-        <v>58133</v>
+        <v>127765</v>
       </c>
       <c r="D752" s="9" t="str">
         <f aca="false">DEC2HEX(C752,4)</f>
-        <v>E315</v>
+        <v>1F315</v>
       </c>
       <c r="E752" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C752)</f>
@@ -24494,16 +24502,18 @@
       <c r="A753" s="7" t="s">
         <v>934</v>
       </c>
-      <c r="B753" s="8" t="s">
-        <v>935</v>
+      <c r="B753" s="8" t="inlineStr">
+        <is>
+          <t>1F316</t>
+        </is>
       </c>
       <c r="C753" s="7" t="n">
         <f aca="false">HEX2DEC(B753)</f>
-        <v>58134</v>
+        <v>127766</v>
       </c>
       <c r="D753" s="9" t="str">
         <f aca="false">DEC2HEX(C753,4)</f>
-        <v>E316</v>
+        <v>1F316</v>
       </c>
       <c r="E753" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C753)</f>
@@ -24519,16 +24529,18 @@
       <c r="A754" s="7" t="s">
         <v>936</v>
       </c>
-      <c r="B754" s="8" t="s">
-        <v>937</v>
+      <c r="B754" s="8" t="inlineStr">
+        <is>
+          <t>1F317</t>
+        </is>
       </c>
       <c r="C754" s="7" t="n">
         <f aca="false">HEX2DEC(B754)</f>
-        <v>58135</v>
+        <v>127767</v>
       </c>
       <c r="D754" s="9" t="str">
         <f aca="false">DEC2HEX(C754,4)</f>
-        <v>E317</v>
+        <v>1F317</v>
       </c>
       <c r="E754" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C754)</f>
@@ -24544,16 +24556,18 @@
       <c r="A755" s="7" t="s">
         <v>938</v>
       </c>
-      <c r="B755" s="8" t="s">
-        <v>939</v>
+      <c r="B755" s="8" t="inlineStr">
+        <is>
+          <t>1F318</t>
+        </is>
       </c>
       <c r="C755" s="7" t="n">
         <f aca="false">HEX2DEC(B755)</f>
-        <v>58136</v>
+        <v>127768</v>
       </c>
       <c r="D755" s="9" t="str">
         <f aca="false">DEC2HEX(C755,4)</f>
-        <v>E318</v>
+        <v>1F318</v>
       </c>
       <c r="E755" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C755)</f>
@@ -24569,16 +24583,18 @@
       <c r="A756" s="7" t="s">
         <v>940</v>
       </c>
-      <c r="B756" s="8" t="s">
-        <v>941</v>
+      <c r="B756" s="8" t="inlineStr">
+        <is>
+          <t>1F3E0</t>
+        </is>
       </c>
       <c r="C756" s="7" t="n">
         <f aca="false">HEX2DEC(B756)</f>
-        <v>58336</v>
+        <v>127968</v>
       </c>
       <c r="D756" s="9" t="str">
         <f aca="false">DEC2HEX(C756,4)</f>
-        <v>E3E0</v>
+        <v>1F3E0</v>
       </c>
       <c r="E756" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C756)</f>
@@ -24594,16 +24610,18 @@
       <c r="A757" s="7" t="s">
         <v>942</v>
       </c>
-      <c r="B757" s="8" t="s">
-        <v>943</v>
+      <c r="B757" s="8" t="inlineStr">
+        <is>
+          <t>1F410</t>
+        </is>
       </c>
       <c r="C757" s="7" t="n">
         <f aca="false">HEX2DEC(B757)</f>
-        <v>58384</v>
+        <v>128016</v>
       </c>
       <c r="D757" s="9" t="str">
         <f aca="false">DEC2HEX(C757,4)</f>
-        <v>E410</v>
+        <v>1F410</v>
       </c>
       <c r="E757" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C757)</f>
@@ -24619,16 +24637,18 @@
       <c r="A758" s="7" t="s">
         <v>944</v>
       </c>
-      <c r="B758" s="8" t="s">
-        <v>945</v>
+      <c r="B758" s="8" t="inlineStr">
+        <is>
+          <t>1F4A1</t>
+        </is>
       </c>
       <c r="C758" s="7" t="n">
         <f aca="false">HEX2DEC(B758)</f>
-        <v>58529</v>
+        <v>128161</v>
       </c>
       <c r="D758" s="9" t="str">
         <f aca="false">DEC2HEX(C758,4)</f>
-        <v>E4A1</v>
+        <v>1F4A1</v>
       </c>
       <c r="E758" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C758)</f>
@@ -24644,16 +24664,18 @@
       <c r="A759" s="7" t="s">
         <v>946</v>
       </c>
-      <c r="B759" s="8" t="s">
-        <v>947</v>
+      <c r="B759" s="8" t="inlineStr">
+        <is>
+          <t>1F4AB</t>
+        </is>
       </c>
       <c r="C759" s="7" t="n">
         <f aca="false">HEX2DEC(B759)</f>
-        <v>58539</v>
+        <v>128171</v>
       </c>
       <c r="D759" s="9" t="str">
         <f aca="false">DEC2HEX(C759,4)</f>
-        <v>E4AB</v>
+        <v>1F4AB</v>
       </c>
       <c r="E759" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C759)</f>
@@ -24669,16 +24691,18 @@
       <c r="A760" s="7" t="s">
         <v>948</v>
       </c>
-      <c r="B760" s="11" t="s">
-        <v>949</v>
+      <c r="B760" s="11" t="inlineStr">
+        <is>
+          <t>1F4C2</t>
+        </is>
       </c>
       <c r="C760" s="7" t="n">
         <f aca="false">HEX2DEC(B760)</f>
-        <v>58562</v>
+        <v>128194</v>
       </c>
       <c r="D760" s="9" t="str">
         <f aca="false">DEC2HEX(C760,4)</f>
-        <v>E4C2</v>
+        <v>1F4C2</v>
       </c>
       <c r="E760" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C760)</f>
@@ -24694,16 +24718,18 @@
       <c r="A761" s="7" t="s">
         <v>950</v>
       </c>
-      <c r="B761" s="11" t="s">
-        <v>951</v>
+      <c r="B761" s="11" t="inlineStr">
+        <is>
+          <t>1F4CB</t>
+        </is>
       </c>
       <c r="C761" s="7" t="n">
         <f aca="false">HEX2DEC(B761)</f>
-        <v>58571</v>
+        <v>128203</v>
       </c>
       <c r="D761" s="9" t="str">
         <f aca="false">DEC2HEX(C761,4)</f>
-        <v>E4CB</v>
+        <v>1F4CB</v>
       </c>
       <c r="E761" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C761)</f>
@@ -24719,16 +24745,18 @@
       <c r="A762" s="7" t="s">
         <v>952</v>
       </c>
-      <c r="B762" s="8" t="s">
-        <v>953</v>
+      <c r="B762" s="8" t="inlineStr">
+        <is>
+          <t>1F4DD</t>
+        </is>
       </c>
       <c r="C762" s="7" t="n">
         <f aca="false">HEX2DEC(B762)</f>
-        <v>58589</v>
+        <v>128221</v>
       </c>
       <c r="D762" s="9" t="str">
         <f aca="false">DEC2HEX(C762,4)</f>
-        <v>E4DD</v>
+        <v>1F4DD</v>
       </c>
       <c r="E762" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C762)</f>
@@ -24744,16 +24772,18 @@
       <c r="A763" s="7" t="s">
         <v>954</v>
       </c>
-      <c r="B763" s="11" t="s">
-        <v>955</v>
+      <c r="B763" s="11" t="inlineStr">
+        <is>
+          <t>1F50E</t>
+        </is>
       </c>
       <c r="C763" s="7" t="n">
         <f aca="false">HEX2DEC(B763)</f>
-        <v>58638</v>
+        <v>128270</v>
       </c>
       <c r="D763" s="9" t="str">
         <f aca="false">DEC2HEX(C763,4)</f>
-        <v>E50E</v>
+        <v>1F50E</v>
       </c>
       <c r="E763" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C763)</f>
@@ -24769,16 +24799,18 @@
       <c r="A764" s="7" t="s">
         <v>956</v>
       </c>
-      <c r="B764" s="8" t="s">
-        <v>957</v>
+      <c r="B764" s="8" t="inlineStr">
+        <is>
+          <t>1F512</t>
+        </is>
       </c>
       <c r="C764" s="7" t="n">
         <f aca="false">HEX2DEC(B764)</f>
-        <v>58642</v>
+        <v>128274</v>
       </c>
       <c r="D764" s="9" t="str">
         <f aca="false">DEC2HEX(C764,4)</f>
-        <v>E512</v>
+        <v>1F512</v>
       </c>
       <c r="E764" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C764)</f>
@@ -24794,16 +24826,18 @@
       <c r="A765" s="7" t="s">
         <v>958</v>
       </c>
-      <c r="B765" s="8" t="s">
-        <v>959</v>
+      <c r="B765" s="8" t="inlineStr">
+        <is>
+          <t>1F527</t>
+        </is>
       </c>
       <c r="C765" s="7" t="n">
         <f aca="false">HEX2DEC(B765)</f>
-        <v>58663</v>
+        <v>128295</v>
       </c>
       <c r="D765" s="9" t="str">
         <f aca="false">DEC2HEX(C765,4)</f>
-        <v>E527</v>
+        <v>1F527</v>
       </c>
       <c r="E765" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C765)</f>
@@ -24819,16 +24853,18 @@
       <c r="A766" s="7" t="s">
         <v>960</v>
       </c>
-      <c r="B766" s="11" t="s">
-        <v>961</v>
+      <c r="B766" s="11" t="inlineStr">
+        <is>
+          <t>1F568</t>
+        </is>
       </c>
       <c r="C766" s="7" t="n">
         <f aca="false">HEX2DEC(B766)</f>
-        <v>58728</v>
+        <v>128360</v>
       </c>
       <c r="D766" s="9" t="str">
         <f aca="false">DEC2HEX(C766,4)</f>
-        <v>E568</v>
+        <v>1F568</v>
       </c>
       <c r="E766" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C766)</f>
@@ -24844,16 +24880,18 @@
       <c r="A767" s="7" t="s">
         <v>962</v>
       </c>
-      <c r="B767" s="8" t="s">
-        <v>963</v>
+      <c r="B767" s="8" t="inlineStr">
+        <is>
+          <t>1F569</t>
+        </is>
       </c>
       <c r="C767" s="7" t="n">
         <f aca="false">HEX2DEC(B767)</f>
-        <v>58729</v>
+        <v>128361</v>
       </c>
       <c r="D767" s="9" t="str">
         <f aca="false">DEC2HEX(C767,4)</f>
-        <v>E569</v>
+        <v>1F569</v>
       </c>
       <c r="E767" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C767)</f>
@@ -24869,16 +24907,18 @@
       <c r="A768" s="7" t="s">
         <v>964</v>
       </c>
-      <c r="B768" s="8" t="s">
-        <v>965</v>
+      <c r="B768" s="8" t="inlineStr">
+        <is>
+          <t>1F56A</t>
+        </is>
       </c>
       <c r="C768" s="7" t="n">
         <f aca="false">HEX2DEC(B768)</f>
-        <v>58730</v>
+        <v>128362</v>
       </c>
       <c r="D768" s="9" t="str">
         <f aca="false">DEC2HEX(C768,4)</f>
-        <v>E56A</v>
+        <v>1F56A</v>
       </c>
       <c r="E768" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C768)</f>
@@ -24894,16 +24934,18 @@
       <c r="A769" s="7" t="s">
         <v>966</v>
       </c>
-      <c r="B769" s="8" t="s">
-        <v>967</v>
+      <c r="B769" s="8" t="inlineStr">
+        <is>
+          <t>1F5A9</t>
+        </is>
       </c>
       <c r="C769" s="7" t="n">
         <f aca="false">HEX2DEC(B769)</f>
-        <v>58793</v>
+        <v>128425</v>
       </c>
       <c r="D769" s="9" t="str">
         <f aca="false">DEC2HEX(C769,4)</f>
-        <v>E5A9</v>
+        <v>1F5A9</v>
       </c>
       <c r="E769" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C769)</f>
@@ -24919,16 +24961,18 @@
       <c r="A770" s="7" t="s">
         <v>968</v>
       </c>
-      <c r="B770" s="8" t="s">
-        <v>969</v>
+      <c r="B770" s="8" t="inlineStr">
+        <is>
+          <t>1F5AB</t>
+        </is>
       </c>
       <c r="C770" s="7" t="n">
         <f aca="false">HEX2DEC(B770)</f>
-        <v>58795</v>
+        <v>128427</v>
       </c>
       <c r="D770" s="9" t="str">
         <f aca="false">DEC2HEX(C770,4)</f>
-        <v>E5AB</v>
+        <v>1F5AB</v>
       </c>
       <c r="E770" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C770)</f>
@@ -24944,16 +24988,18 @@
       <c r="A771" s="7" t="s">
         <v>970</v>
       </c>
-      <c r="B771" s="11" t="s">
-        <v>971</v>
+      <c r="B771" s="11" t="inlineStr">
+        <is>
+          <t>1F5B3</t>
+        </is>
       </c>
       <c r="C771" s="7" t="n">
         <f aca="false">HEX2DEC(B771)</f>
-        <v>58803</v>
+        <v>128435</v>
       </c>
       <c r="D771" s="9" t="str">
         <f aca="false">DEC2HEX(C771,4)</f>
-        <v>E5B3</v>
+        <v>1F5B3</v>
       </c>
       <c r="E771" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C771)</f>
@@ -24969,16 +25015,18 @@
       <c r="A772" s="7" t="s">
         <v>972</v>
       </c>
-      <c r="B772" s="8" t="s">
-        <v>973</v>
+      <c r="B772" s="8" t="inlineStr">
+        <is>
+          <t>1F5B4</t>
+        </is>
       </c>
       <c r="C772" s="7" t="n">
         <f aca="false">HEX2DEC(B772)</f>
-        <v>58804</v>
+        <v>128436</v>
       </c>
       <c r="D772" s="9" t="str">
         <f aca="false">DEC2HEX(C772,4)</f>
-        <v>E5B4</v>
+        <v>1F5B4</v>
       </c>
       <c r="E772" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C772)</f>
@@ -24994,16 +25042,18 @@
       <c r="A773" s="7" t="s">
         <v>974</v>
       </c>
-      <c r="B773" s="8" t="s">
-        <v>975</v>
+      <c r="B773" s="8" t="inlineStr">
+        <is>
+          <t>1F5B5</t>
+        </is>
       </c>
       <c r="C773" s="7" t="n">
         <f aca="false">HEX2DEC(B773)</f>
-        <v>58805</v>
+        <v>128437</v>
       </c>
       <c r="D773" s="9" t="str">
         <f aca="false">DEC2HEX(C773,4)</f>
-        <v>E5B5</v>
+        <v>1F5B5</v>
       </c>
       <c r="E773" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C773)</f>
@@ -25019,16 +25069,18 @@
       <c r="A774" s="7" t="s">
         <v>976</v>
       </c>
-      <c r="B774" s="8" t="s">
-        <v>977</v>
+      <c r="B774" s="8" t="inlineStr">
+        <is>
+          <t>1F5B6</t>
+        </is>
       </c>
       <c r="C774" s="7" t="n">
         <f aca="false">HEX2DEC(B774)</f>
-        <v>58806</v>
+        <v>128438</v>
       </c>
       <c r="D774" s="9" t="str">
         <f aca="false">DEC2HEX(C774,4)</f>
-        <v>E5B6</v>
+        <v>1F5B6</v>
       </c>
       <c r="E774" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C774)</f>
@@ -25044,16 +25096,18 @@
       <c r="A775" s="7" t="s">
         <v>978</v>
       </c>
-      <c r="B775" s="8" t="s">
-        <v>979</v>
+      <c r="B775" s="8" t="inlineStr">
+        <is>
+          <t>1F5B7</t>
+        </is>
       </c>
       <c r="C775" s="7" t="n">
         <f aca="false">HEX2DEC(B775)</f>
-        <v>58807</v>
+        <v>128439</v>
       </c>
       <c r="D775" s="9" t="str">
         <f aca="false">DEC2HEX(C775,4)</f>
-        <v>E5B7</v>
+        <v>1F5B7</v>
       </c>
       <c r="E775" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C775)</f>
@@ -25069,16 +25123,18 @@
       <c r="A776" s="7" t="s">
         <v>980</v>
       </c>
-      <c r="B776" s="8" t="s">
-        <v>981</v>
+      <c r="B776" s="8" t="inlineStr">
+        <is>
+          <t>1F5B8</t>
+        </is>
       </c>
       <c r="C776" s="7" t="n">
         <f aca="false">HEX2DEC(B776)</f>
-        <v>58808</v>
+        <v>128440</v>
       </c>
       <c r="D776" s="9" t="str">
         <f aca="false">DEC2HEX(C776,4)</f>
-        <v>E5B8</v>
+        <v>1F5B8</v>
       </c>
       <c r="E776" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C776)</f>
@@ -25094,16 +25150,18 @@
       <c r="A777" s="7" t="s">
         <v>982</v>
       </c>
-      <c r="B777" s="8" t="s">
-        <v>983</v>
+      <c r="B777" s="8" t="inlineStr">
+        <is>
+          <t>1F5B9</t>
+        </is>
       </c>
       <c r="C777" s="7" t="n">
         <f aca="false">HEX2DEC(B777)</f>
-        <v>58809</v>
+        <v>128441</v>
       </c>
       <c r="D777" s="9" t="str">
         <f aca="false">DEC2HEX(C777,4)</f>
-        <v>E5B9</v>
+        <v>1F5B9</v>
       </c>
       <c r="E777" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C777)</f>
@@ -25119,16 +25177,18 @@
       <c r="A778" s="7" t="s">
         <v>984</v>
       </c>
-      <c r="B778" s="8" t="s">
-        <v>985</v>
+      <c r="B778" s="8" t="inlineStr">
+        <is>
+          <t>1F5BA</t>
+        </is>
       </c>
       <c r="C778" s="7" t="n">
         <f aca="false">HEX2DEC(B778)</f>
-        <v>58810</v>
+        <v>128442</v>
       </c>
       <c r="D778" s="9" t="str">
         <f aca="false">DEC2HEX(C778,4)</f>
-        <v>E5BA</v>
+        <v>1F5BA</v>
       </c>
       <c r="E778" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C778)</f>
@@ -25144,16 +25204,18 @@
       <c r="A779" s="7" t="s">
         <v>986</v>
       </c>
-      <c r="B779" s="8" t="s">
-        <v>987</v>
+      <c r="B779" s="8" t="inlineStr">
+        <is>
+          <t>1F5BB</t>
+        </is>
       </c>
       <c r="C779" s="7" t="n">
         <f aca="false">HEX2DEC(B779)</f>
-        <v>58811</v>
+        <v>128443</v>
       </c>
       <c r="D779" s="9" t="str">
         <f aca="false">DEC2HEX(C779,4)</f>
-        <v>E5BB</v>
+        <v>1F5BB</v>
       </c>
       <c r="E779" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C779)</f>
@@ -25169,16 +25231,18 @@
       <c r="A780" s="7" t="s">
         <v>988</v>
       </c>
-      <c r="B780" s="8" t="s">
-        <v>989</v>
+      <c r="B780" s="8" t="inlineStr">
+        <is>
+          <t>1F5BC</t>
+        </is>
       </c>
       <c r="C780" s="7" t="n">
         <f aca="false">HEX2DEC(B780)</f>
-        <v>58812</v>
+        <v>128444</v>
       </c>
       <c r="D780" s="9" t="str">
         <f aca="false">DEC2HEX(C780,4)</f>
-        <v>E5BC</v>
+        <v>1F5BC</v>
       </c>
       <c r="E780" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C780)</f>
@@ -25194,16 +25258,18 @@
       <c r="A781" s="7" t="s">
         <v>990</v>
       </c>
-      <c r="B781" s="11" t="s">
-        <v>991</v>
+      <c r="B781" s="11" t="inlineStr">
+        <is>
+          <t>1F5CA</t>
+        </is>
       </c>
       <c r="C781" s="7" t="n">
         <f aca="false">HEX2DEC(B781)</f>
-        <v>58826</v>
+        <v>128458</v>
       </c>
       <c r="D781" s="9" t="str">
         <f aca="false">DEC2HEX(C781,4)</f>
-        <v>E5CA</v>
+        <v>1F5CA</v>
       </c>
       <c r="E781" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C781)</f>
@@ -25219,16 +25285,18 @@
       <c r="A782" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="B782" s="11" t="s">
-        <v>993</v>
+      <c r="B782" s="11" t="inlineStr">
+        <is>
+          <t>1F5D5</t>
+        </is>
       </c>
       <c r="C782" s="7" t="n">
         <f aca="false">HEX2DEC(B782)</f>
-        <v>58837</v>
+        <v>128469</v>
       </c>
       <c r="D782" s="9" t="str">
         <f aca="false">DEC2HEX(C782,4)</f>
-        <v>E5D5</v>
+        <v>1F5D5</v>
       </c>
       <c r="E782" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C782)</f>
@@ -25244,16 +25312,18 @@
       <c r="A783" s="7" t="s">
         <v>994</v>
       </c>
-      <c r="B783" s="8" t="s">
-        <v>995</v>
+      <c r="B783" s="8" t="inlineStr">
+        <is>
+          <t>1F5D6</t>
+        </is>
       </c>
       <c r="C783" s="7" t="n">
         <f aca="false">HEX2DEC(B783)</f>
-        <v>58838</v>
+        <v>128470</v>
       </c>
       <c r="D783" s="9" t="str">
         <f aca="false">DEC2HEX(C783,4)</f>
-        <v>E5D6</v>
+        <v>1F5D6</v>
       </c>
       <c r="E783" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C783)</f>
@@ -25269,16 +25339,18 @@
       <c r="A784" s="7" t="s">
         <v>996</v>
       </c>
-      <c r="B784" s="11" t="s">
-        <v>997</v>
+      <c r="B784" s="11" t="inlineStr">
+        <is>
+          <t>1F5D7</t>
+        </is>
       </c>
       <c r="C784" s="7" t="n">
         <f aca="false">HEX2DEC(B784)</f>
-        <v>58839</v>
+        <v>128471</v>
       </c>
       <c r="D784" s="9" t="str">
         <f aca="false">DEC2HEX(C784,4)</f>
-        <v>E5D7</v>
+        <v>1F5D7</v>
       </c>
       <c r="E784" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C784)</f>
@@ -25294,16 +25366,18 @@
       <c r="A785" s="7" t="s">
         <v>998</v>
       </c>
-      <c r="B785" s="8" t="s">
-        <v>999</v>
+      <c r="B785" s="8" t="inlineStr">
+        <is>
+          <t>1F5D8</t>
+        </is>
       </c>
       <c r="C785" s="7" t="n">
         <f aca="false">HEX2DEC(B785)</f>
-        <v>58840</v>
+        <v>128472</v>
       </c>
       <c r="D785" s="9" t="str">
         <f aca="false">DEC2HEX(C785,4)</f>
-        <v>E5D8</v>
+        <v>1F5D8</v>
       </c>
       <c r="E785" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C785)</f>
@@ -25319,16 +25393,18 @@
       <c r="A786" s="7" t="s">
         <v>1000</v>
       </c>
-      <c r="B786" s="11" t="s">
-        <v>1001</v>
+      <c r="B786" s="11" t="inlineStr">
+        <is>
+          <t>1F5D9</t>
+        </is>
       </c>
       <c r="C786" s="7" t="n">
         <f aca="false">HEX2DEC(B786)</f>
-        <v>58841</v>
+        <v>128473</v>
       </c>
       <c r="D786" s="9" t="str">
         <f aca="false">DEC2HEX(C786,4)</f>
-        <v>E5D9</v>
+        <v>1F5D9</v>
       </c>
       <c r="E786" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C786)</f>
@@ -25344,16 +25420,18 @@
       <c r="A787" s="7" t="s">
         <v>1002</v>
       </c>
-      <c r="B787" s="8" t="s">
-        <v>1003</v>
+      <c r="B787" s="8" t="inlineStr">
+        <is>
+          <t>1F5DA</t>
+        </is>
       </c>
       <c r="C787" s="7" t="n">
         <f aca="false">HEX2DEC(B787)</f>
-        <v>58842</v>
+        <v>128474</v>
       </c>
       <c r="D787" s="9" t="str">
         <f aca="false">DEC2HEX(C787,4)</f>
-        <v>E5DA</v>
+        <v>1F5DA</v>
       </c>
       <c r="E787" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C787)</f>
@@ -25369,16 +25447,18 @@
       <c r="A788" s="7" t="s">
         <v>1004</v>
       </c>
-      <c r="B788" s="11" t="s">
-        <v>1005</v>
+      <c r="B788" s="11" t="inlineStr">
+        <is>
+          <t>1F5DB</t>
+        </is>
       </c>
       <c r="C788" s="7" t="n">
         <f aca="false">HEX2DEC(B788)</f>
-        <v>58843</v>
+        <v>128475</v>
       </c>
       <c r="D788" s="9" t="str">
         <f aca="false">DEC2HEX(C788,4)</f>
-        <v>E5DB</v>
+        <v>1F5DB</v>
       </c>
       <c r="E788" s="10" t="str">
         <f aca="false">_xlfn.UNICHAR(C788)</f>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -30588,7 +30588,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DE79"/>
+  <dimension ref="A1:DI79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -30843,6 +30843,11 @@
       <c r="DE1" s="63" t="n">
         <v>1029</v>
       </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hr-HR</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -31173,6 +31178,11 @@
       <c r="DE3" s="115" t="s">
         <v>1137</v>
       </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -31708,6 +31718,11 @@
       <c r="DE6" s="115" t="s">
         <v>682</v>
       </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="7" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="93" t="s">
@@ -31871,6 +31886,11 @@
       <c r="DE7" s="115" t="s">
         <v>1154</v>
       </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -32032,6 +32052,11 @@
       <c r="DE8" s="115" t="s">
         <v>1145</v>
       </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -33203,6 +33228,11 @@
       <c r="DE15" s="115" t="s">
         <v>1185</v>
       </c>
+      <c r="DI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -33722,6 +33752,11 @@
       <c r="DE18" s="115" t="s">
         <v>16</v>
       </c>
+      <c r="DI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
     </row>
     <row r="19" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="93" t="s">
@@ -34551,6 +34586,11 @@
       <c r="DE23" s="115" t="s">
         <v>1195</v>
       </c>
+      <c r="DI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -34727,6 +34767,11 @@
       <c r="DD24" s="115"/>
       <c r="DE24" s="115" t="s">
         <v>1224</v>
+      </c>
+      <c r="DI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
       </c>
     </row>
     <row r="25" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35072,6 +35117,16 @@
       </c>
       <c r="DD26" s="115"/>
       <c r="DE26" s="115"/>
+      <c r="DF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="DG26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -35255,6 +35310,16 @@
       </c>
       <c r="DD27" s="115"/>
       <c r="DE27" s="115"/>
+      <c r="DF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y</t>
+        </is>
+      </c>
+      <c r="DG27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -35533,6 +35598,22 @@
       </c>
       <c r="DE28" s="115" t="s">
         <v>198</v>
+      </c>
+      <c r="DF28">
+        <v>1</v>
+      </c>
+      <c r="DG28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="DH28">
+        <v>1</v>
+      </c>
+      <c r="DI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_TILDE</t>
+        </is>
       </c>
     </row>
     <row r="29" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35829,6 +35910,22 @@
       <c r="DE29" s="115" t="s">
         <v>1241</v>
       </c>
+      <c r="DF29">
+        <v>2</v>
+      </c>
+      <c r="DG29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"</t>
+        </is>
+      </c>
+      <c r="DH29">
+        <v>2</v>
+      </c>
+      <c r="DI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_CARON</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -36126,6 +36223,22 @@
       <c r="DE30" s="115" t="s">
         <v>1245</v>
       </c>
+      <c r="DF30">
+        <v>3</v>
+      </c>
+      <c r="DG30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="DH30">
+        <v>3</v>
+      </c>
+      <c r="DI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -36423,6 +36536,22 @@
       <c r="DE31" s="115" t="s">
         <v>190</v>
       </c>
+      <c r="DF31">
+        <v>4</v>
+      </c>
+      <c r="DG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="DH31">
+        <v>4</v>
+      </c>
+      <c r="DI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_BREVE</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -36720,6 +36849,22 @@
       <c r="DE32" s="115" t="s">
         <v>194</v>
       </c>
+      <c r="DF32">
+        <v>5</v>
+      </c>
+      <c r="DG32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="DH32">
+        <v>5</v>
+      </c>
+      <c r="DI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_RING</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -37005,6 +37150,22 @@
       <c r="DE33" s="127" t="s">
         <v>196</v>
       </c>
+      <c r="DF33">
+        <v>6</v>
+      </c>
+      <c r="DG33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="DH33">
+        <v>6</v>
+      </c>
+      <c r="DI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_OGONEK</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -37299,6 +37460,22 @@
       </c>
       <c r="DE34" s="115" t="s">
         <v>1268</v>
+      </c>
+      <c r="DF34">
+        <v>7</v>
+      </c>
+      <c r="DG34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="DH34">
+        <v>7</v>
+      </c>
+      <c r="DI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
+        </is>
       </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37595,6 +37772,22 @@
       <c r="DE35" s="127" t="s">
         <v>192</v>
       </c>
+      <c r="DF35">
+        <v>8</v>
+      </c>
+      <c r="DG35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="DH35">
+        <v>8</v>
+      </c>
+      <c r="DI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_DOT_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -37890,6 +38083,22 @@
       <c r="DE36" s="127" t="s">
         <v>80</v>
       </c>
+      <c r="DF36">
+        <v>9</v>
+      </c>
+      <c r="DG36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="DH36">
+        <v>9</v>
+      </c>
+      <c r="DI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -38182,6 +38391,26 @@
       </c>
       <c r="DE37" s="127" t="s">
         <v>200</v>
+      </c>
+      <c r="DF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="DH37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_HUNGARUMLAUT</t>
+        </is>
       </c>
     </row>
     <row r="38" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39023,6 +39252,26 @@
       <c r="DE43" s="127" t="s">
         <v>59</v>
       </c>
+      <c r="DF43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="DG43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="DH43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="DI43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -39302,6 +39551,26 @@
       <c r="DE44" s="115" t="s">
         <v>1295</v>
       </c>
+      <c r="DF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="DG44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="DH44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="DI44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -39573,6 +39842,16 @@
       <c r="DE45" s="127" t="s">
         <v>163</v>
       </c>
+      <c r="DF45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="DG45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0160</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -39849,6 +40128,16 @@
       </c>
       <c r="DE46" s="115" t="s">
         <v>1311</v>
+      </c>
+      <c r="DF46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0111</t>
+        </is>
+      </c>
+      <c r="DG46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0110</t>
+        </is>
       </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40252,6 +40541,16 @@
       <c r="DC48" s="115"/>
       <c r="DD48" s="115"/>
       <c r="DE48" s="115"/>
+      <c r="DF48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017E</t>
+        </is>
+      </c>
+      <c r="DG48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017D</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -40506,6 +40805,16 @@
       </c>
       <c r="DE49" s="115" t="s">
         <v>1249</v>
+      </c>
+      <c r="DF49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010D</t>
+        </is>
+      </c>
+      <c r="DG49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010C</t>
+        </is>
       </c>
     </row>
     <row r="50" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40766,6 +41075,16 @@
       <c r="DE50" s="115" t="s">
         <v>135</v>
       </c>
+      <c r="DF50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0107</t>
+        </is>
+      </c>
+      <c r="DG50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0106</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -41033,6 +41352,21 @@
         <v>1197</v>
       </c>
       <c r="DE51" s="115"/>
+      <c r="DF51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
+      <c r="DG51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="DH51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
     </row>
     <row r="52" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="93" t="s">
@@ -42037,6 +42371,26 @@
         <v>16</v>
       </c>
       <c r="DE55" s="171"/>
+      <c r="DF55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DG55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="DH55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DI55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -42250,6 +42604,14 @@
       <c r="DE56" s="171" t="n">
         <v>48</v>
       </c>
+      <c r="DG56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DI56">
+        <v>52</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -42463,6 +42825,14 @@
       <c r="DE57" s="171" t="n">
         <v>12</v>
       </c>
+      <c r="DG57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DI57">
+        <v>12</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -42676,6 +43046,12 @@
       <c r="DE58" s="171" t="n">
         <v>50</v>
       </c>
+      <c r="DG58">
+        <v>30</v>
+      </c>
+      <c r="DI58">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -42889,6 +43265,12 @@
       <c r="DE59" s="171" t="n">
         <v>12</v>
       </c>
+      <c r="DG59">
+        <v>0</v>
+      </c>
+      <c r="DI59">
+        <v>12</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -43102,6 +43484,12 @@
       <c r="DE60" s="171" t="n">
         <v>48</v>
       </c>
+      <c r="DG60">
+        <v>30</v>
+      </c>
+      <c r="DI60">
+        <v>52</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -43313,6 +43701,12 @@
       </c>
       <c r="DD61" s="171"/>
       <c r="DE61" s="171" t="n">
+        <v>12</v>
+      </c>
+      <c r="DG61">
+        <v>0</v>
+      </c>
+      <c r="DI61">
         <v>12</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -30588,7 +30588,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:DI79"/>
+  <dimension ref="A1:EC79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -30848,6 +30848,31 @@
           <t xml:space="preserve">hr-HR</t>
         </is>
       </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sk-SK</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lt-LT</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lv-LV</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">et-EE</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pt-BR</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -31015,6 +31040,11 @@
       <c r="DC2" s="90"/>
       <c r="DD2" s="90"/>
       <c r="DE2" s="91"/>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0101</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="93" t="s">
@@ -31352,6 +31382,11 @@
       <c r="DE4" s="127" t="s">
         <v>1141</v>
       </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010D</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -31723,6 +31758,31 @@
           <t xml:space="preserve">EURO_SIGN</t>
         </is>
       </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0113</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="7" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="93" t="s">
@@ -32057,6 +32117,11 @@
           <t xml:space="preserve">]</t>
         </is>
       </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0123</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -32389,6 +32454,11 @@
       <c r="DE10" s="115" t="s">
         <v>116</v>
       </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012B</t>
+        </is>
+      </c>
     </row>
     <row r="11" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="93" t="s">
@@ -32717,6 +32787,11 @@
       <c r="DE12" s="115" t="s">
         <v>1170</v>
       </c>
+      <c r="DU12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0137</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -32882,6 +32957,11 @@
       <c r="DE13" s="115" t="s">
         <v>1174</v>
       </c>
+      <c r="DU13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_013C</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -33233,6 +33313,11 @@
           <t xml:space="preserve">}</t>
         </is>
       </c>
+      <c r="DU15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0146</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -34093,6 +34178,16 @@
       <c r="DE20" s="127" t="s">
         <v>1207</v>
       </c>
+      <c r="DU20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
     </row>
     <row r="21" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="93" t="s">
@@ -34421,6 +34516,11 @@
       <c r="DE22" s="115" t="s">
         <v>682</v>
       </c>
+      <c r="DU22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016B</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -35127,6 +35227,16 @@
           <t xml:space="preserve">Z</t>
         </is>
       </c>
+      <c r="DJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="DK26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -35320,6 +35430,26 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
+      <c r="DJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y</t>
+        </is>
+      </c>
+      <c r="DK27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="DU27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017E</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017E</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -35614,6 +35744,46 @@
         <is>
           <t xml:space="preserve">MOD_TILDE</t>
         </is>
+      </c>
+      <c r="DJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="DK28">
+        <v>1</v>
+      </c>
+      <c r="DL28">
+        <v>1</v>
+      </c>
+      <c r="DM28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_TILDE</t>
+        </is>
+      </c>
+      <c r="DN28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0105</t>
+        </is>
+      </c>
+      <c r="DO28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0104</t>
+        </is>
+      </c>
+      <c r="DQ28">
+        <v>1</v>
+      </c>
+      <c r="DV28">
+        <v>1</v>
+      </c>
+      <c r="DW28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="DX28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35926,6 +36096,51 @@
           <t xml:space="preserve">MOD_CARON</t>
         </is>
       </c>
+      <c r="DJ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_013E</t>
+        </is>
+      </c>
+      <c r="DK29">
+        <v>2</v>
+      </c>
+      <c r="DL29">
+        <v>2</v>
+      </c>
+      <c r="DM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_CARON</t>
+        </is>
+      </c>
+      <c r="DN29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010D</t>
+        </is>
+      </c>
+      <c r="DO29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010C</t>
+        </is>
+      </c>
+      <c r="DQ29">
+        <v>2</v>
+      </c>
+      <c r="DV29">
+        <v>2</v>
+      </c>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"</t>
+        </is>
+      </c>
+      <c r="DX29">
+        <v>2</v>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -36239,6 +36454,51 @@
           <t xml:space="preserve">^</t>
         </is>
       </c>
+      <c r="DJ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="DK30">
+        <v>3</v>
+      </c>
+      <c r="DL30">
+        <v>3</v>
+      </c>
+      <c r="DM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="DN30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0119</t>
+        </is>
+      </c>
+      <c r="DO30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0118</t>
+        </is>
+      </c>
+      <c r="DQ30">
+        <v>3</v>
+      </c>
+      <c r="DV30">
+        <v>3</v>
+      </c>
+      <c r="DW30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="DX30">
+        <v>3</v>
+      </c>
+      <c r="DY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -36552,6 +36812,51 @@
           <t xml:space="preserve">MOD_BREVE</t>
         </is>
       </c>
+      <c r="DJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_010D</t>
+        </is>
+      </c>
+      <c r="DK31">
+        <v>4</v>
+      </c>
+      <c r="DL31">
+        <v>4</v>
+      </c>
+      <c r="DM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_BREVE</t>
+        </is>
+      </c>
+      <c r="DN31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0117</t>
+        </is>
+      </c>
+      <c r="DO31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0116</t>
+        </is>
+      </c>
+      <c r="DQ31">
+        <v>4</v>
+      </c>
+      <c r="DV31">
+        <v>4</v>
+      </c>
+      <c r="DW31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
+      <c r="DX31">
+        <v>4</v>
+      </c>
+      <c r="DY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -36865,6 +37170,46 @@
           <t xml:space="preserve">MOD_RING</t>
         </is>
       </c>
+      <c r="DJ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0165</t>
+        </is>
+      </c>
+      <c r="DK32">
+        <v>5</v>
+      </c>
+      <c r="DL32">
+        <v>5</v>
+      </c>
+      <c r="DM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_RING</t>
+        </is>
+      </c>
+      <c r="DN32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012F</t>
+        </is>
+      </c>
+      <c r="DO32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012E</t>
+        </is>
+      </c>
+      <c r="DQ32">
+        <v>5</v>
+      </c>
+      <c r="DV32">
+        <v>5</v>
+      </c>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="DX32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -37166,6 +37511,46 @@
           <t xml:space="preserve">MOD_OGONEK</t>
         </is>
       </c>
+      <c r="DJ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017E</t>
+        </is>
+      </c>
+      <c r="DK33">
+        <v>6</v>
+      </c>
+      <c r="DL33">
+        <v>6</v>
+      </c>
+      <c r="DM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_OGONEK</t>
+        </is>
+      </c>
+      <c r="DN33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="DO33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0160</t>
+        </is>
+      </c>
+      <c r="DQ33">
+        <v>6</v>
+      </c>
+      <c r="DV33">
+        <v>6</v>
+      </c>
+      <c r="DW33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="DX33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -37477,6 +37862,51 @@
           <t xml:space="preserve">`</t>
         </is>
       </c>
+      <c r="DJ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FD</t>
+        </is>
+      </c>
+      <c r="DK34">
+        <v>7</v>
+      </c>
+      <c r="DL34">
+        <v>7</v>
+      </c>
+      <c r="DM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
+        </is>
+      </c>
+      <c r="DN34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0173</t>
+        </is>
+      </c>
+      <c r="DO34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0172</t>
+        </is>
+      </c>
+      <c r="DQ34">
+        <v>7</v>
+      </c>
+      <c r="DV34">
+        <v>7</v>
+      </c>
+      <c r="DW34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="DX34">
+        <v>7</v>
+      </c>
+      <c r="DY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="93" t="s">
@@ -37788,6 +38218,51 @@
           <t xml:space="preserve">MOD_DOT_ACCENT</t>
         </is>
       </c>
+      <c r="DJ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E1</t>
+        </is>
+      </c>
+      <c r="DK35">
+        <v>8</v>
+      </c>
+      <c r="DL35">
+        <v>8</v>
+      </c>
+      <c r="DM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_DOT_ACCENT</t>
+        </is>
+      </c>
+      <c r="DN35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016B</t>
+        </is>
+      </c>
+      <c r="DO35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016A</t>
+        </is>
+      </c>
+      <c r="DQ35">
+        <v>8</v>
+      </c>
+      <c r="DV35">
+        <v>8</v>
+      </c>
+      <c r="DW35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="DX35">
+        <v>8</v>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -38099,6 +38574,49 @@
           <t xml:space="preserve">ACUTE_ACCENT</t>
         </is>
       </c>
+      <c r="DJ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00ED</t>
+        </is>
+      </c>
+      <c r="DK36">
+        <v>9</v>
+      </c>
+      <c r="DL36">
+        <v>9</v>
+      </c>
+      <c r="DM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="DN36">
+        <v>9</v>
+      </c>
+      <c r="DO36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="DP36">
+        <v>9</v>
+      </c>
+      <c r="DV36">
+        <v>9</v>
+      </c>
+      <c r="DW36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="DX36">
+        <v>9</v>
+      </c>
+      <c r="DY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -38410,6 +38928,61 @@
       <c r="DI37" t="inlineStr">
         <is>
           <t xml:space="preserve">MOD_HUNGARUMLAUT</t>
+        </is>
+      </c>
+      <c r="DJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E9</t>
+        </is>
+      </c>
+      <c r="DK37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DL37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_HUNGARUMLAUT</t>
+        </is>
+      </c>
+      <c r="DN37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DO37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="DP37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DV37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DW37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
         </is>
       </c>
     </row>
@@ -39272,6 +39845,56 @@
           <t xml:space="preserve">DIAERESIS</t>
         </is>
       </c>
+      <c r="DJ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="DK43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="DL43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="DN43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="DO43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="DP43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="DV43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="DW43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="DX43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="DY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -39571,6 +40194,46 @@
           <t xml:space="preserve">CEDILLA</t>
         </is>
       </c>
+      <c r="DJ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="DK44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_CARON</t>
+        </is>
+      </c>
+      <c r="DL44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="DN44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017E</t>
+        </is>
+      </c>
+      <c r="DO44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_017D</t>
+        </is>
+      </c>
+      <c r="DV44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="DW44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
+        </is>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -39852,6 +40515,46 @@
           <t xml:space="preserve">LATIN_0160</t>
         </is>
       </c>
+      <c r="DJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FA</t>
+        </is>
+      </c>
+      <c r="DK45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="DL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FA</t>
+        </is>
+      </c>
+      <c r="DV45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FC</t>
+        </is>
+      </c>
+      <c r="DW45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00DC</t>
+        </is>
+      </c>
+      <c r="DZ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="EA45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
+        </is>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -40139,6 +40842,46 @@
           <t xml:space="preserve">LATIN_0110</t>
         </is>
       </c>
+      <c r="DJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E4</t>
+        </is>
+      </c>
+      <c r="DK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="DL46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E4</t>
+        </is>
+      </c>
+      <c r="DV46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F5</t>
+        </is>
+      </c>
+      <c r="DW46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00D5</t>
+        </is>
+      </c>
+      <c r="DZ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="EA46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -40405,6 +41148,21 @@
       </c>
       <c r="DE47" s="127" t="s">
         <v>51</v>
+      </c>
+      <c r="DZ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="EA47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
       </c>
     </row>
     <row r="48" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40551,6 +41309,36 @@
           <t xml:space="preserve">LATIN_017D</t>
         </is>
       </c>
+      <c r="DJ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0148</t>
+        </is>
+      </c>
+      <c r="DK48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="DL48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0148</t>
+        </is>
+      </c>
+      <c r="DV48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="DW48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -40814,6 +41602,41 @@
       <c r="DG49" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_010C</t>
+        </is>
+      </c>
+      <c r="DJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F4</t>
+        </is>
+      </c>
+      <c r="DK49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"</t>
+        </is>
+      </c>
+      <c r="DL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F4</t>
+        </is>
+      </c>
+      <c r="DV49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F6</t>
+        </is>
+      </c>
+      <c r="DW49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00D6</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E7</t>
+        </is>
+      </c>
+      <c r="EA49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00C7</t>
         </is>
       </c>
     </row>
@@ -41085,6 +41908,46 @@
           <t xml:space="preserve">LATIN_0106</t>
         </is>
       </c>
+      <c r="DJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="DK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="DL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="DV50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E4</t>
+        </is>
+      </c>
+      <c r="DW50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00C4</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="EA50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="EB50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -41365,6 +42228,21 @@
       <c r="DH51" t="inlineStr">
         <is>
           <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
+      <c r="DJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="DK51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="DL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
         </is>
       </c>
     </row>
@@ -42391,6 +43269,41 @@
           <t xml:space="preserve">|</t>
         </is>
       </c>
+      <c r="DJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="DL55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DV55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DW55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="DX55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="DY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -42612,6 +43525,46 @@
       <c r="DI56">
         <v>52</v>
       </c>
+      <c r="DK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DM56">
+        <v>52</v>
+      </c>
+      <c r="DO56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DQ56">
+        <v>52</v>
+      </c>
+      <c r="DS56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DU56">
+        <v>52</v>
+      </c>
+      <c r="DW56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DY56">
+        <v>52</v>
+      </c>
+      <c r="EA56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EC56">
+        <v>52</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -42833,6 +43786,46 @@
       <c r="DI57">
         <v>12</v>
       </c>
+      <c r="DK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DM57">
+        <v>12</v>
+      </c>
+      <c r="DO57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DQ57">
+        <v>12</v>
+      </c>
+      <c r="DS57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DU57">
+        <v>12</v>
+      </c>
+      <c r="DW57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="DY57">
+        <v>12</v>
+      </c>
+      <c r="EA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EC57">
+        <v>12</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -43052,6 +44045,36 @@
       <c r="DI58">
         <v>52</v>
       </c>
+      <c r="DK58">
+        <v>30</v>
+      </c>
+      <c r="DM58">
+        <v>52</v>
+      </c>
+      <c r="DO58">
+        <v>30</v>
+      </c>
+      <c r="DQ58">
+        <v>52</v>
+      </c>
+      <c r="DS58">
+        <v>30</v>
+      </c>
+      <c r="DU58">
+        <v>52</v>
+      </c>
+      <c r="DW58">
+        <v>30</v>
+      </c>
+      <c r="DY58">
+        <v>52</v>
+      </c>
+      <c r="EA58">
+        <v>30</v>
+      </c>
+      <c r="EC58">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -43271,6 +44294,36 @@
       <c r="DI59">
         <v>12</v>
       </c>
+      <c r="DK59">
+        <v>0</v>
+      </c>
+      <c r="DM59">
+        <v>12</v>
+      </c>
+      <c r="DO59">
+        <v>0</v>
+      </c>
+      <c r="DQ59">
+        <v>12</v>
+      </c>
+      <c r="DS59">
+        <v>0</v>
+      </c>
+      <c r="DU59">
+        <v>12</v>
+      </c>
+      <c r="DW59">
+        <v>0</v>
+      </c>
+      <c r="DY59">
+        <v>12</v>
+      </c>
+      <c r="EA59">
+        <v>0</v>
+      </c>
+      <c r="EC59">
+        <v>12</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -43490,6 +44543,36 @@
       <c r="DI60">
         <v>52</v>
       </c>
+      <c r="DK60">
+        <v>30</v>
+      </c>
+      <c r="DM60">
+        <v>52</v>
+      </c>
+      <c r="DO60">
+        <v>30</v>
+      </c>
+      <c r="DQ60">
+        <v>52</v>
+      </c>
+      <c r="DS60">
+        <v>30</v>
+      </c>
+      <c r="DU60">
+        <v>52</v>
+      </c>
+      <c r="DW60">
+        <v>30</v>
+      </c>
+      <c r="DY60">
+        <v>52</v>
+      </c>
+      <c r="EA60">
+        <v>30</v>
+      </c>
+      <c r="EC60">
+        <v>52</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -43707,6 +44790,36 @@
         <v>0</v>
       </c>
       <c r="DI61">
+        <v>12</v>
+      </c>
+      <c r="DK61">
+        <v>0</v>
+      </c>
+      <c r="DM61">
+        <v>12</v>
+      </c>
+      <c r="DO61">
+        <v>0</v>
+      </c>
+      <c r="DQ61">
+        <v>12</v>
+      </c>
+      <c r="DS61">
+        <v>0</v>
+      </c>
+      <c r="DU61">
+        <v>12</v>
+      </c>
+      <c r="DW61">
+        <v>0</v>
+      </c>
+      <c r="DY61">
+        <v>12</v>
+      </c>
+      <c r="EA61">
+        <v>0</v>
+      </c>
+      <c r="EC61">
         <v>12</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -29387,128 +29387,272 @@
       <c r="I955" s="15"/>
     </row>
     <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A956" s="12"/>
-      <c r="B956" s="15"/>
+      <c r="A956" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DJE</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t xml:space="preserve">402</t>
+        </is>
+      </c>
       <c r="D956" s="9"/>
       <c r="E956" s="10"/>
       <c r="F956" s="1"/>
       <c r="H956" s="7"/>
     </row>
     <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A957" s="7"/>
-      <c r="B957" s="7"/>
+      <c r="A957" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DJE</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452</t>
+        </is>
+      </c>
       <c r="C957" s="7"/>
       <c r="D957" s="7"/>
       <c r="E957" s="7"/>
     </row>
     <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A958" s="7"/>
-      <c r="B958" s="7"/>
+      <c r="A958" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TSHE</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40B</t>
+        </is>
+      </c>
       <c r="C958" s="7"/>
       <c r="D958" s="7"/>
       <c r="E958" s="7"/>
     </row>
     <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A959" s="7"/>
-      <c r="B959" s="7"/>
+      <c r="A959" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TSHE</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45B</t>
+        </is>
+      </c>
       <c r="C959" s="7"/>
       <c r="D959" s="7"/>
       <c r="E959" s="7"/>
     </row>
     <row r="960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A960" s="7"/>
-      <c r="B960" s="7"/>
+      <c r="A960" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_LJE</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t xml:space="preserve">409</t>
+        </is>
+      </c>
       <c r="C960" s="7"/>
       <c r="D960" s="7"/>
       <c r="E960" s="7"/>
     </row>
     <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A961" s="7"/>
-      <c r="B961" s="7"/>
+      <c r="A961" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_LJE</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t xml:space="preserve">459</t>
+        </is>
+      </c>
       <c r="C961" s="7"/>
       <c r="D961" s="7"/>
       <c r="E961" s="7"/>
     </row>
     <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A962" s="7"/>
-      <c r="B962" s="7"/>
+      <c r="A962" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_NJE</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40A</t>
+        </is>
+      </c>
       <c r="C962" s="7"/>
       <c r="D962" s="7"/>
       <c r="E962" s="7"/>
     </row>
     <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A963" s="7"/>
-      <c r="B963" s="7"/>
+      <c r="A963" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_NJE</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45A</t>
+        </is>
+      </c>
       <c r="C963" s="7"/>
       <c r="D963" s="7"/>
       <c r="E963" s="7"/>
     </row>
     <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A964" s="7"/>
-      <c r="B964" s="7"/>
+      <c r="A964" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZHE</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40F</t>
+        </is>
+      </c>
       <c r="C964" s="7"/>
       <c r="D964" s="7"/>
       <c r="E964" s="7"/>
     </row>
     <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A965" s="7"/>
-      <c r="B965" s="7"/>
+      <c r="A965" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZHE</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45F</t>
+        </is>
+      </c>
       <c r="C965" s="7"/>
       <c r="D965" s="7"/>
       <c r="E965" s="7"/>
     </row>
     <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A966" s="7"/>
-      <c r="B966" s="7"/>
+      <c r="A966" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_JE</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t xml:space="preserve">408</t>
+        </is>
+      </c>
       <c r="C966" s="7"/>
       <c r="D966" s="7"/>
       <c r="E966" s="7"/>
     </row>
     <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A967" s="7"/>
-      <c r="B967" s="7"/>
+      <c r="A967" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_JE</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458</t>
+        </is>
+      </c>
       <c r="C967" s="7"/>
       <c r="D967" s="7"/>
       <c r="E967" s="7"/>
     </row>
     <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A968" s="7"/>
-      <c r="B968" s="7"/>
+      <c r="A968" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_GJE</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t xml:space="preserve">403</t>
+        </is>
+      </c>
       <c r="C968" s="7"/>
       <c r="D968" s="7"/>
       <c r="E968" s="7"/>
     </row>
     <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A969" s="7"/>
-      <c r="B969" s="7"/>
+      <c r="A969" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_GJE</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t xml:space="preserve">453</t>
+        </is>
+      </c>
       <c r="C969" s="7"/>
       <c r="D969" s="7"/>
       <c r="E969" s="7"/>
     </row>
     <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A970" s="7"/>
-      <c r="B970" s="7"/>
+      <c r="A970" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_KJE</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40C</t>
+        </is>
+      </c>
       <c r="C970" s="7"/>
       <c r="D970" s="7"/>
       <c r="E970" s="7"/>
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A971" s="7"/>
-      <c r="B971" s="7"/>
+      <c r="A971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_KJE</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45C</t>
+        </is>
+      </c>
       <c r="C971" s="7"/>
       <c r="D971" s="7"/>
       <c r="E971" s="7"/>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A972" s="7"/>
-      <c r="B972" s="7"/>
+      <c r="A972" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZE</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t xml:space="preserve">405</t>
+        </is>
+      </c>
       <c r="C972" s="7"/>
       <c r="D972" s="7"/>
       <c r="E972" s="7"/>
     </row>
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A973" s="7"/>
-      <c r="B973" s="7"/>
+      <c r="A973" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZE</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t xml:space="preserve">455</t>
+        </is>
+      </c>
       <c r="C973" s="7"/>
       <c r="D973" s="7"/>
       <c r="E973" s="7"/>
@@ -30588,7 +30732,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:EC79"/>
+  <dimension ref="A1:EK79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -30873,6 +31017,16 @@
           <t xml:space="preserve">pt-BR</t>
         </is>
       </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sr-RS</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mk-MK</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -31043,6 +31197,26 @@
       <c r="DU2" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_0101</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_A</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_A</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_A</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_A</t>
         </is>
       </c>
     </row>
@@ -31213,6 +31387,26 @@
           <t xml:space="preserve">{</t>
         </is>
       </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_BE</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_BE</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_BE</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_BE</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -31387,6 +31581,26 @@
           <t xml:space="preserve">LATIN_010D</t>
         </is>
       </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TSE</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TSE</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TSE</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TSE</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -31556,6 +31770,26 @@
       <c r="DE5" s="115" t="s">
         <v>1146</v>
       </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DE</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DE</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DE</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DE</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -31781,6 +32015,26 @@
       <c r="EC6" t="inlineStr">
         <is>
           <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_IE</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_IE</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_IE</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_IE</t>
         </is>
       </c>
     </row>
@@ -31951,6 +32205,26 @@
           <t xml:space="preserve">[</t>
         </is>
       </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EF</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EF</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EF</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EF</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -32122,6 +32396,26 @@
           <t xml:space="preserve">LATIN_0123</t>
         </is>
       </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_GHE</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_GHE</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_GHE</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_GHE</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -32283,6 +32577,26 @@
       <c r="DC9" s="115"/>
       <c r="DD9" s="115"/>
       <c r="DE9" s="115"/>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_HA</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_HA</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_HA</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_HA</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -32457,6 +32771,26 @@
       <c r="DU10" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_012B</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_I</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_I</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_I</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_I</t>
         </is>
       </c>
     </row>
@@ -32624,6 +32958,26 @@
       <c r="DE11" s="127" t="s">
         <v>151</v>
       </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_JE</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_JE</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_JE</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_JE</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -32792,6 +33146,26 @@
           <t xml:space="preserve">LATIN_0137</t>
         </is>
       </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_KA</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_KA</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_KA</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_KA</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -32962,6 +33336,26 @@
           <t xml:space="preserve">LATIN_013C</t>
         </is>
       </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EL</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EL</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EL</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EL</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -33142,6 +33536,26 @@
       <c r="DD14" s="115"/>
       <c r="DE14" s="115" t="s">
         <v>1181</v>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EM</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EM</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EM</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EM</t>
+        </is>
       </c>
     </row>
     <row r="15" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33318,6 +33732,26 @@
           <t xml:space="preserve">LATIN_0146</t>
         </is>
       </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EN</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EN</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EN</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EN</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -33483,6 +33917,26 @@
       <c r="DC16" s="115"/>
       <c r="DD16" s="115"/>
       <c r="DE16" s="115"/>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_O</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_O</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_O</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_O</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -33648,6 +34102,26 @@
       <c r="DC17" s="115"/>
       <c r="DD17" s="115"/>
       <c r="DE17" s="127"/>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_PE</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_PE</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_PE</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_PE</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -33840,6 +34314,26 @@
       <c r="DI18" t="inlineStr">
         <is>
           <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_LJE</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_LJE</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_LJE</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_LJE</t>
         </is>
       </c>
     </row>
@@ -34011,6 +34505,26 @@
       <c r="DC19" s="115"/>
       <c r="DD19" s="115"/>
       <c r="DE19" s="115"/>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ER</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ER</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ER</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ER</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -34186,6 +34700,26 @@
       <c r="DY20" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ES</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ES</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ES</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ES</t>
         </is>
       </c>
     </row>
@@ -34347,6 +34881,26 @@
       <c r="DC21" s="115"/>
       <c r="DD21" s="115"/>
       <c r="DE21" s="115"/>
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TE</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TE</t>
+        </is>
+      </c>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TE</t>
+        </is>
+      </c>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TE</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -34521,6 +35075,26 @@
           <t xml:space="preserve">LATIN_016B</t>
         </is>
       </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_U</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_U</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_U</t>
+        </is>
+      </c>
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_U</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -34691,6 +35265,26 @@
           <t xml:space="preserve">@</t>
         </is>
       </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_VE</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_VE</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_VE</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_VE</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -34871,6 +35465,26 @@
       <c r="DI24" t="inlineStr">
         <is>
           <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_NJE</t>
+        </is>
+      </c>
+      <c r="EE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_NJE</t>
+        </is>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_NJE</t>
+        </is>
+      </c>
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_NJE</t>
         </is>
       </c>
     </row>
@@ -35038,6 +35652,26 @@
       <c r="DE25" s="115" t="s">
         <v>1228</v>
       </c>
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZHE</t>
+        </is>
+      </c>
+      <c r="EE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZHE</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZHE</t>
+        </is>
+      </c>
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZHE</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -35237,6 +35871,26 @@
           <t xml:space="preserve">Z</t>
         </is>
       </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZE</t>
+        </is>
+      </c>
+      <c r="EE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZE</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZE</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZE</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -35450,6 +36104,26 @@
           <t xml:space="preserve">LATIN_017E</t>
         </is>
       </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DZE</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DZE</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZE</t>
+        </is>
+      </c>
+      <c r="EI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZE</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -35783,6 +36457,28 @@
         </is>
       </c>
       <c r="DX28">
+        <v>1</v>
+      </c>
+      <c r="ED28">
+        <v>1</v>
+      </c>
+      <c r="EE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="EF28">
+        <v>1</v>
+      </c>
+      <c r="EH28">
+        <v>1</v>
+      </c>
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="EJ28">
         <v>1</v>
       </c>
     </row>
@@ -36141,6 +36837,28 @@
           <t xml:space="preserve">@</t>
         </is>
       </c>
+      <c r="ED29">
+        <v>2</v>
+      </c>
+      <c r="EE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"</t>
+        </is>
+      </c>
+      <c r="EF29">
+        <v>2</v>
+      </c>
+      <c r="EH29">
+        <v>2</v>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"</t>
+        </is>
+      </c>
+      <c r="EJ29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -36499,6 +37217,28 @@
           <t xml:space="preserve">POUND_SIGN</t>
         </is>
       </c>
+      <c r="ED30">
+        <v>3</v>
+      </c>
+      <c r="EE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="EF30">
+        <v>3</v>
+      </c>
+      <c r="EH30">
+        <v>3</v>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="EJ30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -36857,6 +37597,28 @@
           <t xml:space="preserve">$</t>
         </is>
       </c>
+      <c r="ED31">
+        <v>4</v>
+      </c>
+      <c r="EE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="EF31">
+        <v>4</v>
+      </c>
+      <c r="EH31">
+        <v>4</v>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="EJ31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -37210,6 +37972,28 @@
       <c r="DX32">
         <v>5</v>
       </c>
+      <c r="ED32">
+        <v>5</v>
+      </c>
+      <c r="EE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="EF32">
+        <v>5</v>
+      </c>
+      <c r="EH32">
+        <v>5</v>
+      </c>
+      <c r="EI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="EJ32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -37551,6 +38335,28 @@
       <c r="DX33">
         <v>6</v>
       </c>
+      <c r="ED33">
+        <v>6</v>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="EF33">
+        <v>6</v>
+      </c>
+      <c r="EH33">
+        <v>6</v>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="EJ33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -37907,6 +38713,28 @@
           <t xml:space="preserve">{</t>
         </is>
       </c>
+      <c r="ED34">
+        <v>7</v>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="EF34">
+        <v>7</v>
+      </c>
+      <c r="EH34">
+        <v>7</v>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="EJ34">
+        <v>7</v>
+      </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="93" t="s">
@@ -38263,6 +39091,28 @@
           <t xml:space="preserve">[</t>
         </is>
       </c>
+      <c r="ED35">
+        <v>8</v>
+      </c>
+      <c r="EE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="EF35">
+        <v>8</v>
+      </c>
+      <c r="EH35">
+        <v>8</v>
+      </c>
+      <c r="EI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="EJ35">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -38617,6 +39467,28 @@
           <t xml:space="preserve">]</t>
         </is>
       </c>
+      <c r="ED36">
+        <v>9</v>
+      </c>
+      <c r="EE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="EF36">
+        <v>9</v>
+      </c>
+      <c r="EH36">
+        <v>9</v>
+      </c>
+      <c r="EI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="EJ36">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -38983,6 +39855,36 @@
       <c r="DY37" t="inlineStr">
         <is>
           <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="EE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
         </is>
       </c>
     </row>
@@ -39895,6 +40797,36 @@
           <t xml:space="preserve">BACKSLASH</t>
         </is>
       </c>
+      <c r="ED43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="EE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="EH43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="EJ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -40234,6 +41166,36 @@
           <t xml:space="preserve">ACUTE_ACCENT</t>
         </is>
       </c>
+      <c r="ED44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="EE44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="EF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="EH44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="EI44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="EJ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -40555,6 +41517,26 @@
           <t xml:space="preserve">ACUTE_ACCENT</t>
         </is>
       </c>
+      <c r="ED45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SHA</t>
+        </is>
+      </c>
+      <c r="EE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SHA</t>
+        </is>
+      </c>
+      <c r="EH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SHA</t>
+        </is>
+      </c>
+      <c r="EI45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SHA</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -40880,6 +41862,26 @@
       <c r="EB46" t="inlineStr">
         <is>
           <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="ED46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DJE</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DJE</t>
+        </is>
+      </c>
+      <c r="EH46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_GJE</t>
+        </is>
+      </c>
+      <c r="EI46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_GJE</t>
         </is>
       </c>
     </row>
@@ -41339,6 +42341,26 @@
           <t xml:space="preserve">'</t>
         </is>
       </c>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZHE</t>
+        </is>
+      </c>
+      <c r="EE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZHE</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZHE</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZHE</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -41637,6 +42659,26 @@
       <c r="EA49" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_00C7</t>
+        </is>
+      </c>
+      <c r="ED49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_CHE</t>
+        </is>
+      </c>
+      <c r="EE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_CHE</t>
+        </is>
+      </c>
+      <c r="EH49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_CHE</t>
+        </is>
+      </c>
+      <c r="EI49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_CHE</t>
         </is>
       </c>
     </row>
@@ -41946,6 +42988,26 @@
       <c r="EB50" t="inlineStr">
         <is>
           <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TSHE</t>
+        </is>
+      </c>
+      <c r="EE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TSHE</t>
+        </is>
+      </c>
+      <c r="EH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_KJE</t>
+        </is>
+      </c>
+      <c r="EI50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_KJE</t>
         </is>
       </c>
     </row>
@@ -43304,6 +44366,36 @@
           <t xml:space="preserve">|</t>
         </is>
       </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -43565,6 +44657,22 @@
       <c r="EC56">
         <v>52</v>
       </c>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EG56">
+        <v>50</v>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EK56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -43826,6 +44934,22 @@
       <c r="EC57">
         <v>12</v>
       </c>
+      <c r="EE57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EG57">
+        <v>13</v>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="EK57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -44075,6 +45199,18 @@
       <c r="EC58">
         <v>52</v>
       </c>
+      <c r="EE58">
+        <v>30</v>
+      </c>
+      <c r="EG58">
+        <v>50</v>
+      </c>
+      <c r="EI58">
+        <v>30</v>
+      </c>
+      <c r="EK58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -44324,6 +45460,18 @@
       <c r="EC59">
         <v>12</v>
       </c>
+      <c r="EE59">
+        <v>0</v>
+      </c>
+      <c r="EG59">
+        <v>13</v>
+      </c>
+      <c r="EI59">
+        <v>0</v>
+      </c>
+      <c r="EK59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -44573,6 +45721,18 @@
       <c r="EC60">
         <v>52</v>
       </c>
+      <c r="EE60">
+        <v>30</v>
+      </c>
+      <c r="EG60">
+        <v>50</v>
+      </c>
+      <c r="EI60">
+        <v>30</v>
+      </c>
+      <c r="EK60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -44821,6 +45981,18 @@
       </c>
       <c r="EC61">
         <v>12</v>
+      </c>
+      <c r="EE61">
+        <v>0</v>
+      </c>
+      <c r="EG61">
+        <v>13</v>
+      </c>
+      <c r="EI61">
+        <v>0</v>
+      </c>
+      <c r="EK61">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -29658,92 +29658,196 @@
       <c r="E973" s="7"/>
     </row>
     <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A974" s="7"/>
-      <c r="B974" s="7"/>
+      <c r="A974" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67E</t>
+        </is>
+      </c>
       <c r="C974" s="7"/>
       <c r="D974" s="7"/>
       <c r="E974" s="7"/>
     </row>
     <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A975" s="7"/>
-      <c r="B975" s="7"/>
+      <c r="A975" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TCHEH</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686</t>
+        </is>
+      </c>
       <c r="C975" s="7"/>
       <c r="D975" s="7"/>
       <c r="E975" s="7"/>
     </row>
     <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A976" s="7"/>
-      <c r="B976" s="7"/>
+      <c r="A976" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEH</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t xml:space="preserve">698</t>
+        </is>
+      </c>
       <c r="C976" s="7"/>
       <c r="D976" s="7"/>
       <c r="E976" s="7"/>
     </row>
     <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A977" s="7"/>
-      <c r="B977" s="7"/>
+      <c r="A977" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6AF</t>
+        </is>
+      </c>
       <c r="C977" s="7"/>
       <c r="D977" s="7"/>
       <c r="E977" s="7"/>
     </row>
     <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A978" s="7"/>
-      <c r="B978" s="7"/>
+      <c r="A978" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6A9</t>
+        </is>
+      </c>
       <c r="C978" s="7"/>
       <c r="D978" s="7"/>
       <c r="E978" s="7"/>
     </row>
     <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A979" s="7"/>
-      <c r="B979" s="7"/>
+      <c r="A979" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6CC</t>
+        </is>
+      </c>
       <c r="C979" s="7"/>
       <c r="D979" s="7"/>
       <c r="E979" s="7"/>
     </row>
     <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A980" s="7"/>
-      <c r="B980" s="7"/>
+      <c r="A980" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TTEH</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t xml:space="preserve">679</t>
+        </is>
+      </c>
       <c r="C980" s="7"/>
       <c r="D980" s="7"/>
       <c r="E980" s="7"/>
     </row>
     <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A981" s="7"/>
-      <c r="B981" s="7"/>
+      <c r="A981" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DDAL</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688</t>
+        </is>
+      </c>
       <c r="C981" s="7"/>
       <c r="D981" s="7"/>
       <c r="E981" s="7"/>
     </row>
     <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A982" s="7"/>
-      <c r="B982" s="7"/>
+      <c r="A982" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_RREH</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691</t>
+        </is>
+      </c>
       <c r="C982" s="7"/>
       <c r="D982" s="7"/>
       <c r="E982" s="7"/>
     </row>
     <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A983" s="7"/>
-      <c r="B983" s="7"/>
+      <c r="A983" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON_GHUNNA</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6BA</t>
+        </is>
+      </c>
       <c r="C983" s="7"/>
       <c r="D983" s="7"/>
       <c r="E983" s="7"/>
     </row>
     <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A984" s="7"/>
-      <c r="B984" s="7"/>
+      <c r="A984" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_DOACHASHMEE</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6BE</t>
+        </is>
+      </c>
       <c r="C984" s="7"/>
       <c r="D984" s="7"/>
       <c r="E984" s="7"/>
     </row>
     <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A985" s="7"/>
-      <c r="B985" s="7"/>
+      <c r="A985" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_GOAL</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6C1</t>
+        </is>
+      </c>
       <c r="C985" s="7"/>
       <c r="D985" s="7"/>
       <c r="E985" s="7"/>
     </row>
     <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A986" s="7"/>
-      <c r="B986" s="7"/>
+      <c r="A986" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_BARREE</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6D2</t>
+        </is>
+      </c>
       <c r="C986" s="7"/>
       <c r="D986" s="7"/>
       <c r="E986" s="7"/>
@@ -30732,7 +30836,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:EK79"/>
+  <dimension ref="A1:EO79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -31027,6 +31131,11 @@
           <t xml:space="preserve">mk-MK</t>
         </is>
       </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fa-IR</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -31217,6 +31326,16 @@
       <c r="EI2" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_A</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
         </is>
       </c>
     </row>
@@ -31407,6 +31526,16 @@
           <t xml:space="preserve">CYRILLIC_BE</t>
         </is>
       </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -31601,6 +31730,21 @@
           <t xml:space="preserve">CYRILLIC_TSE</t>
         </is>
       </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEH</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -31790,6 +31934,16 @@
           <t xml:space="preserve">CYRILLIC_DE</t>
         </is>
       </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -32035,6 +32189,16 @@
       <c r="EI6" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_IE</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
         </is>
       </c>
     </row>
@@ -32225,6 +32389,16 @@
           <t xml:space="preserve">CYRILLIC_EF</t>
         </is>
       </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -32416,6 +32590,16 @@
           <t xml:space="preserve">CYRILLIC_GHE</t>
         </is>
       </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -32597,6 +32781,16 @@
           <t xml:space="preserve">CYRILLIC_HA</t>
         </is>
       </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -32791,6 +32985,16 @@
       <c r="EI10" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_I</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
         </is>
       </c>
     </row>
@@ -32978,6 +33182,16 @@
           <t xml:space="preserve">CYRILLIC_JE</t>
         </is>
       </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="EN11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -33166,6 +33380,16 @@
           <t xml:space="preserve">CYRILLIC_KA</t>
         </is>
       </c>
+      <c r="EL12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="EN12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -33356,6 +33580,16 @@
           <t xml:space="preserve">CYRILLIC_EL</t>
         </is>
       </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="EN13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -33555,6 +33789,16 @@
       <c r="EI14" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_EM</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
+      <c r="EN14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
         </is>
       </c>
     </row>
@@ -33752,6 +33996,16 @@
           <t xml:space="preserve">CYRILLIC_EN</t>
         </is>
       </c>
+      <c r="EL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="EN15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -33937,6 +34191,16 @@
           <t xml:space="preserve">CYRILLIC_O</t>
         </is>
       </c>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KHAH</t>
+        </is>
+      </c>
+      <c r="EN16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KHAH</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -34122,6 +34386,16 @@
           <t xml:space="preserve">CYRILLIC_PE</t>
         </is>
       </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="EN17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -34334,6 +34608,16 @@
       <c r="EI18" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_LJE</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="EN18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
         </is>
       </c>
     </row>
@@ -34525,6 +34809,16 @@
           <t xml:space="preserve">CYRILLIC_ER</t>
         </is>
       </c>
+      <c r="EL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="EN19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -34720,6 +35014,16 @@
       <c r="EI20" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_ES</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="EN20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
         </is>
       </c>
     </row>
@@ -34901,6 +35205,16 @@
           <t xml:space="preserve">CYRILLIC_TE</t>
         </is>
       </c>
+      <c r="EL21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="EN21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -35095,6 +35409,16 @@
           <t xml:space="preserve">CYRILLIC_U</t>
         </is>
       </c>
+      <c r="EL22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="EN22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -35285,6 +35609,16 @@
           <t xml:space="preserve">CYRILLIC_VE</t>
         </is>
       </c>
+      <c r="EL23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="EN23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -35485,6 +35819,16 @@
       <c r="EI24" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_NJE</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="EN24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
         </is>
       </c>
     </row>
@@ -35672,6 +36016,16 @@
           <t xml:space="preserve">CYRILLIC_DZHE</t>
         </is>
       </c>
+      <c r="EL25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="EN25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -35891,6 +36245,16 @@
           <t xml:space="preserve">CYRILLIC_DZE</t>
         </is>
       </c>
+      <c r="EL26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="EN26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -36122,6 +36486,16 @@
       <c r="EI27" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_ZE</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="EN27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
         </is>
       </c>
     </row>
@@ -41537,6 +41911,16 @@
           <t xml:space="preserve">CYRILLIC_SHA</t>
         </is>
       </c>
+      <c r="EL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="EN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -41882,6 +42266,16 @@
       <c r="EI46" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_GJE</t>
+        </is>
+      </c>
+      <c r="EL46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TCHEH</t>
+        </is>
+      </c>
+      <c r="EN46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TCHEH</t>
         </is>
       </c>
     </row>
@@ -42681,6 +43075,16 @@
           <t xml:space="preserve">CYRILLIC_CHE</t>
         </is>
       </c>
+      <c r="EL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
+      <c r="EN49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
     </row>
     <row r="50" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="93" t="s">
@@ -43010,6 +43414,16 @@
           <t xml:space="preserve">CYRILLIC_KJE</t>
         </is>
       </c>
+      <c r="EL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
+      <c r="EN50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -43561,6 +43975,16 @@
       </c>
       <c r="DE52" s="115" t="s">
         <v>1181</v>
+      </c>
+      <c r="EL52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="EN52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
       </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44673,6 +45097,12 @@
       <c r="EK56">
         <v>50</v>
       </c>
+      <c r="EM56">
+        <v>42</v>
+      </c>
+      <c r="EO56">
+        <v>52</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -44950,6 +45380,12 @@
       <c r="EK57">
         <v>13</v>
       </c>
+      <c r="EM57">
+        <v>0</v>
+      </c>
+      <c r="EO57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -45211,6 +45647,12 @@
       <c r="EK58">
         <v>50</v>
       </c>
+      <c r="EM58">
+        <v>27</v>
+      </c>
+      <c r="EO58">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -45472,6 +45914,12 @@
       <c r="EK59">
         <v>13</v>
       </c>
+      <c r="EM59">
+        <v>0</v>
+      </c>
+      <c r="EO59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -45733,6 +46181,12 @@
       <c r="EK60">
         <v>50</v>
       </c>
+      <c r="EM60">
+        <v>42</v>
+      </c>
+      <c r="EO60">
+        <v>52</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -45992,6 +46446,12 @@
         <v>0</v>
       </c>
       <c r="EK61">
+        <v>13</v>
+      </c>
+      <c r="EM61">
+        <v>0</v>
+      </c>
+      <c r="EO61">
         <v>13</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -37155,7 +37155,7 @@
       </c>
       <c r="DG29" t="inlineStr">
         <is>
-          <t xml:space="preserve">"</t>
+          <t xml:space="preserve">QUOTE</t>
         </is>
       </c>
       <c r="DH29">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="DW29" t="inlineStr">
         <is>
-          <t xml:space="preserve">"</t>
+          <t xml:space="preserve">QUOTE</t>
         </is>
       </c>
       <c r="DX29">
@@ -37216,7 +37216,7 @@
       </c>
       <c r="EE29" t="inlineStr">
         <is>
-          <t xml:space="preserve">"</t>
+          <t xml:space="preserve">QUOTE</t>
         </is>
       </c>
       <c r="EF29">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="EI29" t="inlineStr">
         <is>
-          <t xml:space="preserve">"</t>
+          <t xml:space="preserve">QUOTE</t>
         </is>
       </c>
       <c r="EJ29">
@@ -43027,7 +43027,7 @@
       </c>
       <c r="DK49" t="inlineStr">
         <is>
-          <t xml:space="preserve">"</t>
+          <t xml:space="preserve">QUOTE</t>
         </is>
       </c>
       <c r="DL49" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -29853,582 +29853,1246 @@
       <c r="E986" s="7"/>
     </row>
     <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A987" s="7"/>
-      <c r="B987" s="7"/>
+      <c r="A987" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0901</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901</t>
+        </is>
+      </c>
       <c r="C987" s="7"/>
       <c r="D987" s="7"/>
       <c r="E987" s="7"/>
     </row>
     <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A988" s="7"/>
-      <c r="B988" s="7"/>
+      <c r="A988" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902</t>
+        </is>
+      </c>
       <c r="C988" s="7"/>
       <c r="D988" s="7"/>
       <c r="E988" s="7"/>
     </row>
     <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A989" s="7"/>
-      <c r="B989" s="7"/>
+      <c r="A989" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0903</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t xml:space="preserve">903</t>
+        </is>
+      </c>
       <c r="C989" s="7"/>
       <c r="D989" s="7"/>
       <c r="E989" s="7"/>
     </row>
     <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A990" s="7"/>
-      <c r="B990" s="7"/>
+      <c r="A990" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0905</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t xml:space="preserve">905</t>
+        </is>
+      </c>
       <c r="C990" s="7"/>
       <c r="D990" s="7"/>
       <c r="E990" s="7"/>
     </row>
     <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A991" s="7"/>
-      <c r="B991" s="7"/>
+      <c r="A991" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0906</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906</t>
+        </is>
+      </c>
       <c r="C991" s="7"/>
       <c r="D991" s="7"/>
       <c r="E991" s="7"/>
     </row>
     <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A992" s="7"/>
-      <c r="B992" s="7"/>
+      <c r="A992" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0907</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t xml:space="preserve">907</t>
+        </is>
+      </c>
       <c r="C992" s="7"/>
       <c r="D992" s="7"/>
       <c r="E992" s="7"/>
     </row>
     <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A993" s="7"/>
-      <c r="B993" s="7"/>
+      <c r="A993" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0908</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t xml:space="preserve">908</t>
+        </is>
+      </c>
       <c r="C993" s="7"/>
       <c r="D993" s="7"/>
       <c r="E993" s="7"/>
     </row>
     <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A994" s="7"/>
-      <c r="B994" s="7"/>
+      <c r="A994" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0909</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t xml:space="preserve">909</t>
+        </is>
+      </c>
       <c r="C994" s="7"/>
       <c r="D994" s="7"/>
       <c r="E994" s="7"/>
     </row>
     <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A995" s="7"/>
-      <c r="B995" s="7"/>
+      <c r="A995" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090A</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90A</t>
+        </is>
+      </c>
       <c r="C995" s="7"/>
       <c r="D995" s="7"/>
       <c r="E995" s="7"/>
     </row>
     <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A996" s="7"/>
-      <c r="B996" s="7"/>
+      <c r="A996" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090B</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90B</t>
+        </is>
+      </c>
       <c r="C996" s="7"/>
       <c r="D996" s="7"/>
       <c r="E996" s="7"/>
     </row>
     <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A997" s="7"/>
-      <c r="B997" s="7"/>
+      <c r="A997" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090D</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90D</t>
+        </is>
+      </c>
       <c r="C997" s="7"/>
       <c r="D997" s="7"/>
       <c r="E997" s="7"/>
     </row>
     <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A998" s="7"/>
-      <c r="B998" s="7"/>
+      <c r="A998" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090E</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90E</t>
+        </is>
+      </c>
       <c r="C998" s="7"/>
       <c r="D998" s="7"/>
       <c r="E998" s="7"/>
     </row>
     <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A999" s="7"/>
-      <c r="B999" s="7"/>
+      <c r="A999" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090F</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90F</t>
+        </is>
+      </c>
       <c r="C999" s="7"/>
       <c r="D999" s="7"/>
       <c r="E999" s="7"/>
     </row>
     <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1000" s="7"/>
-      <c r="B1000" s="7"/>
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0910</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910</t>
+        </is>
+      </c>
       <c r="C1000" s="7"/>
       <c r="D1000" s="7"/>
       <c r="E1000" s="7"/>
     </row>
     <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1001" s="7"/>
-      <c r="B1001" s="7"/>
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0911</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t xml:space="preserve">911</t>
+        </is>
+      </c>
       <c r="C1001" s="7"/>
       <c r="D1001" s="7"/>
       <c r="E1001" s="7"/>
     </row>
     <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1002" s="7"/>
-      <c r="B1002" s="7"/>
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0912</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912</t>
+        </is>
+      </c>
       <c r="C1002" s="7"/>
       <c r="D1002" s="7"/>
       <c r="E1002" s="7"/>
     </row>
     <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1003" s="7"/>
-      <c r="B1003" s="7"/>
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0913</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t xml:space="preserve">913</t>
+        </is>
+      </c>
       <c r="C1003" s="7"/>
       <c r="D1003" s="7"/>
       <c r="E1003" s="7"/>
     </row>
     <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1004" s="7"/>
-      <c r="B1004" s="7"/>
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0914</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914</t>
+        </is>
+      </c>
       <c r="C1004" s="7"/>
       <c r="D1004" s="7"/>
       <c r="E1004" s="7"/>
     </row>
     <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1005" s="7"/>
-      <c r="B1005" s="7"/>
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t xml:space="preserve">915</t>
+        </is>
+      </c>
       <c r="C1005" s="7"/>
       <c r="D1005" s="7"/>
       <c r="E1005" s="7"/>
     </row>
     <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1006" s="7"/>
-      <c r="B1006" s="7"/>
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0916</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916</t>
+        </is>
+      </c>
       <c r="C1006" s="7"/>
       <c r="D1006" s="7"/>
       <c r="E1006" s="7"/>
     </row>
     <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1007" s="7"/>
-      <c r="B1007" s="7"/>
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917</t>
+        </is>
+      </c>
       <c r="C1007" s="7"/>
       <c r="D1007" s="7"/>
       <c r="E1007" s="7"/>
     </row>
     <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1008" s="7"/>
-      <c r="B1008" s="7"/>
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0918</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918</t>
+        </is>
+      </c>
       <c r="C1008" s="7"/>
       <c r="D1008" s="7"/>
       <c r="E1008" s="7"/>
     </row>
     <row r="1009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1009" s="7"/>
-      <c r="B1009" s="7"/>
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0919</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919</t>
+        </is>
+      </c>
       <c r="C1009" s="7"/>
       <c r="D1009" s="7"/>
       <c r="E1009" s="7"/>
     </row>
     <row r="1010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1010" s="7"/>
-      <c r="B1010" s="7"/>
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91A</t>
+        </is>
+      </c>
       <c r="C1010" s="7"/>
       <c r="D1010" s="7"/>
       <c r="E1010" s="7"/>
     </row>
     <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1011" s="7"/>
-      <c r="B1011" s="7"/>
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091B</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91B</t>
+        </is>
+      </c>
       <c r="C1011" s="7"/>
       <c r="D1011" s="7"/>
       <c r="E1011" s="7"/>
     </row>
     <row r="1012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1012" s="7"/>
-      <c r="B1012" s="7"/>
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91C</t>
+        </is>
+      </c>
       <c r="C1012" s="7"/>
       <c r="D1012" s="7"/>
       <c r="E1012" s="7"/>
     </row>
     <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1013" s="7"/>
-      <c r="B1013" s="7"/>
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091D</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91D</t>
+        </is>
+      </c>
       <c r="C1013" s="7"/>
       <c r="D1013" s="7"/>
       <c r="E1013" s="7"/>
     </row>
     <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1014" s="7"/>
-      <c r="B1014" s="7"/>
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091E</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91E</t>
+        </is>
+      </c>
       <c r="C1014" s="7"/>
       <c r="D1014" s="7"/>
       <c r="E1014" s="7"/>
     </row>
     <row r="1015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1015" s="7"/>
-      <c r="B1015" s="7"/>
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91F</t>
+        </is>
+      </c>
       <c r="C1015" s="7"/>
       <c r="D1015" s="7"/>
       <c r="E1015" s="7"/>
     </row>
     <row r="1016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1016" s="7"/>
-      <c r="B1016" s="7"/>
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0920</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920</t>
+        </is>
+      </c>
       <c r="C1016" s="7"/>
       <c r="D1016" s="7"/>
       <c r="E1016" s="7"/>
     </row>
     <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1017" s="7"/>
-      <c r="B1017" s="7"/>
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921</t>
+        </is>
+      </c>
       <c r="C1017" s="7"/>
       <c r="D1017" s="7"/>
       <c r="E1017" s="7"/>
     </row>
     <row r="1018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1018" s="7"/>
-      <c r="B1018" s="7"/>
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0922</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922</t>
+        </is>
+      </c>
       <c r="C1018" s="7"/>
       <c r="D1018" s="7"/>
       <c r="E1018" s="7"/>
     </row>
     <row r="1019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1019" s="7"/>
-      <c r="B1019" s="7"/>
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0923</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923</t>
+        </is>
+      </c>
       <c r="C1019" s="7"/>
       <c r="D1019" s="7"/>
       <c r="E1019" s="7"/>
     </row>
     <row r="1020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1020" s="7"/>
-      <c r="B1020" s="7"/>
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924</t>
+        </is>
+      </c>
       <c r="C1020" s="7"/>
       <c r="D1020" s="7"/>
       <c r="E1020" s="7"/>
     </row>
     <row r="1021" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1021" s="7"/>
-      <c r="B1021" s="7"/>
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0925</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t xml:space="preserve">925</t>
+        </is>
+      </c>
       <c r="C1021" s="7"/>
       <c r="D1021" s="7"/>
       <c r="E1021" s="7"/>
     </row>
     <row r="1022" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1022" s="7"/>
-      <c r="B1022" s="7"/>
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926</t>
+        </is>
+      </c>
       <c r="C1022" s="7"/>
       <c r="D1022" s="7"/>
       <c r="E1022" s="7"/>
     </row>
     <row r="1023" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1023" s="7"/>
-      <c r="B1023" s="7"/>
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0927</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t xml:space="preserve">927</t>
+        </is>
+      </c>
       <c r="C1023" s="7"/>
       <c r="D1023" s="7"/>
       <c r="E1023" s="7"/>
     </row>
     <row r="1024" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1024" s="7"/>
-      <c r="B1024" s="7"/>
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928</t>
+        </is>
+      </c>
       <c r="C1024" s="7"/>
       <c r="D1024" s="7"/>
       <c r="E1024" s="7"/>
     </row>
     <row r="1025" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1025" s="7"/>
-      <c r="B1025" s="7"/>
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0929</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929</t>
+        </is>
+      </c>
       <c r="C1025" s="7"/>
       <c r="D1025" s="7"/>
       <c r="E1025" s="7"/>
     </row>
     <row r="1026" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1026" s="7"/>
-      <c r="B1026" s="7"/>
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92A</t>
+        </is>
+      </c>
       <c r="C1026" s="7"/>
       <c r="D1026" s="7"/>
       <c r="E1026" s="7"/>
     </row>
     <row r="1027" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1027" s="7"/>
-      <c r="B1027" s="7"/>
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092B</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92B</t>
+        </is>
+      </c>
       <c r="C1027" s="7"/>
       <c r="D1027" s="7"/>
       <c r="E1027" s="7"/>
     </row>
     <row r="1028" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1028" s="7"/>
-      <c r="B1028" s="7"/>
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92C</t>
+        </is>
+      </c>
       <c r="C1028" s="7"/>
       <c r="D1028" s="7"/>
       <c r="E1028" s="7"/>
     </row>
     <row r="1029" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1029" s="7"/>
-      <c r="B1029" s="7"/>
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092D</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92D</t>
+        </is>
+      </c>
       <c r="C1029" s="7"/>
       <c r="D1029" s="7"/>
       <c r="E1029" s="7"/>
     </row>
     <row r="1030" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1030" s="7"/>
-      <c r="B1030" s="7"/>
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92E</t>
+        </is>
+      </c>
       <c r="C1030" s="7"/>
       <c r="D1030" s="7"/>
       <c r="E1030" s="7"/>
     </row>
     <row r="1031" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1031" s="7"/>
-      <c r="B1031" s="7"/>
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92F</t>
+        </is>
+      </c>
       <c r="C1031" s="7"/>
       <c r="D1031" s="7"/>
       <c r="E1031" s="7"/>
     </row>
     <row r="1032" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1032" s="7"/>
-      <c r="B1032" s="7"/>
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930</t>
+        </is>
+      </c>
       <c r="C1032" s="7"/>
       <c r="D1032" s="7"/>
       <c r="E1032" s="7"/>
     </row>
     <row r="1033" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1033" s="7"/>
-      <c r="B1033" s="7"/>
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0931</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t xml:space="preserve">931</t>
+        </is>
+      </c>
       <c r="C1033" s="7"/>
       <c r="D1033" s="7"/>
       <c r="E1033" s="7"/>
     </row>
     <row r="1034" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1034" s="7"/>
-      <c r="B1034" s="7"/>
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t xml:space="preserve">932</t>
+        </is>
+      </c>
       <c r="C1034" s="7"/>
       <c r="D1034" s="7"/>
       <c r="E1034" s="7"/>
     </row>
     <row r="1035" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1035" s="7"/>
-      <c r="B1035" s="7"/>
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0933</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t xml:space="preserve">933</t>
+        </is>
+      </c>
       <c r="C1035" s="7"/>
       <c r="D1035" s="7"/>
       <c r="E1035" s="7"/>
     </row>
     <row r="1036" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1036" s="7"/>
-      <c r="B1036" s="7"/>
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0934</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t xml:space="preserve">934</t>
+        </is>
+      </c>
       <c r="C1036" s="7"/>
       <c r="D1036" s="7"/>
       <c r="E1036" s="7"/>
     </row>
     <row r="1037" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1037" s="7"/>
-      <c r="B1037" s="7"/>
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t xml:space="preserve">935</t>
+        </is>
+      </c>
       <c r="C1037" s="7"/>
       <c r="D1037" s="7"/>
       <c r="E1037" s="7"/>
     </row>
     <row r="1038" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1038" s="7"/>
-      <c r="B1038" s="7"/>
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0936</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t xml:space="preserve">936</t>
+        </is>
+      </c>
       <c r="C1038" s="7"/>
       <c r="D1038" s="7"/>
       <c r="E1038" s="7"/>
     </row>
     <row r="1039" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1039" s="7"/>
-      <c r="B1039" s="7"/>
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0937</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937</t>
+        </is>
+      </c>
       <c r="C1039" s="7"/>
       <c r="D1039" s="7"/>
       <c r="E1039" s="7"/>
     </row>
     <row r="1040" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1040" s="7"/>
-      <c r="B1040" s="7"/>
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t xml:space="preserve">938</t>
+        </is>
+      </c>
       <c r="C1040" s="7"/>
       <c r="D1040" s="7"/>
       <c r="E1040" s="7"/>
     </row>
     <row r="1041" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1041" s="7"/>
-      <c r="B1041" s="7"/>
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t xml:space="preserve">939</t>
+        </is>
+      </c>
       <c r="C1041" s="7"/>
       <c r="D1041" s="7"/>
       <c r="E1041" s="7"/>
     </row>
     <row r="1042" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1042" s="7"/>
-      <c r="B1042" s="7"/>
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93C</t>
+        </is>
+      </c>
       <c r="C1042" s="7"/>
       <c r="D1042" s="7"/>
       <c r="E1042" s="7"/>
     </row>
     <row r="1043" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1043" s="7"/>
-      <c r="B1043" s="7"/>
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93E</t>
+        </is>
+      </c>
       <c r="C1043" s="7"/>
       <c r="D1043" s="7"/>
       <c r="E1043" s="7"/>
     </row>
     <row r="1044" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1044" s="7"/>
-      <c r="B1044" s="7"/>
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93F</t>
+        </is>
+      </c>
       <c r="C1044" s="7"/>
       <c r="D1044" s="7"/>
       <c r="E1044" s="7"/>
     </row>
     <row r="1045" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1045" s="7"/>
-      <c r="B1045" s="7"/>
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t xml:space="preserve">940</t>
+        </is>
+      </c>
       <c r="C1045" s="7"/>
       <c r="D1045" s="7"/>
       <c r="E1045" s="7"/>
     </row>
     <row r="1046" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1046" s="7"/>
-      <c r="B1046" s="7"/>
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t xml:space="preserve">941</t>
+        </is>
+      </c>
       <c r="C1046" s="7"/>
       <c r="D1046" s="7"/>
       <c r="E1046" s="7"/>
     </row>
     <row r="1047" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1047" s="7"/>
-      <c r="B1047" s="7"/>
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t xml:space="preserve">942</t>
+        </is>
+      </c>
       <c r="C1047" s="7"/>
       <c r="D1047" s="7"/>
       <c r="E1047" s="7"/>
     </row>
     <row r="1048" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1048" s="7"/>
-      <c r="B1048" s="7"/>
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t xml:space="preserve">943</t>
+        </is>
+      </c>
       <c r="C1048" s="7"/>
       <c r="D1048" s="7"/>
       <c r="E1048" s="7"/>
     </row>
     <row r="1049" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1049" s="7"/>
-      <c r="B1049" s="7"/>
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0945</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t xml:space="preserve">945</t>
+        </is>
+      </c>
       <c r="C1049" s="7"/>
       <c r="D1049" s="7"/>
       <c r="E1049" s="7"/>
     </row>
     <row r="1050" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1050" s="7"/>
-      <c r="B1050" s="7"/>
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946</t>
+        </is>
+      </c>
       <c r="C1050" s="7"/>
       <c r="D1050" s="7"/>
       <c r="E1050" s="7"/>
     </row>
     <row r="1051" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1051" s="7"/>
-      <c r="B1051" s="7"/>
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t xml:space="preserve">947</t>
+        </is>
+      </c>
       <c r="C1051" s="7"/>
       <c r="D1051" s="7"/>
       <c r="E1051" s="7"/>
     </row>
     <row r="1052" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1052" s="7"/>
-      <c r="B1052" s="7"/>
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948</t>
+        </is>
+      </c>
       <c r="C1052" s="7"/>
       <c r="D1052" s="7"/>
       <c r="E1052" s="7"/>
     </row>
     <row r="1053" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1053" s="7"/>
-      <c r="B1053" s="7"/>
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94A</t>
+        </is>
+      </c>
       <c r="C1053" s="7"/>
       <c r="D1053" s="7"/>
       <c r="E1053" s="7"/>
     </row>
     <row r="1054" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1054" s="7"/>
-      <c r="B1054" s="7"/>
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94B</t>
+        </is>
+      </c>
       <c r="C1054" s="7"/>
       <c r="D1054" s="7"/>
       <c r="E1054" s="7"/>
     </row>
     <row r="1055" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1055" s="7"/>
-      <c r="B1055" s="7"/>
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94C</t>
+        </is>
+      </c>
       <c r="C1055" s="7"/>
       <c r="D1055" s="7"/>
       <c r="E1055" s="7"/>
     </row>
     <row r="1056" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1056" s="7"/>
-      <c r="B1056" s="7"/>
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94D</t>
+        </is>
+      </c>
       <c r="C1056" s="7"/>
       <c r="D1056" s="7"/>
       <c r="E1056" s="7"/>
     </row>
     <row r="1057" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1057" s="7"/>
-      <c r="B1057" s="7"/>
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_095F</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95F</t>
+        </is>
+      </c>
       <c r="C1057" s="7"/>
       <c r="D1057" s="7"/>
       <c r="E1057" s="7"/>
     </row>
     <row r="1058" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1058" s="7"/>
-      <c r="B1058" s="7"/>
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0964</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t xml:space="preserve">964</t>
+        </is>
+      </c>
       <c r="C1058" s="7"/>
       <c r="D1058" s="7"/>
       <c r="E1058" s="7"/>
     </row>
     <row r="1059" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1059" s="7"/>
-      <c r="B1059" s="7"/>
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t xml:space="preserve">966</t>
+        </is>
+      </c>
       <c r="C1059" s="7"/>
       <c r="D1059" s="7"/>
       <c r="E1059" s="7"/>
     </row>
     <row r="1060" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1060" s="7"/>
-      <c r="B1060" s="7"/>
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t xml:space="preserve">967</t>
+        </is>
+      </c>
       <c r="C1060" s="7"/>
       <c r="D1060" s="7"/>
       <c r="E1060" s="7"/>
     </row>
     <row r="1061" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1061" s="7"/>
-      <c r="B1061" s="7"/>
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968</t>
+        </is>
+      </c>
       <c r="C1061" s="7"/>
       <c r="D1061" s="7"/>
       <c r="E1061" s="7"/>
     </row>
     <row r="1062" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1062" s="7"/>
-      <c r="B1062" s="7"/>
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t xml:space="preserve">969</t>
+        </is>
+      </c>
       <c r="C1062" s="7"/>
       <c r="D1062" s="7"/>
       <c r="E1062" s="7"/>
     </row>
     <row r="1063" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1063" s="7"/>
-      <c r="B1063" s="7"/>
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96A</t>
+        </is>
+      </c>
       <c r="C1063" s="7"/>
       <c r="D1063" s="7"/>
       <c r="E1063" s="7"/>
     </row>
     <row r="1064" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1064" s="7"/>
-      <c r="B1064" s="7"/>
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96B</t>
+        </is>
+      </c>
       <c r="C1064" s="7"/>
       <c r="D1064" s="7"/>
       <c r="E1064" s="7"/>
     </row>
     <row r="1065" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1065" s="7"/>
-      <c r="B1065" s="7"/>
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96C</t>
+        </is>
+      </c>
       <c r="C1065" s="7"/>
       <c r="D1065" s="7"/>
       <c r="E1065" s="7"/>
     </row>
     <row r="1066" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1066" s="7"/>
-      <c r="B1066" s="7"/>
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96D</t>
+        </is>
+      </c>
       <c r="C1066" s="7"/>
       <c r="D1066" s="7"/>
       <c r="E1066" s="7"/>
     </row>
     <row r="1067" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1067" s="7"/>
-      <c r="B1067" s="7"/>
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96E</t>
+        </is>
+      </c>
       <c r="C1067" s="7"/>
       <c r="D1067" s="7"/>
       <c r="E1067" s="7"/>
     </row>
     <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1068" s="7"/>
-      <c r="B1068" s="7"/>
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96F</t>
+        </is>
+      </c>
       <c r="C1068" s="7"/>
       <c r="D1068" s="7"/>
       <c r="E1068" s="7"/>
     </row>
     <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1069" s="7"/>
-      <c r="B1069" s="7"/>
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0972</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t xml:space="preserve">972</t>
+        </is>
+      </c>
       <c r="C1069" s="7"/>
       <c r="D1069" s="7"/>
       <c r="E1069" s="7"/>
@@ -30836,7 +31500,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:EO79"/>
+  <dimension ref="A1:FE79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -31136,6 +31800,26 @@
           <t xml:space="preserve">fa-IR</t>
         </is>
       </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hi-IN</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mr-IN</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ne-NP</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mn-MN</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -31336,6 +32020,61 @@
       <c r="EN2" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0913</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0913</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0913</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094B</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SHORT_I</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SHORT_I</t>
         </is>
       </c>
     </row>
@@ -31536,6 +32275,61 @@
           <t xml:space="preserve">ARABIC_THAL</t>
         </is>
       </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0934</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0934</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0934</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0935</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EM</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EM</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -31745,6 +32539,61 @@
           <t xml:space="preserve">ARABIC_ZAIN</t>
         </is>
       </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0923</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0923</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0923</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092E</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_IO</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_IO</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -31944,6 +32793,61 @@
           <t xml:space="preserve">ARABIC_FARSI_YEH</t>
         </is>
       </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0905</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0905</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0905</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094D</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_BE</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_BE</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -32199,6 +33103,61 @@
       <c r="EN6" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0906</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0906</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0906</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093E</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_U</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_U</t>
         </is>
       </c>
     </row>
@@ -32399,6 +33358,61 @@
           <t xml:space="preserve">ARABIC_BEH</t>
         </is>
       </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0907</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0907</t>
+        </is>
+      </c>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0907</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093F</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_BARRED_O</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_BARRED_O</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -32600,6 +33614,61 @@
           <t xml:space="preserve">ARABIC_LAM</t>
         </is>
       </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0909</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0909</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0909</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0941</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_A</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_A</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -32791,6 +33860,61 @@
           <t xml:space="preserve">ARABIC_ALEF</t>
         </is>
       </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092B</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092B</t>
+        </is>
+      </c>
+      <c r="EV9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="EX9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092B</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092A</t>
+        </is>
+      </c>
+      <c r="FB9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_HA</t>
+        </is>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_HA</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -32995,6 +34119,61 @@
       <c r="EN10" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0918</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0918</t>
+        </is>
+      </c>
+      <c r="EV10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="EX10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0918</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0917</t>
+        </is>
+      </c>
+      <c r="FB10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SHA</t>
+        </is>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SHA</t>
         </is>
       </c>
     </row>
@@ -33192,6 +34371,61 @@
           <t xml:space="preserve">ARABIC_TEH</t>
         </is>
       </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="EQ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0931</t>
+        </is>
+      </c>
+      <c r="ER11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="ET11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="EU11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0931</t>
+        </is>
+      </c>
+      <c r="EV11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="EX11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="EY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0931</t>
+        </is>
+      </c>
+      <c r="EZ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0930</t>
+        </is>
+      </c>
+      <c r="FB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ER</t>
+        </is>
+      </c>
+      <c r="FC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ER</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -33390,6 +34624,61 @@
           <t xml:space="preserve">ARABIC_NOON</t>
         </is>
       </c>
+      <c r="EP12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="EQ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0916</t>
+        </is>
+      </c>
+      <c r="ER12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="ET12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="EU12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0916</t>
+        </is>
+      </c>
+      <c r="EV12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="EX12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="EY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0916</t>
+        </is>
+      </c>
+      <c r="EZ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0915</t>
+        </is>
+      </c>
+      <c r="FB12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_O</t>
+        </is>
+      </c>
+      <c r="FC12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_O</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -33590,6 +34879,61 @@
           <t xml:space="preserve">ARABIC_MEEM</t>
         </is>
       </c>
+      <c r="EP13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="EQ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0925</t>
+        </is>
+      </c>
+      <c r="ER13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="ET13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="EU13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0925</t>
+        </is>
+      </c>
+      <c r="EV13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="EX13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="EY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0925</t>
+        </is>
+      </c>
+      <c r="EZ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0924</t>
+        </is>
+      </c>
+      <c r="FB13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EL</t>
+        </is>
+      </c>
+      <c r="FC13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EL</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -33799,6 +35143,61 @@
       <c r="EN14" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
+      <c r="EP14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="EQ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0936</t>
+        </is>
+      </c>
+      <c r="ER14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="ET14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="EU14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0936</t>
+        </is>
+      </c>
+      <c r="EV14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="EX14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="EY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0936</t>
+        </is>
+      </c>
+      <c r="EZ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0938</t>
+        </is>
+      </c>
+      <c r="FB14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TE</t>
+        </is>
+      </c>
+      <c r="FC14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TE</t>
         </is>
       </c>
     </row>
@@ -34006,6 +35405,61 @@
           <t xml:space="preserve">ARABIC_DAL</t>
         </is>
       </c>
+      <c r="EP15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="EQ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0933</t>
+        </is>
+      </c>
+      <c r="ER15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="ET15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="EU15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0933</t>
+        </is>
+      </c>
+      <c r="EV15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="EX15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="EY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0933</t>
+        </is>
+      </c>
+      <c r="EZ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0932</t>
+        </is>
+      </c>
+      <c r="FB15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_I</t>
+        </is>
+      </c>
+      <c r="FC15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_I</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -34201,6 +35655,61 @@
           <t xml:space="preserve">ARABIC_KHAH</t>
         </is>
       </c>
+      <c r="EP16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="EQ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0927</t>
+        </is>
+      </c>
+      <c r="ER16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="ET16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="EU16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0927</t>
+        </is>
+      </c>
+      <c r="EV16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="EX16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="EY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0927</t>
+        </is>
+      </c>
+      <c r="EZ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0926</t>
+        </is>
+      </c>
+      <c r="FB16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_STRAIGHT_U</t>
+        </is>
+      </c>
+      <c r="FC16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_STRAIGHT_U</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -34396,6 +35905,61 @@
           <t xml:space="preserve">ARABIC_HAH</t>
         </is>
       </c>
+      <c r="EP17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="EQ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091D</t>
+        </is>
+      </c>
+      <c r="ER17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="ET17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="EU17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091D</t>
+        </is>
+      </c>
+      <c r="EV17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="EX17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="EY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091D</t>
+        </is>
+      </c>
+      <c r="EZ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091C</t>
+        </is>
+      </c>
+      <c r="FB17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZE</t>
+        </is>
+      </c>
+      <c r="FC17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZE</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -34618,6 +36182,61 @@
       <c r="EN18" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="EP18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="EQ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0914</t>
+        </is>
+      </c>
+      <c r="ER18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="ET18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="EU18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0914</t>
+        </is>
+      </c>
+      <c r="EV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="EX18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="EY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0914</t>
+        </is>
+      </c>
+      <c r="EZ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094C</t>
+        </is>
+      </c>
+      <c r="FB18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EF</t>
+        </is>
+      </c>
+      <c r="FC18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EF</t>
         </is>
       </c>
     </row>
@@ -34819,6 +36438,61 @@
           <t xml:space="preserve">ARABIC_QAF</t>
         </is>
       </c>
+      <c r="EP19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="EQ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0908</t>
+        </is>
+      </c>
+      <c r="ER19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="ET19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="EU19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0908</t>
+        </is>
+      </c>
+      <c r="EV19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="EX19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="EY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0908</t>
+        </is>
+      </c>
+      <c r="EZ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0940</t>
+        </is>
+      </c>
+      <c r="FB19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ZHE</t>
+        </is>
+      </c>
+      <c r="FC19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ZHE</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -35024,6 +36698,61 @@
       <c r="EN20" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="EP20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="EQ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090F</t>
+        </is>
+      </c>
+      <c r="ER20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="ET20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="EU20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090F</t>
+        </is>
+      </c>
+      <c r="EV20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="EX20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="EY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090F</t>
+        </is>
+      </c>
+      <c r="EZ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0947</t>
+        </is>
+      </c>
+      <c r="FB20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_YERU</t>
+        </is>
+      </c>
+      <c r="FC20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_YERU</t>
         </is>
       </c>
     </row>
@@ -35215,6 +36944,61 @@
           <t xml:space="preserve">ARABIC_FEH</t>
         </is>
       </c>
+      <c r="EP21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="EQ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090A</t>
+        </is>
+      </c>
+      <c r="ER21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="ET21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="EU21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090A</t>
+        </is>
+      </c>
+      <c r="EV21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="EX21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="EY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090A</t>
+        </is>
+      </c>
+      <c r="EZ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0942</t>
+        </is>
+      </c>
+      <c r="FB21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_E</t>
+        </is>
+      </c>
+      <c r="FC21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_E</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -35419,6 +37203,61 @@
           <t xml:space="preserve">ARABIC_AIN</t>
         </is>
       </c>
+      <c r="EP22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="EQ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0919</t>
+        </is>
+      </c>
+      <c r="ER22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="ET22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="EU22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0919</t>
+        </is>
+      </c>
+      <c r="EV22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="EX22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="EY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0919</t>
+        </is>
+      </c>
+      <c r="EZ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0939</t>
+        </is>
+      </c>
+      <c r="FB22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_GHE</t>
+        </is>
+      </c>
+      <c r="FC22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_GHE</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -35619,6 +37458,61 @@
           <t xml:space="preserve">ARABIC_REH</t>
         </is>
       </c>
+      <c r="EP23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="EQ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0929</t>
+        </is>
+      </c>
+      <c r="ER23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="ET23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="EU23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0929</t>
+        </is>
+      </c>
+      <c r="EV23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="EX23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="EY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0929</t>
+        </is>
+      </c>
+      <c r="EZ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0928</t>
+        </is>
+      </c>
+      <c r="FB23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_ES</t>
+        </is>
+      </c>
+      <c r="FC23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_ES</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -35829,6 +37723,61 @@
       <c r="EN24" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="EP24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="EQ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0910</t>
+        </is>
+      </c>
+      <c r="ER24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="ET24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="EU24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0910</t>
+        </is>
+      </c>
+      <c r="EV24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="EX24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="EY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0910</t>
+        </is>
+      </c>
+      <c r="EZ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0948</t>
+        </is>
+      </c>
+      <c r="FB24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_TSE</t>
+        </is>
+      </c>
+      <c r="FC24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_TSE</t>
         </is>
       </c>
     </row>
@@ -36026,6 +37975,61 @@
           <t xml:space="preserve">ARABIC_TAH</t>
         </is>
       </c>
+      <c r="EP25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="EQ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0901</t>
+        </is>
+      </c>
+      <c r="ER25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="ET25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="EU25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0901</t>
+        </is>
+      </c>
+      <c r="EV25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="EX25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="EY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0901</t>
+        </is>
+      </c>
+      <c r="EZ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0902</t>
+        </is>
+      </c>
+      <c r="FB25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_CHE</t>
+        </is>
+      </c>
+      <c r="FC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_CHE</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -36255,6 +38259,61 @@
           <t xml:space="preserve">ARABIC_GHAIN</t>
         </is>
       </c>
+      <c r="EP26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="EQ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092D</t>
+        </is>
+      </c>
+      <c r="ER26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="ET26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="EU26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092D</t>
+        </is>
+      </c>
+      <c r="EV26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="EX26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="EY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092D</t>
+        </is>
+      </c>
+      <c r="EZ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092C</t>
+        </is>
+      </c>
+      <c r="FB26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_EN</t>
+        </is>
+      </c>
+      <c r="FC26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_EN</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -36498,6 +38557,61 @@
           <t xml:space="preserve">ARABIC_ZAH</t>
         </is>
       </c>
+      <c r="EP27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="EQ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090E</t>
+        </is>
+      </c>
+      <c r="ER27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="ET27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="EU27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090E</t>
+        </is>
+      </c>
+      <c r="EV27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="EX27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="EY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090E</t>
+        </is>
+      </c>
+      <c r="EZ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0946</t>
+        </is>
+      </c>
+      <c r="FB27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_YA</t>
+        </is>
+      </c>
+      <c r="FC27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_YA</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -36853,6 +38967,62 @@
         </is>
       </c>
       <c r="EJ28">
+        <v>1</v>
+      </c>
+      <c r="EP28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="EQ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090D</t>
+        </is>
+      </c>
+      <c r="ER28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="ET28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="EU28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090D</t>
+        </is>
+      </c>
+      <c r="EV28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="EX28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="EY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090D</t>
+        </is>
+      </c>
+      <c r="EZ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0967</t>
+        </is>
+      </c>
+      <c r="FB28">
+        <v>1</v>
+      </c>
+      <c r="FC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUMERO_SIGN</t>
+        </is>
+      </c>
+      <c r="FD28">
         <v>1</v>
       </c>
     </row>
@@ -37233,6 +39403,62 @@
       <c r="EJ29">
         <v>2</v>
       </c>
+      <c r="EP29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="EQ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0945</t>
+        </is>
+      </c>
+      <c r="ER29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="ET29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="EU29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0945</t>
+        </is>
+      </c>
+      <c r="EV29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="EX29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="EY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0945</t>
+        </is>
+      </c>
+      <c r="EZ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0968</t>
+        </is>
+      </c>
+      <c r="FB29">
+        <v>2</v>
+      </c>
+      <c r="FC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FD29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -37613,6 +39839,62 @@
       <c r="EJ30">
         <v>3</v>
       </c>
+      <c r="EP30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="EQ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="ER30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="ET30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="EU30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="EV30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="EX30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="EY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="EZ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0969</t>
+        </is>
+      </c>
+      <c r="FB30">
+        <v>3</v>
+      </c>
+      <c r="FC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FD30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -37993,6 +40275,57 @@
       <c r="EJ31">
         <v>4</v>
       </c>
+      <c r="EP31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="EQ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="ER31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="ET31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="EU31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="EV31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="EX31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="EY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="EZ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096A</t>
+        </is>
+      </c>
+      <c r="FB31">
+        <v>4</v>
+      </c>
+      <c r="FD31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -38368,6 +40701,62 @@
       <c r="EJ32">
         <v>5</v>
       </c>
+      <c r="EP32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="EQ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="ER32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="ET32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="EU32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="EV32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="EX32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="EY32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="EZ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096B</t>
+        </is>
+      </c>
+      <c r="FB32">
+        <v>5</v>
+      </c>
+      <c r="FC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="FD32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -38731,6 +41120,62 @@
       <c r="EJ33">
         <v>6</v>
       </c>
+      <c r="EP33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="EQ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="ER33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="ET33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="EU33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="EV33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="EX33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="EY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="EZ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096C</t>
+        </is>
+      </c>
+      <c r="FB33">
+        <v>6</v>
+      </c>
+      <c r="FC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="FD33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -39107,6 +41552,62 @@
         </is>
       </c>
       <c r="EJ34">
+        <v>7</v>
+      </c>
+      <c r="EP34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="EQ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="ER34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="ET34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="EU34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="EV34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="EX34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="EY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="EZ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096D</t>
+        </is>
+      </c>
+      <c r="FB34">
+        <v>7</v>
+      </c>
+      <c r="FC34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="FD34">
         <v>7</v>
       </c>
     </row>
@@ -39487,6 +41988,62 @@
       <c r="EJ35">
         <v>8</v>
       </c>
+      <c r="EP35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="EQ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="ER35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="ET35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="EU35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="EV35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="EX35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="EY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="EZ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096E</t>
+        </is>
+      </c>
+      <c r="FB35">
+        <v>8</v>
+      </c>
+      <c r="FC35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="FD35">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -39863,6 +42420,62 @@
       <c r="EJ36">
         <v>9</v>
       </c>
+      <c r="EP36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="EQ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="ER36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="ET36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="EU36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="EV36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="EX36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="EY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="EZ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_096F</t>
+        </is>
+      </c>
+      <c r="FB36">
+        <v>9</v>
+      </c>
+      <c r="FC36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="FD36">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -40257,6 +42870,66 @@
         </is>
       </c>
       <c r="EJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="EP37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="EQ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="ER37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="ET37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="EU37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="EV37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="EX37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="EY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="EZ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0966</t>
+        </is>
+      </c>
+      <c r="FB37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FC37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="FD37" t="inlineStr">
         <is>
           <t xml:space="preserve">ZERO</t>
         </is>
@@ -41201,6 +43874,61 @@
           <t xml:space="preserve">'</t>
         </is>
       </c>
+      <c r="EP43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="EQ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0903</t>
+        </is>
+      </c>
+      <c r="ER43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="ET43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="EU43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0903</t>
+        </is>
+      </c>
+      <c r="EV43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="EX43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="EY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0903</t>
+        </is>
+      </c>
+      <c r="EZ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FB43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_IE</t>
+        </is>
+      </c>
+      <c r="FC43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_IE</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -41570,6 +44298,61 @@
           <t xml:space="preserve">+</t>
         </is>
       </c>
+      <c r="EP44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="EQ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090B</t>
+        </is>
+      </c>
+      <c r="ER44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="ET44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="EU44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090B</t>
+        </is>
+      </c>
+      <c r="EV44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="EX44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="EY44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_090B</t>
+        </is>
+      </c>
+      <c r="EZ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0943</t>
+        </is>
+      </c>
+      <c r="FB44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SHCHA</t>
+        </is>
+      </c>
+      <c r="FC44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SHCHA</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -41921,6 +44704,61 @@
           <t xml:space="preserve">ARABIC_JEEM</t>
         </is>
       </c>
+      <c r="EP45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="EQ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0922</t>
+        </is>
+      </c>
+      <c r="ER45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="ET45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="EU45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0922</t>
+        </is>
+      </c>
+      <c r="EV45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="EX45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="EY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0922</t>
+        </is>
+      </c>
+      <c r="EZ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0921</t>
+        </is>
+      </c>
+      <c r="FB45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_KA</t>
+        </is>
+      </c>
+      <c r="FC45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_KA</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -42278,6 +45116,61 @@
           <t xml:space="preserve">ARABIC_TCHEH</t>
         </is>
       </c>
+      <c r="EP46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="EQ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091E</t>
+        </is>
+      </c>
+      <c r="ER46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="ET46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="EU46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091E</t>
+        </is>
+      </c>
+      <c r="EV46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="EX46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="EY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091E</t>
+        </is>
+      </c>
+      <c r="EZ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_093C</t>
+        </is>
+      </c>
+      <c r="FB46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_HARD_SIGN</t>
+        </is>
+      </c>
+      <c r="FC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_HARD_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -42558,6 +45451,21 @@
       <c r="EB47" t="inlineStr">
         <is>
           <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FB47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FC47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
         </is>
       </c>
     </row>
@@ -43085,6 +45993,61 @@
           <t xml:space="preserve">ARABIC_KEHEH</t>
         </is>
       </c>
+      <c r="EP49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="EQ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091B</t>
+        </is>
+      </c>
+      <c r="ER49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="ET49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="EU49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091B</t>
+        </is>
+      </c>
+      <c r="EV49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="EX49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="EY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091B</t>
+        </is>
+      </c>
+      <c r="EZ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091A</t>
+        </is>
+      </c>
+      <c r="FB49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_DE</t>
+        </is>
+      </c>
+      <c r="FC49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_DE</t>
+        </is>
+      </c>
     </row>
     <row r="50" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="93" t="s">
@@ -43424,6 +46387,61 @@
           <t xml:space="preserve">ARABIC_GAF</t>
         </is>
       </c>
+      <c r="EP50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="EQ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0920</t>
+        </is>
+      </c>
+      <c r="ER50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="ET50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="EU50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0920</t>
+        </is>
+      </c>
+      <c r="EV50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="EX50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="EY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0920</t>
+        </is>
+      </c>
+      <c r="EZ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_091F</t>
+        </is>
+      </c>
+      <c r="FB50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_PE</t>
+        </is>
+      </c>
+      <c r="FC50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_PE</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -43719,6 +46737,66 @@
       <c r="DL51" t="inlineStr">
         <is>
           <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="EP51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="EQ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0912</t>
+        </is>
+      </c>
+      <c r="ER51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="ET51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="EU51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0912</t>
+        </is>
+      </c>
+      <c r="EV51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="EX51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="EY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0912</t>
+        </is>
+      </c>
+      <c r="EZ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_094A</t>
+        </is>
+      </c>
+      <c r="FB51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="FC51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
         </is>
       </c>
     </row>
@@ -43986,6 +47064,61 @@
           <t xml:space="preserve">ARABIC_WAW</t>
         </is>
       </c>
+      <c r="EP52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="EQ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0937</t>
+        </is>
+      </c>
+      <c r="ER52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="ET52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="EU52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0937</t>
+        </is>
+      </c>
+      <c r="EV52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="EX52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="EY52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0937</t>
+        </is>
+      </c>
+      <c r="EZ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="FB52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_SOFT_SIGN</t>
+        </is>
+      </c>
+      <c r="FC52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SOFT_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -44245,6 +47378,61 @@
       <c r="DE53" s="115" t="s">
         <v>1223</v>
       </c>
+      <c r="EP53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="EQ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0964</t>
+        </is>
+      </c>
+      <c r="ER53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="ET53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="EU53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0964</t>
+        </is>
+      </c>
+      <c r="EV53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="EX53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="EY53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0964</t>
+        </is>
+      </c>
+      <c r="EZ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="FB53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_VE</t>
+        </is>
+      </c>
+      <c r="FC53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_VE</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -44509,6 +47697,61 @@
       </c>
       <c r="DE54" s="115" t="s">
         <v>1272</v>
+      </c>
+      <c r="EP54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="EQ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_095F</t>
+        </is>
+      </c>
+      <c r="ER54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="ET54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="EU54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_095F</t>
+        </is>
+      </c>
+      <c r="EV54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="EX54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="EY54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_095F</t>
+        </is>
+      </c>
+      <c r="EZ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_092F</t>
+        </is>
+      </c>
+      <c r="FB54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_SM_YU</t>
+        </is>
+      </c>
+      <c r="FC54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYRILLIC_YU</t>
+        </is>
       </c>
     </row>
     <row r="55" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44820,6 +48063,21 @@
           <t xml:space="preserve">&lt;</t>
         </is>
       </c>
+      <c r="FB55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="FC55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="FD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -45103,6 +48361,32 @@
       <c r="EO56">
         <v>52</v>
       </c>
+      <c r="EQ56">
+        <v>40</v>
+      </c>
+      <c r="ES56">
+        <v>52</v>
+      </c>
+      <c r="EU56">
+        <v>40</v>
+      </c>
+      <c r="EW56">
+        <v>52</v>
+      </c>
+      <c r="EY56">
+        <v>40</v>
+      </c>
+      <c r="FA56">
+        <v>52</v>
+      </c>
+      <c r="FC56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FE56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -45386,6 +48670,32 @@
       <c r="EO57">
         <v>13</v>
       </c>
+      <c r="EQ57">
+        <v>0</v>
+      </c>
+      <c r="ES57">
+        <v>13</v>
+      </c>
+      <c r="EU57">
+        <v>0</v>
+      </c>
+      <c r="EW57">
+        <v>13</v>
+      </c>
+      <c r="EY57">
+        <v>0</v>
+      </c>
+      <c r="FA57">
+        <v>13</v>
+      </c>
+      <c r="FC57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FE57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -45653,6 +48963,30 @@
       <c r="EO58">
         <v>52</v>
       </c>
+      <c r="EQ58">
+        <v>28</v>
+      </c>
+      <c r="ES58">
+        <v>52</v>
+      </c>
+      <c r="EU58">
+        <v>28</v>
+      </c>
+      <c r="EW58">
+        <v>52</v>
+      </c>
+      <c r="EY58">
+        <v>28</v>
+      </c>
+      <c r="FA58">
+        <v>52</v>
+      </c>
+      <c r="FC58">
+        <v>30</v>
+      </c>
+      <c r="FE58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -45920,6 +49254,30 @@
       <c r="EO59">
         <v>13</v>
       </c>
+      <c r="EQ59">
+        <v>0</v>
+      </c>
+      <c r="ES59">
+        <v>13</v>
+      </c>
+      <c r="EU59">
+        <v>0</v>
+      </c>
+      <c r="EW59">
+        <v>13</v>
+      </c>
+      <c r="EY59">
+        <v>0</v>
+      </c>
+      <c r="FA59">
+        <v>13</v>
+      </c>
+      <c r="FC59">
+        <v>0</v>
+      </c>
+      <c r="FE59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -46187,6 +49545,30 @@
       <c r="EO60">
         <v>52</v>
       </c>
+      <c r="EQ60">
+        <v>40</v>
+      </c>
+      <c r="ES60">
+        <v>52</v>
+      </c>
+      <c r="EU60">
+        <v>40</v>
+      </c>
+      <c r="EW60">
+        <v>52</v>
+      </c>
+      <c r="EY60">
+        <v>40</v>
+      </c>
+      <c r="FA60">
+        <v>52</v>
+      </c>
+      <c r="FC60">
+        <v>30</v>
+      </c>
+      <c r="FE60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -46452,6 +49834,30 @@
         <v>0</v>
       </c>
       <c r="EO61">
+        <v>13</v>
+      </c>
+      <c r="EQ61">
+        <v>0</v>
+      </c>
+      <c r="ES61">
+        <v>13</v>
+      </c>
+      <c r="EU61">
+        <v>0</v>
+      </c>
+      <c r="EW61">
+        <v>13</v>
+      </c>
+      <c r="EY61">
+        <v>0</v>
+      </c>
+      <c r="FA61">
+        <v>13</v>
+      </c>
+      <c r="FC61">
+        <v>0</v>
+      </c>
+      <c r="FE61">
         <v>13</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -31098,29 +31098,61 @@
       <c r="E1069" s="7"/>
     </row>
     <row r="1070" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1070" s="7"/>
-      <c r="B1070" s="7"/>
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_GOAL_HAMZA</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6C2</t>
+        </is>
+      </c>
       <c r="C1070" s="7"/>
       <c r="D1070" s="7"/>
       <c r="E1070" s="7"/>
     </row>
     <row r="1071" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1071" s="7"/>
-      <c r="B1071" s="7"/>
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA_GOAL</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6C3</t>
+        </is>
+      </c>
       <c r="C1071" s="7"/>
       <c r="D1071" s="7"/>
       <c r="E1071" s="7"/>
     </row>
     <row r="1072" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1072" s="7"/>
-      <c r="B1072" s="7"/>
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_BARREE_HAMZA</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6D3</t>
+        </is>
+      </c>
       <c r="C1072" s="7"/>
       <c r="D1072" s="7"/>
       <c r="E1072" s="7"/>
     </row>
     <row r="1073" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1073" s="7"/>
-      <c r="B1073" s="7"/>
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FULL_STOP</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6D4</t>
+        </is>
+      </c>
       <c r="C1073" s="7"/>
       <c r="D1073" s="7"/>
       <c r="E1073" s="7"/>
@@ -31500,7 +31532,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:FE79"/>
+  <dimension ref="A1:FI79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -31820,6 +31852,11 @@
           <t xml:space="preserve">mn-MN</t>
         </is>
       </c>
+      <c r="FF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ur-PK</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -32075,6 +32112,21 @@
       <c r="FC2" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_SHORT_I</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEH</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
         </is>
       </c>
     </row>
@@ -32330,6 +32382,21 @@
           <t xml:space="preserve">CYRILLIC_EM</t>
         </is>
       </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -32594,6 +32661,21 @@
           <t xml:space="preserve">CYRILLIC_IO</t>
         </is>
       </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_BARREE</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_BARREE_HAMZA</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_BARREE</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -32848,6 +32930,21 @@
           <t xml:space="preserve">CYRILLIC_BE</t>
         </is>
       </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_RREH</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -33158,6 +33255,21 @@
       <c r="FC6" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_U</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_DOACHASHMEE</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_DOACHASHMEE</t>
         </is>
       </c>
     </row>
@@ -33413,6 +33525,21 @@
           <t xml:space="preserve">CYRILLIC_BARRED_O</t>
         </is>
       </c>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON_GHUNNA</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -33669,6 +33796,21 @@
           <t xml:space="preserve">CYRILLIC_A</t>
         </is>
       </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_GOAL_HAMZA</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -33915,6 +34057,21 @@
           <t xml:space="preserve">CYRILLIC_HA</t>
         </is>
       </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_GOAL</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH_GOAL</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -34174,6 +34331,21 @@
       <c r="FC10" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_SHA</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="FH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
         </is>
       </c>
     </row>
@@ -34426,6 +34598,21 @@
           <t xml:space="preserve">CYRILLIC_ER</t>
         </is>
       </c>
+      <c r="FF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="FG11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MADDA_A</t>
+        </is>
+      </c>
+      <c r="FH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -34679,6 +34866,21 @@
           <t xml:space="preserve">CYRILLIC_O</t>
         </is>
       </c>
+      <c r="FF12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
+      <c r="FG12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
+      <c r="FH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -34934,6 +35136,21 @@
           <t xml:space="preserve">CYRILLIC_EL</t>
         </is>
       </c>
+      <c r="FF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
+      <c r="FG13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="FH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -35198,6 +35415,16 @@
       <c r="FC14" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_TE</t>
+        </is>
+      </c>
+      <c r="FF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="FH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
         </is>
       </c>
     </row>
@@ -35460,6 +35687,21 @@
           <t xml:space="preserve">CYRILLIC_I</t>
         </is>
       </c>
+      <c r="FF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="FG15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="FH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -35710,6 +35952,21 @@
           <t xml:space="preserve">CYRILLIC_STRAIGHT_U</t>
         </is>
       </c>
+      <c r="FF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="FG16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TCHEH</t>
+        </is>
+      </c>
+      <c r="FH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -35960,6 +36217,21 @@
           <t xml:space="preserve">CYRILLIC_ZE</t>
         </is>
       </c>
+      <c r="FF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="FG17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KHAH</t>
+        </is>
+      </c>
+      <c r="FH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -36237,6 +36509,21 @@
       <c r="FC18" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_EF</t>
+        </is>
+      </c>
+      <c r="FF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="FG18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="FH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
         </is>
       </c>
     </row>
@@ -36493,6 +36780,21 @@
           <t xml:space="preserve">CYRILLIC_ZHE</t>
         </is>
       </c>
+      <c r="FF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="FG19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DDAL</t>
+        </is>
+      </c>
+      <c r="FH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -36753,6 +37055,21 @@
       <c r="FC20" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_YERU</t>
+        </is>
+      </c>
+      <c r="FF20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="FG20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="FH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
         </is>
       </c>
     </row>
@@ -36999,6 +37316,21 @@
           <t xml:space="preserve">CYRILLIC_E</t>
         </is>
       </c>
+      <c r="FF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TTEH</t>
+        </is>
+      </c>
+      <c r="FG21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="FH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TTEH</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -37258,6 +37590,21 @@
           <t xml:space="preserve">CYRILLIC_GHE</t>
         </is>
       </c>
+      <c r="FF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="FG22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA_GOAL</t>
+        </is>
+      </c>
+      <c r="FH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -37513,6 +37860,16 @@
           <t xml:space="preserve">CYRILLIC_ES</t>
         </is>
       </c>
+      <c r="FF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="FH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -37778,6 +38135,21 @@
       <c r="FC24" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_TSE</t>
+        </is>
+      </c>
+      <c r="FF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="FG24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="FH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
         </is>
       </c>
     </row>
@@ -38030,6 +38402,16 @@
           <t xml:space="preserve">CYRILLIC_CHE</t>
         </is>
       </c>
+      <c r="FF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="FH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -38314,6 +38696,21 @@
           <t xml:space="preserve">CYRILLIC_EN</t>
         </is>
       </c>
+      <c r="FF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
+      <c r="FG26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHADDA</t>
+        </is>
+      </c>
+      <c r="FH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -38612,6 +39009,16 @@
           <t xml:space="preserve">CYRILLIC_YA</t>
         </is>
       </c>
+      <c r="FF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="FH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -39023,6 +39430,17 @@
         </is>
       </c>
       <c r="FD28">
+        <v>1</v>
+      </c>
+      <c r="FF28">
+        <v>1</v>
+      </c>
+      <c r="FG28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FH28">
         <v>1</v>
       </c>
     </row>
@@ -39459,6 +39877,17 @@
       <c r="FD29">
         <v>2</v>
       </c>
+      <c r="FF29">
+        <v>2</v>
+      </c>
+      <c r="FG29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="FH29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -39895,6 +40324,17 @@
       <c r="FD30">
         <v>3</v>
       </c>
+      <c r="FF30">
+        <v>3</v>
+      </c>
+      <c r="FG30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FH30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -40326,6 +40766,17 @@
       <c r="FD31">
         <v>4</v>
       </c>
+      <c r="FF31">
+        <v>4</v>
+      </c>
+      <c r="FG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FH31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -40757,6 +41208,12 @@
       <c r="FD32">
         <v>5</v>
       </c>
+      <c r="FF32">
+        <v>5</v>
+      </c>
+      <c r="FH32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -41176,6 +41633,17 @@
       <c r="FD33">
         <v>6</v>
       </c>
+      <c r="FF33">
+        <v>6</v>
+      </c>
+      <c r="FG33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FH33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -41608,6 +42076,12 @@
         </is>
       </c>
       <c r="FD34">
+        <v>7</v>
+      </c>
+      <c r="FF34">
+        <v>7</v>
+      </c>
+      <c r="FH34">
         <v>7</v>
       </c>
     </row>
@@ -42044,6 +42518,12 @@
       <c r="FD35">
         <v>8</v>
       </c>
+      <c r="FF35">
+        <v>8</v>
+      </c>
+      <c r="FH35">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -42476,6 +42956,17 @@
       <c r="FD36">
         <v>9</v>
       </c>
+      <c r="FF36">
+        <v>9</v>
+      </c>
+      <c r="FG36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="FH36">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -42930,6 +43421,21 @@
         </is>
       </c>
       <c r="FD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="FH37" t="inlineStr">
         <is>
           <t xml:space="preserve">ZERO</t>
         </is>
@@ -43929,6 +44435,21 @@
           <t xml:space="preserve">CYRILLIC_IE</t>
         </is>
       </c>
+      <c r="FF43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FG43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="FH43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -44353,6 +44874,21 @@
           <t xml:space="preserve">CYRILLIC_SHCHA</t>
         </is>
       </c>
+      <c r="FF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="FG44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FH44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">=</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -44759,6 +45295,21 @@
           <t xml:space="preserve">CYRILLIC_KA</t>
         </is>
       </c>
+      <c r="FF45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FG45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -45171,6 +45722,21 @@
           <t xml:space="preserve">CYRILLIC_HARD_SIGN</t>
         </is>
       </c>
+      <c r="FF46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="FG46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FH46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -45466,6 +46032,21 @@
       <c r="FD47" t="inlineStr">
         <is>
           <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FF47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FG47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FH47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
         </is>
       </c>
     </row>
@@ -46048,6 +46629,21 @@
           <t xml:space="preserve">CYRILLIC_DE</t>
         </is>
       </c>
+      <c r="FF49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="FG49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="FH49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
     </row>
     <row r="50" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="93" t="s">
@@ -46442,6 +47038,21 @@
           <t xml:space="preserve">CYRILLIC_PE</t>
         </is>
       </c>
+      <c r="FF50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FG50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -46797,6 +47408,21 @@
       <c r="FD51" t="inlineStr">
         <is>
           <t xml:space="preserve">=</t>
+        </is>
+      </c>
+      <c r="FF51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
+        </is>
+      </c>
+      <c r="FG51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FH51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">`</t>
         </is>
       </c>
     </row>
@@ -47119,6 +47745,21 @@
           <t xml:space="preserve">CYRILLIC_SOFT_SIGN</t>
         </is>
       </c>
+      <c r="FF52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="FG52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="FH52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -47433,6 +48074,21 @@
           <t xml:space="preserve">CYRILLIC_VE</t>
         </is>
       </c>
+      <c r="FF53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FULL_STOP</t>
+        </is>
+      </c>
+      <c r="FG53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FH53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FULL_STOP</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -47751,6 +48407,21 @@
       <c r="FC54" t="inlineStr">
         <is>
           <t xml:space="preserve">CYRILLIC_YU</t>
+        </is>
+      </c>
+      <c r="FF54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="FG54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QMARK</t>
+        </is>
+      </c>
+      <c r="FH54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
     </row>
@@ -48387,6 +49058,12 @@
       <c r="FE56">
         <v>50</v>
       </c>
+      <c r="FG56">
+        <v>42</v>
+      </c>
+      <c r="FI56">
+        <v>52</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -48696,6 +49373,12 @@
       <c r="FE57">
         <v>13</v>
       </c>
+      <c r="FG57">
+        <v>0</v>
+      </c>
+      <c r="FI57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -48987,6 +49670,12 @@
       <c r="FE58">
         <v>50</v>
       </c>
+      <c r="FG58">
+        <v>27</v>
+      </c>
+      <c r="FI58">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -49278,6 +49967,12 @@
       <c r="FE59">
         <v>13</v>
       </c>
+      <c r="FG59">
+        <v>0</v>
+      </c>
+      <c r="FI59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -49569,6 +50264,12 @@
       <c r="FE60">
         <v>50</v>
       </c>
+      <c r="FG60">
+        <v>42</v>
+      </c>
+      <c r="FI60">
+        <v>52</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -49858,6 +50559,12 @@
         <v>0</v>
       </c>
       <c r="FE61">
+        <v>13</v>
+      </c>
+      <c r="FG61">
+        <v>0</v>
+      </c>
+      <c r="FI61">
         <v>13</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -31158,78 +31158,166 @@
       <c r="E1073" s="7"/>
     </row>
     <row r="1074" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1074" s="7"/>
-      <c r="B1074" s="7"/>
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t xml:space="preserve">949</t>
+        </is>
+      </c>
       <c r="C1074" s="7"/>
       <c r="D1074" s="7"/>
       <c r="E1074" s="7"/>
     </row>
     <row r="1075" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1075" s="7"/>
-      <c r="B1075" s="7"/>
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_0</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F0</t>
+        </is>
+      </c>
       <c r="C1075" s="7"/>
       <c r="D1075" s="7"/>
       <c r="E1075" s="7"/>
     </row>
     <row r="1076" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1076" s="7"/>
-      <c r="B1076" s="7"/>
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_1</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F1</t>
+        </is>
+      </c>
       <c r="C1076" s="7"/>
       <c r="D1076" s="7"/>
       <c r="E1076" s="7"/>
     </row>
     <row r="1077" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1077" s="7"/>
-      <c r="B1077" s="7"/>
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_2</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F2</t>
+        </is>
+      </c>
       <c r="C1077" s="7"/>
       <c r="D1077" s="7"/>
       <c r="E1077" s="7"/>
     </row>
     <row r="1078" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1078" s="7"/>
-      <c r="B1078" s="7"/>
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_3</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F3</t>
+        </is>
+      </c>
       <c r="C1078" s="7"/>
       <c r="D1078" s="7"/>
       <c r="E1078" s="7"/>
     </row>
     <row r="1079" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1079" s="7"/>
-      <c r="B1079" s="7"/>
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_4</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F4</t>
+        </is>
+      </c>
       <c r="C1079" s="7"/>
       <c r="D1079" s="7"/>
       <c r="E1079" s="7"/>
     </row>
     <row r="1080" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1080" s="7"/>
-      <c r="B1080" s="7"/>
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_5</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F5</t>
+        </is>
+      </c>
       <c r="C1080" s="7"/>
       <c r="D1080" s="7"/>
       <c r="E1080" s="7"/>
     </row>
     <row r="1081" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1081" s="7"/>
-      <c r="B1081" s="7"/>
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_6</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F6</t>
+        </is>
+      </c>
       <c r="C1081" s="7"/>
       <c r="D1081" s="7"/>
       <c r="E1081" s="7"/>
     </row>
     <row r="1082" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1082" s="7"/>
-      <c r="B1082" s="7"/>
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_7</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F7</t>
+        </is>
+      </c>
       <c r="C1082" s="7"/>
       <c r="D1082" s="7"/>
       <c r="E1082" s="7"/>
     </row>
     <row r="1083" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1083" s="7"/>
-      <c r="B1083" s="7"/>
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_8</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F8</t>
+        </is>
+      </c>
       <c r="C1083" s="7"/>
       <c r="D1083" s="7"/>
       <c r="E1083" s="7"/>
     </row>
     <row r="1084" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1084" s="7"/>
-      <c r="B1084" s="7"/>
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_9</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6F9</t>
+        </is>
+      </c>
       <c r="C1084" s="7"/>
       <c r="D1084" s="7"/>
       <c r="E1084" s="7"/>
@@ -39343,6 +39431,11 @@
       <c r="DQ28">
         <v>1</v>
       </c>
+      <c r="DU28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_1</t>
+        </is>
+      </c>
       <c r="DV28">
         <v>1</v>
       </c>
@@ -39376,6 +39469,11 @@
       <c r="EJ28">
         <v>1</v>
       </c>
+      <c r="EO28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_1</t>
+        </is>
+      </c>
       <c r="EP28" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_0967</t>
@@ -39442,6 +39540,11 @@
       </c>
       <c r="FH28">
         <v>1</v>
+      </c>
+      <c r="FI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_1</t>
+        </is>
       </c>
     </row>
     <row r="29" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39783,6 +39886,11 @@
       <c r="DQ29">
         <v>2</v>
       </c>
+      <c r="DU29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_2</t>
+        </is>
+      </c>
       <c r="DV29">
         <v>2</v>
       </c>
@@ -39799,6 +39907,11 @@
           <t xml:space="preserve">@</t>
         </is>
       </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_2</t>
+        </is>
+      </c>
       <c r="ED29">
         <v>2</v>
       </c>
@@ -39821,6 +39934,11 @@
       <c r="EJ29">
         <v>2</v>
       </c>
+      <c r="EO29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_2</t>
+        </is>
+      </c>
       <c r="EP29" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_0968</t>
@@ -39887,6 +40005,11 @@
       </c>
       <c r="FH29">
         <v>2</v>
+      </c>
+      <c r="FI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_2</t>
+        </is>
       </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40230,6 +40353,11 @@
       <c r="DQ30">
         <v>3</v>
       </c>
+      <c r="DU30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_3</t>
+        </is>
+      </c>
       <c r="DV30">
         <v>3</v>
       </c>
@@ -40246,6 +40374,11 @@
           <t xml:space="preserve">POUND_SIGN</t>
         </is>
       </c>
+      <c r="EC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_3</t>
+        </is>
+      </c>
       <c r="ED30">
         <v>3</v>
       </c>
@@ -40268,6 +40401,11 @@
       <c r="EJ30">
         <v>3</v>
       </c>
+      <c r="EO30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_3</t>
+        </is>
+      </c>
       <c r="EP30" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_0969</t>
@@ -40334,6 +40472,11 @@
       </c>
       <c r="FH30">
         <v>3</v>
+      </c>
+      <c r="FI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_3</t>
+        </is>
       </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40677,6 +40820,11 @@
       <c r="DQ31">
         <v>4</v>
       </c>
+      <c r="DU31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
       <c r="DV31">
         <v>4</v>
       </c>
@@ -40693,6 +40841,11 @@
           <t xml:space="preserve">$</t>
         </is>
       </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
       <c r="ED31">
         <v>4</v>
       </c>
@@ -40715,6 +40868,11 @@
       <c r="EJ31">
         <v>4</v>
       </c>
+      <c r="EO31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_4</t>
+        </is>
+      </c>
       <c r="EP31" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096A</t>
@@ -40776,6 +40934,11 @@
       </c>
       <c r="FH31">
         <v>4</v>
+      </c>
+      <c r="FI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_4</t>
+        </is>
       </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41119,6 +41282,11 @@
       <c r="DQ32">
         <v>5</v>
       </c>
+      <c r="DU32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HALF_SIGN</t>
+        </is>
+      </c>
       <c r="DV32">
         <v>5</v>
       </c>
@@ -41130,6 +41298,11 @@
       <c r="DX32">
         <v>5</v>
       </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENT_SIGN</t>
+        </is>
+      </c>
       <c r="ED32">
         <v>5</v>
       </c>
@@ -41152,6 +41325,11 @@
       <c r="EJ32">
         <v>5</v>
       </c>
+      <c r="EO32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_5</t>
+        </is>
+      </c>
       <c r="EP32" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096B</t>
@@ -41213,6 +41391,11 @@
       </c>
       <c r="FH32">
         <v>5</v>
+      </c>
+      <c r="FI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_5</t>
+        </is>
       </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41544,6 +41727,11 @@
       <c r="DQ33">
         <v>6</v>
       </c>
+      <c r="DU33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THREE_QUATER_SIGN</t>
+        </is>
+      </c>
       <c r="DV33">
         <v>6</v>
       </c>
@@ -41555,6 +41743,11 @@
       <c r="DX33">
         <v>6</v>
       </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
       <c r="ED33">
         <v>6</v>
       </c>
@@ -41577,6 +41770,11 @@
       <c r="EJ33">
         <v>6</v>
       </c>
+      <c r="EO33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_6</t>
+        </is>
+      </c>
       <c r="EP33" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096C</t>
@@ -41643,6 +41841,11 @@
       </c>
       <c r="FH33">
         <v>6</v>
+      </c>
+      <c r="FI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_6</t>
+        </is>
       </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41984,6 +42187,11 @@
       <c r="DQ34">
         <v>7</v>
       </c>
+      <c r="DU34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
       <c r="DV34">
         <v>7</v>
       </c>
@@ -42022,6 +42230,11 @@
       <c r="EJ34">
         <v>7</v>
       </c>
+      <c r="EO34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_7</t>
+        </is>
+      </c>
       <c r="EP34" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096D</t>
@@ -42083,6 +42296,11 @@
       </c>
       <c r="FH34">
         <v>7</v>
+      </c>
+      <c r="FI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_7</t>
+        </is>
       </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42424,6 +42642,11 @@
       <c r="DQ35">
         <v>8</v>
       </c>
+      <c r="DU35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
       <c r="DV35">
         <v>8</v>
       </c>
@@ -42462,6 +42685,11 @@
       <c r="EJ35">
         <v>8</v>
       </c>
+      <c r="EO35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_8</t>
+        </is>
+      </c>
       <c r="EP35" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096E</t>
@@ -42523,6 +42751,11 @@
       </c>
       <c r="FH35">
         <v>8</v>
+      </c>
+      <c r="FI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_8</t>
+        </is>
       </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42862,6 +43095,11 @@
       <c r="DP36">
         <v>9</v>
       </c>
+      <c r="DU36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
       <c r="DV36">
         <v>9</v>
       </c>
@@ -42900,6 +43138,11 @@
       <c r="EJ36">
         <v>9</v>
       </c>
+      <c r="EO36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_9</t>
+        </is>
+      </c>
       <c r="EP36" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_096F</t>
@@ -42966,6 +43209,11 @@
       </c>
       <c r="FH36">
         <v>9</v>
+      </c>
+      <c r="FI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_9</t>
+        </is>
       </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43315,6 +43563,11 @@
           <t xml:space="preserve">ZERO</t>
         </is>
       </c>
+      <c r="DU37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
       <c r="DV37" t="inlineStr">
         <is>
           <t xml:space="preserve">ZERO</t>
@@ -43365,6 +43618,11 @@
           <t xml:space="preserve">ZERO</t>
         </is>
       </c>
+      <c r="EO37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_0</t>
+        </is>
+      </c>
       <c r="EP37" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVANAGARI_0966</t>
@@ -43438,6 +43696,11 @@
       <c r="FH37" t="inlineStr">
         <is>
           <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_EXT_INDIC_0</t>
         </is>
       </c>
     </row>
@@ -46017,6 +46280,51 @@
       <c r="EB47" t="inlineStr">
         <is>
           <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="EP47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="EQ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0911</t>
+        </is>
+      </c>
+      <c r="ER47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="ET47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="EU47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0911</t>
+        </is>
+      </c>
+      <c r="EV47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="EX47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
+        </is>
+      </c>
+      <c r="EY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0911</t>
+        </is>
+      </c>
+      <c r="EZ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVANAGARI_0949</t>
         </is>
       </c>
       <c r="FB47" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -38442,7 +38442,7 @@
       </c>
       <c r="EQ25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0901</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
         </is>
       </c>
       <c r="ER25" t="inlineStr">
@@ -38457,7 +38457,7 @@
       </c>
       <c r="EU25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0901</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
         </is>
       </c>
       <c r="EV25" t="inlineStr">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="EY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0901</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
         </is>
       </c>
       <c r="EZ25" t="inlineStr">
@@ -39946,7 +39946,7 @@
       </c>
       <c r="EQ29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0945</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
         </is>
       </c>
       <c r="ER29" t="inlineStr">
@@ -39961,7 +39961,7 @@
       </c>
       <c r="EU29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0945</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
         </is>
       </c>
       <c r="EV29" t="inlineStr">
@@ -39976,7 +39976,7 @@
       </c>
       <c r="EY29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0945</t>
+          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
         </is>
       </c>
       <c r="EZ29" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -31323,141 +31323,301 @@
       <c r="E1084" s="7"/>
     </row>
     <row r="1085" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1085" s="7"/>
-      <c r="B1085" s="7"/>
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0901</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E100</t>
+        </is>
+      </c>
       <c r="C1085" s="7"/>
       <c r="D1085" s="7"/>
       <c r="E1085" s="7"/>
     </row>
     <row r="1086" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1086" s="7"/>
-      <c r="B1086" s="7"/>
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0902</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E101</t>
+        </is>
+      </c>
       <c r="C1086" s="7"/>
       <c r="D1086" s="7"/>
       <c r="E1086" s="7"/>
     </row>
     <row r="1087" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1087" s="7"/>
-      <c r="B1087" s="7"/>
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0903</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E102</t>
+        </is>
+      </c>
       <c r="C1087" s="7"/>
       <c r="D1087" s="7"/>
       <c r="E1087" s="7"/>
     </row>
     <row r="1088" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1088" s="7"/>
-      <c r="B1088" s="7"/>
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_093C</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E103</t>
+        </is>
+      </c>
       <c r="C1088" s="7"/>
       <c r="D1088" s="7"/>
       <c r="E1088" s="7"/>
     </row>
     <row r="1089" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1089" s="7"/>
-      <c r="B1089" s="7"/>
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_093E</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E104</t>
+        </is>
+      </c>
       <c r="C1089" s="7"/>
       <c r="D1089" s="7"/>
       <c r="E1089" s="7"/>
     </row>
     <row r="1090" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1090" s="7"/>
-      <c r="B1090" s="7"/>
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_093F</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E105</t>
+        </is>
+      </c>
       <c r="C1090" s="7"/>
       <c r="D1090" s="7"/>
       <c r="E1090" s="7"/>
     </row>
     <row r="1091" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1091" s="7"/>
-      <c r="B1091" s="7"/>
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0940</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E106</t>
+        </is>
+      </c>
       <c r="C1091" s="7"/>
       <c r="D1091" s="7"/>
       <c r="E1091" s="7"/>
     </row>
     <row r="1092" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1092" s="7"/>
-      <c r="B1092" s="7"/>
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0941</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E107</t>
+        </is>
+      </c>
       <c r="C1092" s="7"/>
       <c r="D1092" s="7"/>
       <c r="E1092" s="7"/>
     </row>
     <row r="1093" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1093" s="7"/>
-      <c r="B1093" s="7"/>
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0942</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E108</t>
+        </is>
+      </c>
       <c r="C1093" s="7"/>
       <c r="D1093" s="7"/>
       <c r="E1093" s="7"/>
     </row>
     <row r="1094" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1094" s="7"/>
-      <c r="B1094" s="7"/>
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0943</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E109</t>
+        </is>
+      </c>
       <c r="C1094" s="7"/>
       <c r="D1094" s="7"/>
       <c r="E1094" s="7"/>
     </row>
     <row r="1095" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1095" s="7"/>
-      <c r="B1095" s="7"/>
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0944</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10A</t>
+        </is>
+      </c>
       <c r="C1095" s="7"/>
       <c r="D1095" s="7"/>
       <c r="E1095" s="7"/>
     </row>
     <row r="1096" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1096" s="7"/>
-      <c r="B1096" s="7"/>
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0945</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10B</t>
+        </is>
+      </c>
       <c r="C1096" s="7"/>
       <c r="D1096" s="7"/>
       <c r="E1096" s="7"/>
     </row>
     <row r="1097" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1097" s="7"/>
-      <c r="B1097" s="7"/>
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0946</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10C</t>
+        </is>
+      </c>
       <c r="C1097" s="7"/>
       <c r="D1097" s="7"/>
       <c r="E1097" s="7"/>
     </row>
     <row r="1098" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1098" s="7"/>
-      <c r="B1098" s="7"/>
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0947</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10D</t>
+        </is>
+      </c>
       <c r="C1098" s="7"/>
       <c r="D1098" s="7"/>
       <c r="E1098" s="7"/>
     </row>
     <row r="1099" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1099" s="7"/>
-      <c r="B1099" s="7"/>
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0948</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10E</t>
+        </is>
+      </c>
       <c r="C1099" s="7"/>
       <c r="D1099" s="7"/>
       <c r="E1099" s="7"/>
     </row>
     <row r="1100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1100" s="7"/>
-      <c r="B1100" s="7"/>
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_0949</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E10F</t>
+        </is>
+      </c>
       <c r="C1100" s="7"/>
       <c r="D1100" s="7"/>
       <c r="E1100" s="7"/>
     </row>
     <row r="1101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1101" s="7"/>
-      <c r="B1101" s="7"/>
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_094A</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E110</t>
+        </is>
+      </c>
       <c r="C1101" s="7"/>
       <c r="D1101" s="7"/>
       <c r="E1101" s="7"/>
     </row>
     <row r="1102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1102" s="7"/>
-      <c r="B1102" s="7"/>
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_094B</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E111</t>
+        </is>
+      </c>
       <c r="C1102" s="7"/>
       <c r="D1102" s="7"/>
       <c r="E1102" s="7"/>
     </row>
     <row r="1103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1103" s="7"/>
-      <c r="B1103" s="7"/>
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_094C</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E112</t>
+        </is>
+      </c>
       <c r="C1103" s="7"/>
       <c r="D1103" s="7"/>
       <c r="E1103" s="7"/>
     </row>
     <row r="1104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1104" s="7"/>
-      <c r="B1104" s="7"/>
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVA_DC_094D</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E113</t>
+        </is>
+      </c>
       <c r="C1104" s="7"/>
       <c r="D1104" s="7"/>
       <c r="E1104" s="7"/>
@@ -32149,7 +32309,7 @@
       </c>
       <c r="EP2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr">
@@ -32159,12 +32319,12 @@
       </c>
       <c r="ER2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="ET2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="EU2" t="inlineStr">
@@ -32174,12 +32334,12 @@
       </c>
       <c r="EV2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="EY2" t="inlineStr">
@@ -32189,7 +32349,7 @@
       </c>
       <c r="EZ2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094B</t>
+          <t xml:space="preserve">DEVA_DC_094B</t>
         </is>
       </c>
       <c r="FB2" t="inlineStr">
@@ -32965,7 +33125,7 @@
       </c>
       <c r="EP5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="EQ5" t="inlineStr">
@@ -32975,12 +33135,12 @@
       </c>
       <c r="ER5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -32990,12 +33150,12 @@
       </c>
       <c r="EV5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
@@ -33005,7 +33165,7 @@
       </c>
       <c r="EZ5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094D</t>
+          <t xml:space="preserve">DEVA_DC_094D</t>
         </is>
       </c>
       <c r="FB5" t="inlineStr">
@@ -33292,7 +33452,7 @@
       </c>
       <c r="EP6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="EQ6" t="inlineStr">
@@ -33302,12 +33462,12 @@
       </c>
       <c r="ER6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="ET6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="EU6" t="inlineStr">
@@ -33317,12 +33477,12 @@
       </c>
       <c r="EV6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="EX6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="EY6" t="inlineStr">
@@ -33332,7 +33492,7 @@
       </c>
       <c r="EZ6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093E</t>
+          <t xml:space="preserve">DEVA_DC_093E</t>
         </is>
       </c>
       <c r="FB6" t="inlineStr">
@@ -33560,7 +33720,7 @@
       </c>
       <c r="EP7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="EQ7" t="inlineStr">
@@ -33570,12 +33730,12 @@
       </c>
       <c r="ER7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="ET7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="EU7" t="inlineStr">
@@ -33585,12 +33745,12 @@
       </c>
       <c r="EV7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="EX7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="EY7" t="inlineStr">
@@ -33600,7 +33760,7 @@
       </c>
       <c r="EZ7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093F</t>
+          <t xml:space="preserve">DEVA_DC_093F</t>
         </is>
       </c>
       <c r="FB7" t="inlineStr">
@@ -33831,7 +33991,7 @@
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="EQ8" t="inlineStr">
@@ -33841,12 +34001,12 @@
       </c>
       <c r="ER8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="ET8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="EU8" t="inlineStr">
@@ -33856,12 +34016,12 @@
       </c>
       <c r="EV8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="EX8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="EY8" t="inlineStr">
@@ -33871,7 +34031,7 @@
       </c>
       <c r="EZ8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0941</t>
+          <t xml:space="preserve">DEVA_DC_0941</t>
         </is>
       </c>
       <c r="FB8" t="inlineStr">
@@ -36546,7 +36706,7 @@
       </c>
       <c r="EP18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="EQ18" t="inlineStr">
@@ -36556,12 +36716,12 @@
       </c>
       <c r="ER18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="ET18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="EU18" t="inlineStr">
@@ -36571,12 +36731,12 @@
       </c>
       <c r="EV18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="EX18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="EY18" t="inlineStr">
@@ -36586,7 +36746,7 @@
       </c>
       <c r="EZ18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094C</t>
+          <t xml:space="preserve">DEVA_DC_094C</t>
         </is>
       </c>
       <c r="FB18" t="inlineStr">
@@ -36815,7 +36975,7 @@
       </c>
       <c r="EP19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="EQ19" t="inlineStr">
@@ -36825,12 +36985,12 @@
       </c>
       <c r="ER19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="ET19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="EU19" t="inlineStr">
@@ -36840,12 +37000,12 @@
       </c>
       <c r="EV19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="EX19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="EY19" t="inlineStr">
@@ -36855,7 +37015,7 @@
       </c>
       <c r="EZ19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0940</t>
+          <t xml:space="preserve">DEVA_DC_0940</t>
         </is>
       </c>
       <c r="FB19" t="inlineStr">
@@ -37092,7 +37252,7 @@
       </c>
       <c r="EP20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="EQ20" t="inlineStr">
@@ -37102,12 +37262,12 @@
       </c>
       <c r="ER20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="ET20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="EU20" t="inlineStr">
@@ -37117,12 +37277,12 @@
       </c>
       <c r="EV20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="EX20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="EY20" t="inlineStr">
@@ -37132,7 +37292,7 @@
       </c>
       <c r="EZ20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0947</t>
+          <t xml:space="preserve">DEVA_DC_0947</t>
         </is>
       </c>
       <c r="FB20" t="inlineStr">
@@ -37351,7 +37511,7 @@
       </c>
       <c r="EP21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="EQ21" t="inlineStr">
@@ -37361,12 +37521,12 @@
       </c>
       <c r="ER21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="ET21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="EU21" t="inlineStr">
@@ -37376,12 +37536,12 @@
       </c>
       <c r="EV21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="EX21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="EY21" t="inlineStr">
@@ -37391,7 +37551,7 @@
       </c>
       <c r="EZ21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0942</t>
+          <t xml:space="preserve">DEVA_DC_0942</t>
         </is>
       </c>
       <c r="FB21" t="inlineStr">
@@ -38172,7 +38332,7 @@
       </c>
       <c r="EP24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="EQ24" t="inlineStr">
@@ -38182,12 +38342,12 @@
       </c>
       <c r="ER24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="ET24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="EU24" t="inlineStr">
@@ -38197,12 +38357,12 @@
       </c>
       <c r="EV24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="EX24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="EY24" t="inlineStr">
@@ -38212,7 +38372,7 @@
       </c>
       <c r="EZ24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0948</t>
+          <t xml:space="preserve">DEVA_DC_0948</t>
         </is>
       </c>
       <c r="FB24" t="inlineStr">
@@ -38437,47 +38597,47 @@
       </c>
       <c r="EP25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="EQ25" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
+          <t xml:space="preserve">DEVA_DC_0901</t>
         </is>
       </c>
       <c r="ER25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="ET25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="EU25" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
+          <t xml:space="preserve">DEVA_DC_0901</t>
         </is>
       </c>
       <c r="EV25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="EX25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="EY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0901</t>
+          <t xml:space="preserve">DEVA_DC_0901</t>
         </is>
       </c>
       <c r="EZ25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0902</t>
+          <t xml:space="preserve">DEVA_DC_0902</t>
         </is>
       </c>
       <c r="FB25" t="inlineStr">
@@ -39044,7 +39204,7 @@
       </c>
       <c r="EP27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="EQ27" t="inlineStr">
@@ -39054,12 +39214,12 @@
       </c>
       <c r="ER27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="ET27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="EU27" t="inlineStr">
@@ -39069,12 +39229,12 @@
       </c>
       <c r="EV27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="EX27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="EY27" t="inlineStr">
@@ -39084,7 +39244,7 @@
       </c>
       <c r="EZ27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0946</t>
+          <t xml:space="preserve">DEVA_DC_0946</t>
         </is>
       </c>
       <c r="FB27" t="inlineStr">
@@ -39946,7 +40106,7 @@
       </c>
       <c r="EQ29" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
+          <t xml:space="preserve">DEVA_DC_0945</t>
         </is>
       </c>
       <c r="ER29" t="inlineStr">
@@ -39961,7 +40121,7 @@
       </c>
       <c r="EU29" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
+          <t xml:space="preserve">DEVA_DC_0945</t>
         </is>
       </c>
       <c r="EV29" t="inlineStr">
@@ -39976,7 +40136,7 @@
       </c>
       <c r="EY29" t="inlineStr">
         <is>
-          <t xml:space="preserve">u"\v" DEVANAGARI_0945</t>
+          <t xml:space="preserve">DEVA_DC_0945</t>
         </is>
       </c>
       <c r="EZ29" t="inlineStr">
@@ -44650,7 +44810,7 @@
       </c>
       <c r="EQ43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0903</t>
+          <t xml:space="preserve">DEVA_DC_0903</t>
         </is>
       </c>
       <c r="ER43" t="inlineStr">
@@ -44665,7 +44825,7 @@
       </c>
       <c r="EU43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0903</t>
+          <t xml:space="preserve">DEVA_DC_0903</t>
         </is>
       </c>
       <c r="EV43" t="inlineStr">
@@ -44680,7 +44840,7 @@
       </c>
       <c r="EY43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0903</t>
+          <t xml:space="preserve">DEVA_DC_0903</t>
         </is>
       </c>
       <c r="EZ43" t="inlineStr">
@@ -45084,7 +45244,7 @@
       </c>
       <c r="EP44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="EQ44" t="inlineStr">
@@ -45094,12 +45254,12 @@
       </c>
       <c r="ER44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="ET44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="EU44" t="inlineStr">
@@ -45109,12 +45269,12 @@
       </c>
       <c r="EV44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="EX44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="EY44" t="inlineStr">
@@ -45124,7 +45284,7 @@
       </c>
       <c r="EZ44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0943</t>
+          <t xml:space="preserve">DEVA_DC_0943</t>
         </is>
       </c>
       <c r="FB44" t="inlineStr">
@@ -45932,7 +46092,7 @@
       </c>
       <c r="EP46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="EQ46" t="inlineStr">
@@ -45942,12 +46102,12 @@
       </c>
       <c r="ER46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="ET46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="EU46" t="inlineStr">
@@ -45957,12 +46117,12 @@
       </c>
       <c r="EV46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="EX46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="EY46" t="inlineStr">
@@ -45972,7 +46132,7 @@
       </c>
       <c r="EZ46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_093C</t>
+          <t xml:space="preserve">DEVA_DC_093C</t>
         </is>
       </c>
       <c r="FB46" t="inlineStr">
@@ -46284,7 +46444,7 @@
       </c>
       <c r="EP47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="EQ47" t="inlineStr">
@@ -46294,12 +46454,12 @@
       </c>
       <c r="ER47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="ET47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="EU47" t="inlineStr">
@@ -46309,12 +46469,12 @@
       </c>
       <c r="EV47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="EX47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="EY47" t="inlineStr">
@@ -46324,7 +46484,7 @@
       </c>
       <c r="EZ47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_0949</t>
+          <t xml:space="preserve">DEVA_DC_0949</t>
         </is>
       </c>
       <c r="FB47" t="inlineStr">
@@ -47660,7 +47820,7 @@
       </c>
       <c r="EP51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="EQ51" t="inlineStr">
@@ -47670,12 +47830,12 @@
       </c>
       <c r="ER51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="ET51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="EU51" t="inlineStr">
@@ -47685,12 +47845,12 @@
       </c>
       <c r="EV51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="EX51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="EY51" t="inlineStr">
@@ -47700,7 +47860,7 @@
       </c>
       <c r="EZ51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEVANAGARI_094A</t>
+          <t xml:space="preserve">DEVA_DC_094A</t>
         </is>
       </c>
       <c r="FB51" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -49526,8 +49526,11 @@
       <c r="FE56">
         <v>50</v>
       </c>
+      <c r="FF56">
+        <v>0</v>
+      </c>
       <c r="FG56">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="FI56">
         <v>52</v>
@@ -49841,8 +49844,11 @@
       <c r="FE57">
         <v>13</v>
       </c>
+      <c r="FF57">
+        <v>0</v>
+      </c>
       <c r="FG57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="FI57">
         <v>13</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -31780,7 +31780,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:FI79"/>
+  <dimension ref="A1:GC79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -32105,6 +32105,46 @@
           <t xml:space="preserve">ur-PK</t>
         </is>
       </c>
+      <c r="FJ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-GB</t>
+        </is>
+      </c>
+      <c r="FM1">
+        <v>2057</v>
+      </c>
+      <c r="FN1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">es-MX</t>
+        </is>
+      </c>
+      <c r="FQ1">
+        <v>2058</v>
+      </c>
+      <c r="FR1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de-CH</t>
+        </is>
+      </c>
+      <c r="FU1">
+        <v>2055</v>
+      </c>
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fr-BE</t>
+        </is>
+      </c>
+      <c r="FY1">
+        <v>2060</v>
+      </c>
+      <c r="FZ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fr-CA</t>
+        </is>
+      </c>
+      <c r="GC1">
+        <v>3084</v>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -32375,6 +32415,16 @@
       <c r="FH2" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="FW2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q</t>
         </is>
       </c>
     </row>
@@ -33520,6 +33570,51 @@
           <t xml:space="preserve">ARABIC_HEH_DOACHASHMEE</t>
         </is>
       </c>
+      <c r="FR6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e</t>
+        </is>
+      </c>
+      <c r="FS6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="FU6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="FV6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e</t>
+        </is>
+      </c>
+      <c r="FW6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="FY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="FZ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e</t>
+        </is>
+      </c>
+      <c r="GA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="GC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="7" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="93" t="s">
@@ -35675,6 +35770,21 @@
           <t xml:space="preserve">ARABIC_AIN</t>
         </is>
       </c>
+      <c r="FV14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="FW14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="FX14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
     </row>
     <row r="15" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="93" t="s">
@@ -36774,6 +36884,16 @@
           <t xml:space="preserve">ARABIC_TAH</t>
         </is>
       </c>
+      <c r="FV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="FW18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
     </row>
     <row r="19" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="93" t="s">
@@ -38400,6 +38520,16 @@
           <t xml:space="preserve">ARABIC_SAD</t>
         </is>
       </c>
+      <c r="FV24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="FW24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
     </row>
     <row r="25" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="93" t="s">
@@ -38959,6 +39089,16 @@
           <t xml:space="preserve">ARABIC_PEH</t>
         </is>
       </c>
+      <c r="FR26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="FS26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -39267,6 +39407,26 @@
           <t xml:space="preserve">ARABIC_QAF</t>
         </is>
       </c>
+      <c r="FR27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y</t>
+        </is>
+      </c>
+      <c r="FS27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="FV27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w</t>
+        </is>
+      </c>
+      <c r="FW27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -39704,6 +39864,72 @@
       <c r="FI28" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_EXT_INDIC_1</t>
+        </is>
+      </c>
+      <c r="FN28">
+        <v>1</v>
+      </c>
+      <c r="FO28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FP28">
+        <v>1</v>
+      </c>
+      <c r="FQ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FR28">
+        <v>1</v>
+      </c>
+      <c r="FS28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FT28">
+        <v>1</v>
+      </c>
+      <c r="FU28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FV28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="FW28">
+        <v>1</v>
+      </c>
+      <c r="FX28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="FY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FZ28">
+        <v>1</v>
+      </c>
+      <c r="GA28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="GB28">
+        <v>1</v>
+      </c>
+      <c r="GC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLUS_MINUS</t>
         </is>
       </c>
     </row>
@@ -40171,6 +40397,67 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_2</t>
         </is>
       </c>
+      <c r="FJ29">
+        <v>2</v>
+      </c>
+      <c r="FK29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FL29">
+        <v>2</v>
+      </c>
+      <c r="FR29">
+        <v>2</v>
+      </c>
+      <c r="FS29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FT29">
+        <v>2</v>
+      </c>
+      <c r="FU29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="FV29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_ACUTE_SMALL</t>
+        </is>
+      </c>
+      <c r="FW29">
+        <v>2</v>
+      </c>
+      <c r="FX29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_ACUTE_SMALL</t>
+        </is>
+      </c>
+      <c r="FY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="FZ29">
+        <v>2</v>
+      </c>
+      <c r="GA29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="GB29">
+        <v>2</v>
+      </c>
+      <c r="GC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -40638,6 +40925,83 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_3</t>
         </is>
       </c>
+      <c r="FJ30">
+        <v>3</v>
+      </c>
+      <c r="FK30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="FL30">
+        <v>3</v>
+      </c>
+      <c r="FN30">
+        <v>3</v>
+      </c>
+      <c r="FO30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FP30">
+        <v>3</v>
+      </c>
+      <c r="FQ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDDLE_DOT</t>
+        </is>
+      </c>
+      <c r="FR30">
+        <v>3</v>
+      </c>
+      <c r="FS30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="FT30">
+        <v>3</v>
+      </c>
+      <c r="FU30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FV30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FW30">
+        <v>3</v>
+      </c>
+      <c r="FX30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="FY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FZ30">
+        <v>3</v>
+      </c>
+      <c r="GA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="GB30">
+        <v>3</v>
+      </c>
+      <c r="GC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -41100,6 +41464,78 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_4</t>
         </is>
       </c>
+      <c r="FJ31">
+        <v>4</v>
+      </c>
+      <c r="FK31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FL31">
+        <v>4</v>
+      </c>
+      <c r="FM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="FN31">
+        <v>4</v>
+      </c>
+      <c r="FO31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FP31">
+        <v>4</v>
+      </c>
+      <c r="FQ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FR31">
+        <v>4</v>
+      </c>
+      <c r="FS31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="FT31">
+        <v>4</v>
+      </c>
+      <c r="FV31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FW31">
+        <v>4</v>
+      </c>
+      <c r="FX31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FZ31">
+        <v>4</v>
+      </c>
+      <c r="GA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="GB31">
+        <v>4</v>
+      </c>
+      <c r="GC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENT_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -41557,6 +41993,35 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_5</t>
         </is>
       </c>
+      <c r="FV32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="FW32">
+        <v>5</v>
+      </c>
+      <c r="FX32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="FZ32">
+        <v>5</v>
+      </c>
+      <c r="GA32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="GB32">
+        <v>5</v>
+      </c>
+      <c r="GC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -42007,6 +42472,72 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_6</t>
         </is>
       </c>
+      <c r="FN33">
+        <v>6</v>
+      </c>
+      <c r="FO33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="FP33">
+        <v>6</v>
+      </c>
+      <c r="FQ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="FR33">
+        <v>6</v>
+      </c>
+      <c r="FS33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="FT33">
+        <v>6</v>
+      </c>
+      <c r="FU33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="FV33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="FW33">
+        <v>6</v>
+      </c>
+      <c r="FX33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="FY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FZ33">
+        <v>6</v>
+      </c>
+      <c r="GA33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="GB33">
+        <v>6</v>
+      </c>
+      <c r="GC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -42460,6 +42991,56 @@
       <c r="FI34" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_EXT_INDIC_7</t>
+        </is>
+      </c>
+      <c r="FR34">
+        <v>7</v>
+      </c>
+      <c r="FS34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="FT34">
+        <v>7</v>
+      </c>
+      <c r="FU34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FV34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FW34">
+        <v>7</v>
+      </c>
+      <c r="FX34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FZ34">
+        <v>7</v>
+      </c>
+      <c r="GA34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="GB34">
+        <v>7</v>
+      </c>
+      <c r="GC34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BROKEN_BAR</t>
         </is>
       </c>
     </row>
@@ -42917,6 +43498,56 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_8</t>
         </is>
       </c>
+      <c r="FR35">
+        <v>8</v>
+      </c>
+      <c r="FS35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="FT35">
+        <v>8</v>
+      </c>
+      <c r="FU35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENT_SIGN</t>
+        </is>
+      </c>
+      <c r="FV35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FW35">
+        <v>8</v>
+      </c>
+      <c r="FX35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="FZ35">
+        <v>8</v>
+      </c>
+      <c r="GA35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="GB35">
+        <v>8</v>
+      </c>
+      <c r="GC35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_2</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -43375,6 +44006,51 @@
           <t xml:space="preserve">ARABIC_EXT_INDIC_9</t>
         </is>
       </c>
+      <c r="FR36">
+        <v>9</v>
+      </c>
+      <c r="FS36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="FT36">
+        <v>9</v>
+      </c>
+      <c r="FV36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="FW36">
+        <v>9</v>
+      </c>
+      <c r="FX36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="FY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FZ36">
+        <v>9</v>
+      </c>
+      <c r="GA36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="GB36">
+        <v>9</v>
+      </c>
+      <c r="GC36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_3</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -43861,6 +44537,61 @@
       <c r="FI37" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_EXT_INDIC_0</t>
+        </is>
+      </c>
+      <c r="FR37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FS37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="FT37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FV37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FW37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="FX37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FZ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="GA37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="GB37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="GC37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUATER_SIGN</t>
         </is>
       </c>
     </row>
@@ -44873,6 +45604,86 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
+      <c r="FN43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FO43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="FP43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FQ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FR43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FS43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="FT43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FU43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FV43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="FW43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="FX43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="FY43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FZ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GA43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="GB43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GC43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HALF_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -45312,6 +46123,76 @@
           <t xml:space="preserve">=</t>
         </is>
       </c>
+      <c r="FN44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_QMARK</t>
+        </is>
+      </c>
+      <c r="FO44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_EMARK</t>
+        </is>
+      </c>
+      <c r="FP44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_QMARK</t>
+        </is>
+      </c>
+      <c r="FR44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FS44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FT44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FU44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FV44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FW44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="FX44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FZ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="GA44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="GB44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="GC44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THREE_QUATER_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -45733,6 +46614,81 @@
           <t xml:space="preserve">]</t>
         </is>
       </c>
+      <c r="FN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FO45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="FP45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FR45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_U_SMALL</t>
+        </is>
+      </c>
+      <c r="FS45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FT45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_U_SMALL</t>
+        </is>
+      </c>
+      <c r="FU45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="FV45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FW45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="FX45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FY45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="FZ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GA45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GB45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GC45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -46160,6 +47116,86 @@
           <t xml:space="preserve">[</t>
         </is>
       </c>
+      <c r="FN46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FO46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="FP46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FQ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FR46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="FS46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="FT46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="FU46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FV46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FW46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="FX46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FY46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FZ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
+      <c r="GA46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="GB46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEDILLA</t>
+        </is>
+      </c>
+      <c r="GC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -46515,6 +47551,101 @@
       <c r="FH47" t="inlineStr">
         <is>
           <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FK47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FL47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FN47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FO47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FP47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FQ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FR47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FS47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="FT47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FU47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FV47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICRO_SIGN</t>
+        </is>
+      </c>
+      <c r="FW47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="FX47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICRO_SIGN</t>
+        </is>
+      </c>
+      <c r="FY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FZ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="GA47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="GB47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="GC47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
         </is>
       </c>
     </row>
@@ -46712,6 +47843,101 @@
           <t xml:space="preserve">CYRILLIC_ZHE</t>
         </is>
       </c>
+      <c r="FJ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FK48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="FL48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="FN48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FO48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="FP48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FQ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FR48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FS48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="FT48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="FU48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="FV48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICRO_SIGN</t>
+        </is>
+      </c>
+      <c r="FW48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="FX48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICRO_SIGN</t>
+        </is>
+      </c>
+      <c r="FY48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FZ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="GA48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="GB48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="GC48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -47110,6 +48336,66 @@
       <c r="FH49" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="FN49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE_SMALL</t>
+        </is>
+      </c>
+      <c r="FO49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE</t>
+        </is>
+      </c>
+      <c r="FP49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE_SMALL</t>
+        </is>
+      </c>
+      <c r="FR49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O_SMALL</t>
+        </is>
+      </c>
+      <c r="FS49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E_WITH_ACUTE_SMALL</t>
+        </is>
+      </c>
+      <c r="FT49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O_SMALL</t>
+        </is>
+      </c>
+      <c r="FV49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="FW49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
+      <c r="FZ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="GA49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="GB49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="GC49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
         </is>
       </c>
     </row>
@@ -47521,6 +48807,101 @@
           <t xml:space="preserve">'</t>
         </is>
       </c>
+      <c r="FJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="FL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="FN50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FO50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="FP50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FQ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="FR50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_A_SMALL</t>
+        </is>
+      </c>
+      <c r="FS50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FT50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_A_SMALL</t>
+        </is>
+      </c>
+      <c r="FU50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="FV50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FW50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="FX50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="FY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FZ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="GA50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="GB50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="GC50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -47891,6 +49272,101 @@
       <c r="FH51" t="inlineStr">
         <is>
           <t xml:space="preserve">`</t>
+        </is>
+      </c>
+      <c r="FJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FK51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="FL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="FM51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FO51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="FP51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FQ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="FR51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="FS51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="FT51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
+        </is>
+      </c>
+      <c r="FV51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_2</t>
+        </is>
+      </c>
+      <c r="FW51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_3</t>
+        </is>
+      </c>
+      <c r="FX51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUPER_SCRIPT_2</t>
+        </is>
+      </c>
+      <c r="FY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="FZ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="GA51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="GB51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="GC51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
         </is>
       </c>
     </row>
@@ -48228,6 +49704,36 @@
           <t xml:space="preserve">ARABIC_COMMA</t>
         </is>
       </c>
+      <c r="FR52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="FS52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="FT52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="FV52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="FW52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="FX52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -48557,6 +50063,36 @@
           <t xml:space="preserve">ARABIC_FULL_STOP</t>
         </is>
       </c>
+      <c r="FR53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="FS53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="FT53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="FV53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="FW53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="FX53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -48890,6 +50426,36 @@
       <c r="FH54" t="inlineStr">
         <is>
           <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="FR54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FS54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="FT54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="FV54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="FW54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="FX54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
         </is>
       </c>
     </row>
@@ -49217,6 +50783,101 @@
           <t xml:space="preserve">(</t>
         </is>
       </c>
+      <c r="FJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="FL55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FN55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FO55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="FP55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FQ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FR55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FS55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="FT55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FU55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FV55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FW55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="FX55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="FY55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="FZ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_L</t>
+        </is>
+      </c>
+      <c r="GA55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
+        </is>
+      </c>
+      <c r="GB55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_L</t>
+        </is>
+      </c>
+      <c r="GC55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -49535,6 +51196,46 @@
       <c r="FI56">
         <v>52</v>
       </c>
+      <c r="FK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FM56">
+        <v>50</v>
+      </c>
+      <c r="FO56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FQ56">
+        <v>50</v>
+      </c>
+      <c r="FS56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FU56">
+        <v>50</v>
+      </c>
+      <c r="FW56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FY56">
+        <v>50</v>
+      </c>
+      <c r="GA56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="GC56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -49853,6 +51554,46 @@
       <c r="FI57">
         <v>13</v>
       </c>
+      <c r="FK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FM57">
+        <v>13</v>
+      </c>
+      <c r="FO57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FQ57">
+        <v>13</v>
+      </c>
+      <c r="FS57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FU57">
+        <v>13</v>
+      </c>
+      <c r="FW57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="FY57">
+        <v>13</v>
+      </c>
+      <c r="GA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="GC57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -50150,6 +51891,36 @@
       <c r="FI58">
         <v>52</v>
       </c>
+      <c r="FK58">
+        <v>28</v>
+      </c>
+      <c r="FM58">
+        <v>50</v>
+      </c>
+      <c r="FO58">
+        <v>28</v>
+      </c>
+      <c r="FQ58">
+        <v>50</v>
+      </c>
+      <c r="FS58">
+        <v>28</v>
+      </c>
+      <c r="FU58">
+        <v>50</v>
+      </c>
+      <c r="FW58">
+        <v>28</v>
+      </c>
+      <c r="FY58">
+        <v>50</v>
+      </c>
+      <c r="GA58">
+        <v>28</v>
+      </c>
+      <c r="GC58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -50447,6 +52218,36 @@
       <c r="FI59">
         <v>13</v>
       </c>
+      <c r="FK59">
+        <v>0</v>
+      </c>
+      <c r="FM59">
+        <v>13</v>
+      </c>
+      <c r="FO59">
+        <v>0</v>
+      </c>
+      <c r="FQ59">
+        <v>13</v>
+      </c>
+      <c r="FS59">
+        <v>0</v>
+      </c>
+      <c r="FU59">
+        <v>13</v>
+      </c>
+      <c r="FW59">
+        <v>0</v>
+      </c>
+      <c r="FY59">
+        <v>13</v>
+      </c>
+      <c r="GA59">
+        <v>0</v>
+      </c>
+      <c r="GC59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -50744,6 +52545,36 @@
       <c r="FI60">
         <v>52</v>
       </c>
+      <c r="FK60">
+        <v>28</v>
+      </c>
+      <c r="FM60">
+        <v>50</v>
+      </c>
+      <c r="FO60">
+        <v>28</v>
+      </c>
+      <c r="FQ60">
+        <v>50</v>
+      </c>
+      <c r="FS60">
+        <v>28</v>
+      </c>
+      <c r="FU60">
+        <v>50</v>
+      </c>
+      <c r="FW60">
+        <v>28</v>
+      </c>
+      <c r="FY60">
+        <v>50</v>
+      </c>
+      <c r="GA60">
+        <v>28</v>
+      </c>
+      <c r="GC60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -51039,6 +52870,36 @@
         <v>0</v>
       </c>
       <c r="FI61">
+        <v>13</v>
+      </c>
+      <c r="FK61">
+        <v>0</v>
+      </c>
+      <c r="FM61">
+        <v>13</v>
+      </c>
+      <c r="FO61">
+        <v>0</v>
+      </c>
+      <c r="FQ61">
+        <v>13</v>
+      </c>
+      <c r="FS61">
+        <v>0</v>
+      </c>
+      <c r="FU61">
+        <v>13</v>
+      </c>
+      <c r="FW61">
+        <v>0</v>
+      </c>
+      <c r="FY61">
+        <v>13</v>
+      </c>
+      <c r="GA61">
+        <v>0</v>
+      </c>
+      <c r="GC61">
         <v>13</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -6068,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1125"/>
+  <dimension ref="A1:I1391"/>
   <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.25"/>
@@ -31623,143 +31623,3448 @@
       <c r="E1104" s="7"/>
     </row>
     <row r="1105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1105" s="7"/>
-      <c r="B1105" s="7"/>
-      <c r="C1105" s="7"/>
-      <c r="D1105" s="7"/>
-      <c r="E1105" s="7"/>
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0993</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0993</t>
+        </is>
+      </c>
     </row>
     <row r="1106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1106" s="7"/>
-      <c r="B1106" s="7"/>
-      <c r="C1106" s="7"/>
-      <c r="D1106" s="7"/>
-      <c r="E1106" s="7"/>
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AE</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AE</t>
+        </is>
+      </c>
     </row>
     <row r="1107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1107" s="7"/>
-      <c r="B1107" s="7"/>
-      <c r="C1107" s="7"/>
-      <c r="D1107" s="7"/>
-      <c r="E1107" s="7"/>
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A3</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A3</t>
+        </is>
+      </c>
     </row>
     <row r="1108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1108" s="7"/>
-      <c r="B1108" s="7"/>
-      <c r="C1108" s="7"/>
-      <c r="D1108" s="7"/>
-      <c r="E1108" s="7"/>
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0985</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0985</t>
+        </is>
+      </c>
     </row>
     <row r="1109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1109" s="7"/>
-      <c r="B1109" s="7"/>
-      <c r="C1109" s="7"/>
-      <c r="D1109" s="7"/>
-      <c r="E1109" s="7"/>
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0986</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0986</t>
+        </is>
+      </c>
     </row>
     <row r="1110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1110" s="7"/>
-      <c r="B1110" s="7"/>
-      <c r="C1110" s="7"/>
-      <c r="D1110" s="7"/>
-      <c r="E1110" s="7"/>
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0987</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0987</t>
+        </is>
+      </c>
     </row>
     <row r="1111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1111" s="7"/>
-      <c r="B1111" s="7"/>
-      <c r="C1111" s="7"/>
-      <c r="D1111" s="7"/>
-      <c r="E1111" s="7"/>
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0989</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0989</t>
+        </is>
+      </c>
     </row>
     <row r="1112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1112" s="7"/>
-      <c r="B1112" s="7"/>
-      <c r="C1112" s="7"/>
-      <c r="D1112" s="7"/>
-      <c r="E1112" s="7"/>
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AA</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AA</t>
+        </is>
+      </c>
     </row>
     <row r="1113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1113" s="7"/>
-      <c r="B1113" s="7"/>
-      <c r="C1113" s="7"/>
-      <c r="D1113" s="7"/>
-      <c r="E1113" s="7"/>
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AB</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AB</t>
+        </is>
+      </c>
     </row>
     <row r="1114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1114" s="7"/>
-      <c r="B1114" s="7"/>
-      <c r="C1114" s="7"/>
-      <c r="D1114" s="7"/>
-      <c r="E1114" s="7"/>
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0997</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0997</t>
+        </is>
+      </c>
     </row>
     <row r="1115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1115" s="7"/>
-      <c r="B1115" s="7"/>
-      <c r="C1115" s="7"/>
-      <c r="D1115" s="7"/>
-      <c r="E1115" s="7"/>
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0998</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0998</t>
+        </is>
+      </c>
     </row>
     <row r="1116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1116" s="7"/>
-      <c r="B1116" s="7"/>
-      <c r="C1116" s="7"/>
-      <c r="D1116" s="7"/>
-      <c r="E1116" s="7"/>
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B0</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B0</t>
+        </is>
+      </c>
     </row>
     <row r="1117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1117" s="7"/>
-      <c r="B1117" s="7"/>
-      <c r="C1117" s="7"/>
-      <c r="D1117" s="7"/>
-      <c r="E1117" s="7"/>
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0995</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0995</t>
+        </is>
+      </c>
     </row>
     <row r="1118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1118" s="7"/>
-      <c r="B1118" s="7"/>
-      <c r="C1118" s="7"/>
-      <c r="D1118" s="7"/>
-      <c r="E1118" s="7"/>
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0996</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0996</t>
+        </is>
+      </c>
     </row>
     <row r="1119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1119" s="7"/>
-      <c r="B1119" s="7"/>
-      <c r="C1119" s="7"/>
-      <c r="D1119" s="7"/>
-      <c r="E1119" s="7"/>
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A4</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A4</t>
+        </is>
+      </c>
     </row>
     <row r="1120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1120" s="7"/>
-      <c r="B1120" s="7"/>
-      <c r="C1120" s="7"/>
-      <c r="D1120" s="7"/>
-      <c r="E1120" s="7"/>
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A5</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A5</t>
+        </is>
+      </c>
     </row>
     <row r="1121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1121" s="7"/>
-      <c r="B1121" s="7"/>
-      <c r="C1121" s="7"/>
-      <c r="D1121" s="7"/>
-      <c r="E1121" s="7"/>
-    </row>
-    <row r="1122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1122" s="11"/>
-      <c r="D1122" s="9"/>
-      <c r="E1122" s="10"/>
-    </row>
-    <row r="1123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1123" s="11"/>
-      <c r="D1123" s="9"/>
-      <c r="E1123" s="10"/>
-    </row>
-    <row r="1124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1124" s="11"/>
-      <c r="D1124" s="9"/>
-      <c r="E1124" s="10"/>
-    </row>
-    <row r="1125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1125" s="11"/>
-      <c r="D1125" s="9"/>
-      <c r="E1125" s="10"/>
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B8</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B6</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B2</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A6</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A7</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099C</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099D</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0994</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0994</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0988</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0988</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098F</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">098F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098A</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">098A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B9</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0999</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0999</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A8</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0990</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0990</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AC</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AD</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E7</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E8</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E9</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EA</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EB</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EC</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09EC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09ED</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EE</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09EE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EF</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E6</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098B</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">098B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A1</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A2</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099E</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099A</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099B</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099F</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">099F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A0</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B7</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AF</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09DF</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0981</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E120</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0982</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0983</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BC</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E123</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BE</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E124</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BF</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E125</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C0</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E126</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C1</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E127</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C2</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E128</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C3</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E129</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C7</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E12A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C8</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E12B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CB</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E12C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CC</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E12D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CD</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E12E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C13</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C35</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C35</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C34</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2E</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C23</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C05</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C06</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C07</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C09</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2A</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2B</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C17</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C18</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C30</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C31</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C15</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C16</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C24</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C25</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C38</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C38</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C36</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C36</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C32</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C33</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C26</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C27</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1C</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1D</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C14</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C08</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0F</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C0F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0A</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C0A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C39</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C19</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C28</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C10</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2C</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2D</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0E</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C67</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C67</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C68</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C68</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C69</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C69</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6A</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6B</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6C</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6D</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6E</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6F</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C6F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C66</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C66</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0B</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C0B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C21</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C22</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1E</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1A</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1B</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1F</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C1F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C20</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C12</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C37</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C37</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2F</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0C2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C01</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E140</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C02</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E141</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C03</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E142</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3C</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E143</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3E</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E144</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3F</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E145</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C40</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C41</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E147</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C42</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E148</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C43</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C46</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C47</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C48</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4A</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4B</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4C</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E14F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4D</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E150</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B93</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B93</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB5</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB4</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAE</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA3</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B85</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B85</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B86</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B86</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B87</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B87</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B89</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B89</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAA</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB0</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB1</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B95</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B95</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA4</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BA4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB8</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB6</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB2</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB3</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9C</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B94</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B94</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B88</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B88</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8F</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B8F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8A</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B8A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB9</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B99</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B99</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA8</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BA8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA9</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BA9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B90</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B90</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8E</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B8E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE7</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BE7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE8</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BE8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE9</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BE9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEA</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEB</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BEB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEC</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BED</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEE</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEF</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE6</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BE6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9E</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9A</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B9A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9F</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B92</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0B92</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB7</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BB7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAF</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0BAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0B82</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E160</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0B83</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBE</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBF</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E163</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC0</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E164</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC1</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E165</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC2</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E166</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC6</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC7</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC8</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E169</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCA</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E16A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCB</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E16B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCC</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E16C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCD</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E16D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E45</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E45</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E51</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E51</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E52</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E52</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E20</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E53</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E53</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E16</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E16</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E54</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E54</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E3F</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E04</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E55</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E55</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E15</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E56</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E56</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E08</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E08</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E57</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E57</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E02</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E58</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E58</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0A</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E59</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E59</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E46</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E46</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E50</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E50</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E44</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E44</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E33</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E33</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0E</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1E</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E11</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E30</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E30</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E18</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E23</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E13</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E19</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2F</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E22</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E22</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0D</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1A</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E10</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E10</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E25</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1F</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E24</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2B</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E06</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E06</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E01</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E01</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0F</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E14</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E42</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E42</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E40</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E40</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0C</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E32</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E29</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E29</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2A</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E28</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E27</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0B</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E0B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E07</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E07</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E03</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E05</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E05</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1C</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1B</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E41</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E41</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E09</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E09</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2D</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2E</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E17</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E21</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E12</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E12</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E43</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E43</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2C</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1D</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E1D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E26</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0E26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E31</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E180</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E34</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E35</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E182</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E36</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E183</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E37</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E184</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E38</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E185</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E39</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E3A</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E187</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E47</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E188</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E48</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E189</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E49</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E18A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4A</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E18B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4B</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E18C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4C</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E18D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4D</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E18E</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -31780,7 +35085,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:GC79"/>
+  <dimension ref="A1:GS79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -32145,6 +35450,38 @@
       <c r="GC1">
         <v>3084</v>
       </c>
+      <c r="GD1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">th-TH</t>
+        </is>
+      </c>
+      <c r="GG1">
+        <v>1054</v>
+      </c>
+      <c r="GH1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bn-IN</t>
+        </is>
+      </c>
+      <c r="GK1">
+        <v>1093</v>
+      </c>
+      <c r="GL1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">te-IN</t>
+        </is>
+      </c>
+      <c r="GO1">
+        <v>1098</v>
+      </c>
+      <c r="GP1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ta-IN</t>
+        </is>
+      </c>
+      <c r="GS1">
+        <v>1097</v>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -32425,6 +35762,66 @@
       <c r="FW2" t="inlineStr">
         <is>
           <t xml:space="preserve">Q</t>
+        </is>
+      </c>
+      <c r="GD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1F</t>
+        </is>
+      </c>
+      <c r="GE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E24</t>
+        </is>
+      </c>
+      <c r="GF2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1F</t>
+        </is>
+      </c>
+      <c r="GH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CB</t>
+        </is>
+      </c>
+      <c r="GI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0993</t>
+        </is>
+      </c>
+      <c r="GJ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CB</t>
+        </is>
+      </c>
+      <c r="GL2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4B</t>
+        </is>
+      </c>
+      <c r="GM2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C13</t>
+        </is>
+      </c>
+      <c r="GN2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4B</t>
+        </is>
+      </c>
+      <c r="GP2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCB</t>
+        </is>
+      </c>
+      <c r="GQ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B93</t>
+        </is>
+      </c>
+      <c r="GR2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCB</t>
         </is>
       </c>
     </row>
@@ -32695,6 +36092,51 @@
           <t xml:space="preserve">ARABIC_SHEEN</t>
         </is>
       </c>
+      <c r="GD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E34</t>
+        </is>
+      </c>
+      <c r="GE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E3A</t>
+        </is>
+      </c>
+      <c r="GF3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E34</t>
+        </is>
+      </c>
+      <c r="GL3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C35</t>
+        </is>
+      </c>
+      <c r="GM3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C34</t>
+        </is>
+      </c>
+      <c r="GN3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C35</t>
+        </is>
+      </c>
+      <c r="GP3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB5</t>
+        </is>
+      </c>
+      <c r="GQ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB4</t>
+        </is>
+      </c>
+      <c r="GR3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB5</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -32974,6 +36416,66 @@
           <t xml:space="preserve">ARABIC_YEH_BARREE</t>
         </is>
       </c>
+      <c r="GD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E41</t>
+        </is>
+      </c>
+      <c r="GE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E09</t>
+        </is>
+      </c>
+      <c r="GF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E41</t>
+        </is>
+      </c>
+      <c r="GH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AE</t>
+        </is>
+      </c>
+      <c r="GI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A3</t>
+        </is>
+      </c>
+      <c r="GJ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AE</t>
+        </is>
+      </c>
+      <c r="GL4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2E</t>
+        </is>
+      </c>
+      <c r="GM4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C23</t>
+        </is>
+      </c>
+      <c r="GN4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2E</t>
+        </is>
+      </c>
+      <c r="GP4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAE</t>
+        </is>
+      </c>
+      <c r="GQ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA3</t>
+        </is>
+      </c>
+      <c r="GR4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAE</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -33243,6 +36745,66 @@
           <t xml:space="preserve">ARABIC_REH</t>
         </is>
       </c>
+      <c r="GD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E01</t>
+        </is>
+      </c>
+      <c r="GE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0F</t>
+        </is>
+      </c>
+      <c r="GF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E01</t>
+        </is>
+      </c>
+      <c r="GH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CD</t>
+        </is>
+      </c>
+      <c r="GI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0985</t>
+        </is>
+      </c>
+      <c r="GJ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CD</t>
+        </is>
+      </c>
+      <c r="GL5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4D</t>
+        </is>
+      </c>
+      <c r="GM5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C05</t>
+        </is>
+      </c>
+      <c r="GN5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4D</t>
+        </is>
+      </c>
+      <c r="GP5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCD</t>
+        </is>
+      </c>
+      <c r="GQ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B85</t>
+        </is>
+      </c>
+      <c r="GR5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCD</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -33613,6 +37175,66 @@
       <c r="GC6" t="inlineStr">
         <is>
           <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="GD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E33</t>
+        </is>
+      </c>
+      <c r="GE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0E</t>
+        </is>
+      </c>
+      <c r="GF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E33</t>
+        </is>
+      </c>
+      <c r="GH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BE</t>
+        </is>
+      </c>
+      <c r="GI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0986</t>
+        </is>
+      </c>
+      <c r="GJ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BE</t>
+        </is>
+      </c>
+      <c r="GL6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3E</t>
+        </is>
+      </c>
+      <c r="GM6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C06</t>
+        </is>
+      </c>
+      <c r="GN6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3E</t>
+        </is>
+      </c>
+      <c r="GP6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBE</t>
+        </is>
+      </c>
+      <c r="GQ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B86</t>
+        </is>
+      </c>
+      <c r="GR6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBE</t>
         </is>
       </c>
     </row>
@@ -33883,6 +37505,66 @@
           <t xml:space="preserve">ARABIC_NOON</t>
         </is>
       </c>
+      <c r="GD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E14</t>
+        </is>
+      </c>
+      <c r="GE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E42</t>
+        </is>
+      </c>
+      <c r="GF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E14</t>
+        </is>
+      </c>
+      <c r="GH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BF</t>
+        </is>
+      </c>
+      <c r="GI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0987</t>
+        </is>
+      </c>
+      <c r="GJ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BF</t>
+        </is>
+      </c>
+      <c r="GL7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3F</t>
+        </is>
+      </c>
+      <c r="GM7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C07</t>
+        </is>
+      </c>
+      <c r="GN7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3F</t>
+        </is>
+      </c>
+      <c r="GP7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBF</t>
+        </is>
+      </c>
+      <c r="GQ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B87</t>
+        </is>
+      </c>
+      <c r="GR7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BBF</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -34154,6 +37836,66 @@
           <t xml:space="preserve">ARABIC_LAM</t>
         </is>
       </c>
+      <c r="GD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E40</t>
+        </is>
+      </c>
+      <c r="GE8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0C</t>
+        </is>
+      </c>
+      <c r="GF8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E40</t>
+        </is>
+      </c>
+      <c r="GH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C1</t>
+        </is>
+      </c>
+      <c r="GI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0989</t>
+        </is>
+      </c>
+      <c r="GJ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C1</t>
+        </is>
+      </c>
+      <c r="GL8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C41</t>
+        </is>
+      </c>
+      <c r="GM8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C09</t>
+        </is>
+      </c>
+      <c r="GN8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C41</t>
+        </is>
+      </c>
+      <c r="GP8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC1</t>
+        </is>
+      </c>
+      <c r="GQ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B89</t>
+        </is>
+      </c>
+      <c r="GR8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC1</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -34415,6 +38157,61 @@
           <t xml:space="preserve">ARABIC_HEH_GOAL</t>
         </is>
       </c>
+      <c r="GD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E49</t>
+        </is>
+      </c>
+      <c r="GE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E47</t>
+        </is>
+      </c>
+      <c r="GF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E49</t>
+        </is>
+      </c>
+      <c r="GH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AA</t>
+        </is>
+      </c>
+      <c r="GI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AB</t>
+        </is>
+      </c>
+      <c r="GJ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AA</t>
+        </is>
+      </c>
+      <c r="GL9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2A</t>
+        </is>
+      </c>
+      <c r="GM9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2B</t>
+        </is>
+      </c>
+      <c r="GN9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2A</t>
+        </is>
+      </c>
+      <c r="GP9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAA</t>
+        </is>
+      </c>
+      <c r="GR9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAA</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -34689,6 +38486,51 @@
       <c r="FH10" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="GD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E23</t>
+        </is>
+      </c>
+      <c r="GE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E13</t>
+        </is>
+      </c>
+      <c r="GF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E23</t>
+        </is>
+      </c>
+      <c r="GH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0997</t>
+        </is>
+      </c>
+      <c r="GI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0998</t>
+        </is>
+      </c>
+      <c r="GJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0997</t>
+        </is>
+      </c>
+      <c r="GL10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C17</t>
+        </is>
+      </c>
+      <c r="GM10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C18</t>
+        </is>
+      </c>
+      <c r="GN10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C17</t>
         </is>
       </c>
     </row>
@@ -34956,6 +38798,61 @@
           <t xml:space="preserve">ARABIC_ALEF</t>
         </is>
       </c>
+      <c r="GD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E48</t>
+        </is>
+      </c>
+      <c r="GE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4B</t>
+        </is>
+      </c>
+      <c r="GF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E48</t>
+        </is>
+      </c>
+      <c r="GH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B0</t>
+        </is>
+      </c>
+      <c r="GJ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B0</t>
+        </is>
+      </c>
+      <c r="GL11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C30</t>
+        </is>
+      </c>
+      <c r="GM11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C31</t>
+        </is>
+      </c>
+      <c r="GN11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C30</t>
+        </is>
+      </c>
+      <c r="GP11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB0</t>
+        </is>
+      </c>
+      <c r="GQ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB1</t>
+        </is>
+      </c>
+      <c r="GR11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB0</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -35224,6 +39121,61 @@
           <t xml:space="preserve">ARABIC_KEHEH</t>
         </is>
       </c>
+      <c r="GD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E32</t>
+        </is>
+      </c>
+      <c r="GE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E29</t>
+        </is>
+      </c>
+      <c r="GF12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E32</t>
+        </is>
+      </c>
+      <c r="GH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0995</t>
+        </is>
+      </c>
+      <c r="GI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0996</t>
+        </is>
+      </c>
+      <c r="GJ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0995</t>
+        </is>
+      </c>
+      <c r="GL12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C15</t>
+        </is>
+      </c>
+      <c r="GM12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C16</t>
+        </is>
+      </c>
+      <c r="GN12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C15</t>
+        </is>
+      </c>
+      <c r="GP12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B95</t>
+        </is>
+      </c>
+      <c r="GR12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B95</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -35494,6 +39446,61 @@
           <t xml:space="preserve">ARABIC_FARSI_YEH</t>
         </is>
       </c>
+      <c r="GD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2A</t>
+        </is>
+      </c>
+      <c r="GE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E28</t>
+        </is>
+      </c>
+      <c r="GF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2A</t>
+        </is>
+      </c>
+      <c r="GH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A4</t>
+        </is>
+      </c>
+      <c r="GI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A5</t>
+        </is>
+      </c>
+      <c r="GJ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A4</t>
+        </is>
+      </c>
+      <c r="GL13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C24</t>
+        </is>
+      </c>
+      <c r="GM13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C25</t>
+        </is>
+      </c>
+      <c r="GN13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C24</t>
+        </is>
+      </c>
+      <c r="GP13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA4</t>
+        </is>
+      </c>
+      <c r="GR13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA4</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -35783,6 +39790,66 @@
       <c r="FX14" t="inlineStr">
         <is>
           <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="GD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E17</t>
+        </is>
+      </c>
+      <c r="GE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="GF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E17</t>
+        </is>
+      </c>
+      <c r="GH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B8</t>
+        </is>
+      </c>
+      <c r="GI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B6</t>
+        </is>
+      </c>
+      <c r="GJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B8</t>
+        </is>
+      </c>
+      <c r="GL14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C38</t>
+        </is>
+      </c>
+      <c r="GM14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C36</t>
+        </is>
+      </c>
+      <c r="GN14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C38</t>
+        </is>
+      </c>
+      <c r="GP14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB8</t>
+        </is>
+      </c>
+      <c r="GQ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB6</t>
+        </is>
+      </c>
+      <c r="GR14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB8</t>
         </is>
       </c>
     </row>
@@ -36060,6 +40127,61 @@
           <t xml:space="preserve">ARABIC_GHAIN</t>
         </is>
       </c>
+      <c r="GD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E37</t>
+        </is>
+      </c>
+      <c r="GE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4C</t>
+        </is>
+      </c>
+      <c r="GF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E37</t>
+        </is>
+      </c>
+      <c r="GH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B2</t>
+        </is>
+      </c>
+      <c r="GJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B2</t>
+        </is>
+      </c>
+      <c r="GL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C32</t>
+        </is>
+      </c>
+      <c r="GM15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C33</t>
+        </is>
+      </c>
+      <c r="GN15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C32</t>
+        </is>
+      </c>
+      <c r="GP15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB2</t>
+        </is>
+      </c>
+      <c r="GQ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB3</t>
+        </is>
+      </c>
+      <c r="GR15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB2</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -36325,6 +40447,51 @@
           <t xml:space="preserve">ARABIC_JEEM</t>
         </is>
       </c>
+      <c r="GD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E19</t>
+        </is>
+      </c>
+      <c r="GE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2F</t>
+        </is>
+      </c>
+      <c r="GF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E19</t>
+        </is>
+      </c>
+      <c r="GH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A6</t>
+        </is>
+      </c>
+      <c r="GI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A7</t>
+        </is>
+      </c>
+      <c r="GJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A6</t>
+        </is>
+      </c>
+      <c r="GL16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C26</t>
+        </is>
+      </c>
+      <c r="GM16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C27</t>
+        </is>
+      </c>
+      <c r="GN16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C26</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -36590,6 +40757,61 @@
           <t xml:space="preserve">ARABIC_HAH</t>
         </is>
       </c>
+      <c r="GD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E22</t>
+        </is>
+      </c>
+      <c r="GE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0D</t>
+        </is>
+      </c>
+      <c r="GF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E22</t>
+        </is>
+      </c>
+      <c r="GH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099C</t>
+        </is>
+      </c>
+      <c r="GI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099D</t>
+        </is>
+      </c>
+      <c r="GJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099C</t>
+        </is>
+      </c>
+      <c r="GL17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1C</t>
+        </is>
+      </c>
+      <c r="GM17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1D</t>
+        </is>
+      </c>
+      <c r="GN17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1C</t>
+        </is>
+      </c>
+      <c r="GP17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9C</t>
+        </is>
+      </c>
+      <c r="GR17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9C</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -36892,6 +41114,66 @@
       <c r="FW18" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="GD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E46</t>
+        </is>
+      </c>
+      <c r="GE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E50</t>
+        </is>
+      </c>
+      <c r="GF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E46</t>
+        </is>
+      </c>
+      <c r="GH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CC</t>
+        </is>
+      </c>
+      <c r="GI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0994</t>
+        </is>
+      </c>
+      <c r="GJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09CC</t>
+        </is>
+      </c>
+      <c r="GL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4C</t>
+        </is>
+      </c>
+      <c r="GM18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C14</t>
+        </is>
+      </c>
+      <c r="GN18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4C</t>
+        </is>
+      </c>
+      <c r="GP18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCC</t>
+        </is>
+      </c>
+      <c r="GQ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B94</t>
+        </is>
+      </c>
+      <c r="GR18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCC</t>
         </is>
       </c>
     </row>
@@ -37163,6 +41445,66 @@
           <t xml:space="preserve">ARABIC_DAL</t>
         </is>
       </c>
+      <c r="GD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1E</t>
+        </is>
+      </c>
+      <c r="GE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E11</t>
+        </is>
+      </c>
+      <c r="GF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1E</t>
+        </is>
+      </c>
+      <c r="GH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C0</t>
+        </is>
+      </c>
+      <c r="GI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0988</t>
+        </is>
+      </c>
+      <c r="GJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C0</t>
+        </is>
+      </c>
+      <c r="GL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C40</t>
+        </is>
+      </c>
+      <c r="GM19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C08</t>
+        </is>
+      </c>
+      <c r="GN19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C40</t>
+        </is>
+      </c>
+      <c r="GP19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC0</t>
+        </is>
+      </c>
+      <c r="GQ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B88</t>
+        </is>
+      </c>
+      <c r="GR19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC0</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -37438,6 +41780,66 @@
       <c r="FH20" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="GD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2B</t>
+        </is>
+      </c>
+      <c r="GE20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E06</t>
+        </is>
+      </c>
+      <c r="GF20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2B</t>
+        </is>
+      </c>
+      <c r="GH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C7</t>
+        </is>
+      </c>
+      <c r="GI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098F</t>
+        </is>
+      </c>
+      <c r="GJ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C7</t>
+        </is>
+      </c>
+      <c r="GL20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C47</t>
+        </is>
+      </c>
+      <c r="GM20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0F</t>
+        </is>
+      </c>
+      <c r="GN20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C47</t>
+        </is>
+      </c>
+      <c r="GP20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC7</t>
+        </is>
+      </c>
+      <c r="GQ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8F</t>
+        </is>
+      </c>
+      <c r="GR20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC7</t>
         </is>
       </c>
     </row>
@@ -37699,6 +42101,66 @@
           <t xml:space="preserve">ARABIC_TTEH</t>
         </is>
       </c>
+      <c r="GD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E30</t>
+        </is>
+      </c>
+      <c r="GE21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E18</t>
+        </is>
+      </c>
+      <c r="GF21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E30</t>
+        </is>
+      </c>
+      <c r="GH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C2</t>
+        </is>
+      </c>
+      <c r="GI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098A</t>
+        </is>
+      </c>
+      <c r="GJ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C2</t>
+        </is>
+      </c>
+      <c r="GL21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C42</t>
+        </is>
+      </c>
+      <c r="GM21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0A</t>
+        </is>
+      </c>
+      <c r="GN21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C42</t>
+        </is>
+      </c>
+      <c r="GP21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC2</t>
+        </is>
+      </c>
+      <c r="GQ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8A</t>
+        </is>
+      </c>
+      <c r="GR21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC2</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -37973,6 +42435,66 @@
           <t xml:space="preserve">ARABIC_TEH</t>
         </is>
       </c>
+      <c r="GD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E35</t>
+        </is>
+      </c>
+      <c r="GE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4A</t>
+        </is>
+      </c>
+      <c r="GF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E35</t>
+        </is>
+      </c>
+      <c r="GH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B9</t>
+        </is>
+      </c>
+      <c r="GI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0999</t>
+        </is>
+      </c>
+      <c r="GJ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B9</t>
+        </is>
+      </c>
+      <c r="GL22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C39</t>
+        </is>
+      </c>
+      <c r="GM22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C19</t>
+        </is>
+      </c>
+      <c r="GN22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C39</t>
+        </is>
+      </c>
+      <c r="GP22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB9</t>
+        </is>
+      </c>
+      <c r="GQ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B99</t>
+        </is>
+      </c>
+      <c r="GR22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB9</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -38238,6 +42760,56 @@
           <t xml:space="preserve">ARABIC_SEEN</t>
         </is>
       </c>
+      <c r="GD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2D</t>
+        </is>
+      </c>
+      <c r="GE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2E</t>
+        </is>
+      </c>
+      <c r="GF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2D</t>
+        </is>
+      </c>
+      <c r="GH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A8</t>
+        </is>
+      </c>
+      <c r="GJ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A8</t>
+        </is>
+      </c>
+      <c r="GL23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C28</t>
+        </is>
+      </c>
+      <c r="GN23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C28</t>
+        </is>
+      </c>
+      <c r="GP23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA8</t>
+        </is>
+      </c>
+      <c r="GQ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA9</t>
+        </is>
+      </c>
+      <c r="GR23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BA8</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -38528,6 +43100,66 @@
       <c r="FW24" t="inlineStr">
         <is>
           <t xml:space="preserve">Z</t>
+        </is>
+      </c>
+      <c r="GD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E44</t>
+        </is>
+      </c>
+      <c r="GE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="GF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E44</t>
+        </is>
+      </c>
+      <c r="GH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C8</t>
+        </is>
+      </c>
+      <c r="GI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_0990</t>
+        </is>
+      </c>
+      <c r="GJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C8</t>
+        </is>
+      </c>
+      <c r="GL24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C48</t>
+        </is>
+      </c>
+      <c r="GM24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C10</t>
+        </is>
+      </c>
+      <c r="GN24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C48</t>
+        </is>
+      </c>
+      <c r="GP24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC8</t>
+        </is>
+      </c>
+      <c r="GQ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B90</t>
+        </is>
+      </c>
+      <c r="GR24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC8</t>
         </is>
       </c>
     </row>
@@ -38790,6 +43422,61 @@
           <t xml:space="preserve">ARABIC_FEH</t>
         </is>
       </c>
+      <c r="GD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1B</t>
+        </is>
+      </c>
+      <c r="GE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="GF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1B</t>
+        </is>
+      </c>
+      <c r="GH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0982</t>
+        </is>
+      </c>
+      <c r="GI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0981</t>
+        </is>
+      </c>
+      <c r="GJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0982</t>
+        </is>
+      </c>
+      <c r="GL25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C02</t>
+        </is>
+      </c>
+      <c r="GM25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C01</t>
+        </is>
+      </c>
+      <c r="GN25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C02</t>
+        </is>
+      </c>
+      <c r="GP25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0B82</t>
+        </is>
+      </c>
+      <c r="GR25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0B82</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -39099,6 +43786,51 @@
           <t xml:space="preserve">Z</t>
         </is>
       </c>
+      <c r="GD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E31</t>
+        </is>
+      </c>
+      <c r="GE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E4D</t>
+        </is>
+      </c>
+      <c r="GF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E31</t>
+        </is>
+      </c>
+      <c r="GH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AC</t>
+        </is>
+      </c>
+      <c r="GI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AD</t>
+        </is>
+      </c>
+      <c r="GJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AC</t>
+        </is>
+      </c>
+      <c r="GL26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2C</t>
+        </is>
+      </c>
+      <c r="GM26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2D</t>
+        </is>
+      </c>
+      <c r="GN26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2C</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -39427,6 +44159,51 @@
           <t xml:space="preserve">W</t>
         </is>
       </c>
+      <c r="GD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1C</t>
+        </is>
+      </c>
+      <c r="GE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="GF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1C</t>
+        </is>
+      </c>
+      <c r="GL27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C46</t>
+        </is>
+      </c>
+      <c r="GM27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0E</t>
+        </is>
+      </c>
+      <c r="GN27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C46</t>
+        </is>
+      </c>
+      <c r="GP27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC6</t>
+        </is>
+      </c>
+      <c r="GQ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B8E</t>
+        </is>
+      </c>
+      <c r="GR27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BC6</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -39930,6 +44707,51 @@
       <c r="GC28" t="inlineStr">
         <is>
           <t xml:space="preserve">PLUS_MINUS</t>
+        </is>
+      </c>
+      <c r="GD28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E45</t>
+        </is>
+      </c>
+      <c r="GE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="GF28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E45</t>
+        </is>
+      </c>
+      <c r="GH28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E7</t>
+        </is>
+      </c>
+      <c r="GJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E7</t>
+        </is>
+      </c>
+      <c r="GL28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C67</t>
+        </is>
+      </c>
+      <c r="GN28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C67</t>
+        </is>
+      </c>
+      <c r="GP28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE7</t>
+        </is>
+      </c>
+      <c r="GR28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE7</t>
         </is>
       </c>
     </row>
@@ -40458,6 +45280,51 @@
           <t xml:space="preserve">@</t>
         </is>
       </c>
+      <c r="GD29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="GE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E51</t>
+        </is>
+      </c>
+      <c r="GF29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="GH29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E8</t>
+        </is>
+      </c>
+      <c r="GJ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E8</t>
+        </is>
+      </c>
+      <c r="GL29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C68</t>
+        </is>
+      </c>
+      <c r="GN29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C68</t>
+        </is>
+      </c>
+      <c r="GP29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE8</t>
+        </is>
+      </c>
+      <c r="GR29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE8</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -41002,6 +45869,66 @@
           <t xml:space="preserve">POUND_SIGN</t>
         </is>
       </c>
+      <c r="GD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E52</t>
+        </is>
+      </c>
+      <c r="GF30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GH30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E9</t>
+        </is>
+      </c>
+      <c r="GI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="GJ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E9</t>
+        </is>
+      </c>
+      <c r="GL30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C69</t>
+        </is>
+      </c>
+      <c r="GM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="GN30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C69</t>
+        </is>
+      </c>
+      <c r="GP30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE9</t>
+        </is>
+      </c>
+      <c r="GQ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="GR30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE9</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -41536,6 +46463,66 @@
           <t xml:space="preserve">CENT_SIGN</t>
         </is>
       </c>
+      <c r="GD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E20</t>
+        </is>
+      </c>
+      <c r="GE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E53</t>
+        </is>
+      </c>
+      <c r="GF31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E20</t>
+        </is>
+      </c>
+      <c r="GH31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EA</t>
+        </is>
+      </c>
+      <c r="GI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="GJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EA</t>
+        </is>
+      </c>
+      <c r="GL31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6A</t>
+        </is>
+      </c>
+      <c r="GM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="GN31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6A</t>
+        </is>
+      </c>
+      <c r="GP31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEA</t>
+        </is>
+      </c>
+      <c r="GQ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="GR31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEA</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -42022,6 +47009,66 @@
           <t xml:space="preserve">CURRENCY_SIGN</t>
         </is>
       </c>
+      <c r="GD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E16</t>
+        </is>
+      </c>
+      <c r="GE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E54</t>
+        </is>
+      </c>
+      <c r="GF32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E16</t>
+        </is>
+      </c>
+      <c r="GH32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EB</t>
+        </is>
+      </c>
+      <c r="GI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="GJ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EB</t>
+        </is>
+      </c>
+      <c r="GL32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6B</t>
+        </is>
+      </c>
+      <c r="GM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="GN32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6B</t>
+        </is>
+      </c>
+      <c r="GP32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEB</t>
+        </is>
+      </c>
+      <c r="GQ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="GR32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEB</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -42538,6 +47585,66 @@
           <t xml:space="preserve">NOT_SIGN</t>
         </is>
       </c>
+      <c r="GD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E38</t>
+        </is>
+      </c>
+      <c r="GE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E39</t>
+        </is>
+      </c>
+      <c r="GF33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E38</t>
+        </is>
+      </c>
+      <c r="GH33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EC</t>
+        </is>
+      </c>
+      <c r="GI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GJ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EC</t>
+        </is>
+      </c>
+      <c r="GL33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6C</t>
+        </is>
+      </c>
+      <c r="GM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GN33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6C</t>
+        </is>
+      </c>
+      <c r="GP33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEC</t>
+        </is>
+      </c>
+      <c r="GQ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="GR33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEC</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -43041,6 +48148,66 @@
       <c r="GC34" t="inlineStr">
         <is>
           <t xml:space="preserve">BROKEN_BAR</t>
+        </is>
+      </c>
+      <c r="GD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E36</t>
+        </is>
+      </c>
+      <c r="GE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E3F</t>
+        </is>
+      </c>
+      <c r="GF34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_DC_0E36</t>
+        </is>
+      </c>
+      <c r="GH34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09ED</t>
+        </is>
+      </c>
+      <c r="GI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="GJ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09ED</t>
+        </is>
+      </c>
+      <c r="GL34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6D</t>
+        </is>
+      </c>
+      <c r="GM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="GN34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6D</t>
+        </is>
+      </c>
+      <c r="GP34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BED</t>
+        </is>
+      </c>
+      <c r="GQ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="GR34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BED</t>
         </is>
       </c>
     </row>
@@ -43548,6 +48715,66 @@
           <t xml:space="preserve">SUPER_SCRIPT_2</t>
         </is>
       </c>
+      <c r="GD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E04</t>
+        </is>
+      </c>
+      <c r="GE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E55</t>
+        </is>
+      </c>
+      <c r="GF35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E04</t>
+        </is>
+      </c>
+      <c r="GH35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EE</t>
+        </is>
+      </c>
+      <c r="GI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="GJ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EE</t>
+        </is>
+      </c>
+      <c r="GL35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6E</t>
+        </is>
+      </c>
+      <c r="GM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="GN35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6E</t>
+        </is>
+      </c>
+      <c r="GP35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEE</t>
+        </is>
+      </c>
+      <c r="GQ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="GR35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEE</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -44051,6 +49278,66 @@
           <t xml:space="preserve">SUPER_SCRIPT_3</t>
         </is>
       </c>
+      <c r="GD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E15</t>
+        </is>
+      </c>
+      <c r="GE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E56</t>
+        </is>
+      </c>
+      <c r="GF36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E15</t>
+        </is>
+      </c>
+      <c r="GH36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EF</t>
+        </is>
+      </c>
+      <c r="GI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="GJ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09EF</t>
+        </is>
+      </c>
+      <c r="GL36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6F</t>
+        </is>
+      </c>
+      <c r="GM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="GN36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C6F</t>
+        </is>
+      </c>
+      <c r="GP36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEF</t>
+        </is>
+      </c>
+      <c r="GQ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="GR36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BEF</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -44592,6 +49879,66 @@
       <c r="GC37" t="inlineStr">
         <is>
           <t xml:space="preserve">QUATER_SIGN</t>
+        </is>
+      </c>
+      <c r="GD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E08</t>
+        </is>
+      </c>
+      <c r="GE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E57</t>
+        </is>
+      </c>
+      <c r="GF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E08</t>
+        </is>
+      </c>
+      <c r="GH37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E6</t>
+        </is>
+      </c>
+      <c r="GI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="GJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09E6</t>
+        </is>
+      </c>
+      <c r="GL37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C66</t>
+        </is>
+      </c>
+      <c r="GM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="GN37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C66</t>
+        </is>
+      </c>
+      <c r="GP37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE6</t>
+        </is>
+      </c>
+      <c r="GQ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="GR37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BE6</t>
         </is>
       </c>
     </row>
@@ -45684,6 +51031,66 @@
           <t xml:space="preserve">HALF_SIGN</t>
         </is>
       </c>
+      <c r="GD43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E02</t>
+        </is>
+      </c>
+      <c r="GE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E58</t>
+        </is>
+      </c>
+      <c r="GF43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E02</t>
+        </is>
+      </c>
+      <c r="GH43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GI43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_0983</t>
+        </is>
+      </c>
+      <c r="GJ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GL43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GM43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C03</t>
+        </is>
+      </c>
+      <c r="GN43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GP43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="GQ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0B83</t>
+        </is>
+      </c>
+      <c r="GR43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -46193,6 +51600,51 @@
           <t xml:space="preserve">THREE_QUATER_SIGN</t>
         </is>
       </c>
+      <c r="GD44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0A</t>
+        </is>
+      </c>
+      <c r="GE44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E59</t>
+        </is>
+      </c>
+      <c r="GF44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0A</t>
+        </is>
+      </c>
+      <c r="GH44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C3</t>
+        </is>
+      </c>
+      <c r="GI44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_098B</t>
+        </is>
+      </c>
+      <c r="GJ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09C3</t>
+        </is>
+      </c>
+      <c r="GL44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C43</t>
+        </is>
+      </c>
+      <c r="GM44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C0B</t>
+        </is>
+      </c>
+      <c r="GN44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C43</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -46689,6 +52141,51 @@
           <t xml:space="preserve">[</t>
         </is>
       </c>
+      <c r="GD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1A</t>
+        </is>
+      </c>
+      <c r="GE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E10</t>
+        </is>
+      </c>
+      <c r="GF45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1A</t>
+        </is>
+      </c>
+      <c r="GH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A1</t>
+        </is>
+      </c>
+      <c r="GI45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A2</t>
+        </is>
+      </c>
+      <c r="GJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A1</t>
+        </is>
+      </c>
+      <c r="GL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C21</t>
+        </is>
+      </c>
+      <c r="GM45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C22</t>
+        </is>
+      </c>
+      <c r="GN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C21</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -47196,6 +52693,56 @@
           <t xml:space="preserve">]</t>
         </is>
       </c>
+      <c r="GD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E25</t>
+        </is>
+      </c>
+      <c r="GE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="GF46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E25</t>
+        </is>
+      </c>
+      <c r="GH46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BC</t>
+        </is>
+      </c>
+      <c r="GI46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099E</t>
+        </is>
+      </c>
+      <c r="GJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENG_DC_09BC</t>
+        </is>
+      </c>
+      <c r="GL46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3C</t>
+        </is>
+      </c>
+      <c r="GM46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1E</t>
+        </is>
+      </c>
+      <c r="GN46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C3C</t>
+        </is>
+      </c>
+      <c r="GQ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9E</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -47646,6 +53193,21 @@
       <c r="GC47" t="inlineStr">
         <is>
           <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="GD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E03</t>
+        </is>
+      </c>
+      <c r="GE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E05</t>
+        </is>
+      </c>
+      <c r="GF47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E03</t>
         </is>
       </c>
     </row>
@@ -47938,6 +53500,21 @@
           <t xml:space="preserve">}</t>
         </is>
       </c>
+      <c r="GD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E03</t>
+        </is>
+      </c>
+      <c r="GE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E05</t>
+        </is>
+      </c>
+      <c r="GF48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E03</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -48396,6 +53973,61 @@
       <c r="GC49" t="inlineStr">
         <is>
           <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="GD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E27</t>
+        </is>
+      </c>
+      <c r="GE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E0B</t>
+        </is>
+      </c>
+      <c r="GF49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E27</t>
+        </is>
+      </c>
+      <c r="GH49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099A</t>
+        </is>
+      </c>
+      <c r="GI49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099B</t>
+        </is>
+      </c>
+      <c r="GJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099A</t>
+        </is>
+      </c>
+      <c r="GL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1A</t>
+        </is>
+      </c>
+      <c r="GM49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1B</t>
+        </is>
+      </c>
+      <c r="GN49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1A</t>
+        </is>
+      </c>
+      <c r="GP49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9A</t>
+        </is>
+      </c>
+      <c r="GR49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9A</t>
         </is>
       </c>
     </row>
@@ -48902,6 +54534,61 @@
           <t xml:space="preserve">{</t>
         </is>
       </c>
+      <c r="GD50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E07</t>
+        </is>
+      </c>
+      <c r="GE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GF50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E07</t>
+        </is>
+      </c>
+      <c r="GH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099F</t>
+        </is>
+      </c>
+      <c r="GI50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09A0</t>
+        </is>
+      </c>
+      <c r="GJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_099F</t>
+        </is>
+      </c>
+      <c r="GL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1F</t>
+        </is>
+      </c>
+      <c r="GM50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C20</t>
+        </is>
+      </c>
+      <c r="GN50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C1F</t>
+        </is>
+      </c>
+      <c r="GP50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9F</t>
+        </is>
+      </c>
+      <c r="GR50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B9F</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -49367,6 +55054,51 @@
       <c r="GC51" t="inlineStr">
         <is>
           <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="GD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="GE51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="GF51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="GL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4A</t>
+        </is>
+      </c>
+      <c r="GM51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C12</t>
+        </is>
+      </c>
+      <c r="GN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELU_DC_0C4A</t>
+        </is>
+      </c>
+      <c r="GP51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCA</t>
+        </is>
+      </c>
+      <c r="GQ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0B92</t>
+        </is>
+      </c>
+      <c r="GR51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAML_DC_0BCA</t>
         </is>
       </c>
     </row>
@@ -49734,6 +55466,66 @@
           <t xml:space="preserve">;</t>
         </is>
       </c>
+      <c r="GD52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E21</t>
+        </is>
+      </c>
+      <c r="GE52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E12</t>
+        </is>
+      </c>
+      <c r="GF52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E21</t>
+        </is>
+      </c>
+      <c r="GH52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="GI52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09B7</t>
+        </is>
+      </c>
+      <c r="GJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="GL52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="GM52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C37</t>
+        </is>
+      </c>
+      <c r="GN52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="GP52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="GQ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BB7</t>
+        </is>
+      </c>
+      <c r="GR52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -50093,6 +55885,51 @@
           <t xml:space="preserve">:</t>
         </is>
       </c>
+      <c r="GD53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E43</t>
+        </is>
+      </c>
+      <c r="GE53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E2C</t>
+        </is>
+      </c>
+      <c r="GF53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E43</t>
+        </is>
+      </c>
+      <c r="GH53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GL53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GN53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GP53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="GR53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -50456,6 +56293,56 @@
       <c r="FX54" t="inlineStr">
         <is>
           <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="GD54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1D</t>
+        </is>
+      </c>
+      <c r="GE54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E26</t>
+        </is>
+      </c>
+      <c r="GF54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THAI_0E1D</t>
+        </is>
+      </c>
+      <c r="GH54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AF</t>
+        </is>
+      </c>
+      <c r="GI54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09DF</t>
+        </is>
+      </c>
+      <c r="GJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENGALI_09AF</t>
+        </is>
+      </c>
+      <c r="GL54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2F</t>
+        </is>
+      </c>
+      <c r="GN54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TELUGU_0C2F</t>
+        </is>
+      </c>
+      <c r="GP54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAF</t>
+        </is>
+      </c>
+      <c r="GR54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAMIL_0BAF</t>
         </is>
       </c>
     </row>
@@ -51236,6 +57123,30 @@
       <c r="GC56">
         <v>50</v>
       </c>
+      <c r="GE56">
+        <v>40</v>
+      </c>
+      <c r="GG56">
+        <v>52</v>
+      </c>
+      <c r="GI56">
+        <v>40</v>
+      </c>
+      <c r="GK56">
+        <v>52</v>
+      </c>
+      <c r="GM56">
+        <v>40</v>
+      </c>
+      <c r="GO56">
+        <v>52</v>
+      </c>
+      <c r="GQ56">
+        <v>40</v>
+      </c>
+      <c r="GS56">
+        <v>52</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -51594,6 +57505,30 @@
       <c r="GC57">
         <v>13</v>
       </c>
+      <c r="GE57">
+        <v>0</v>
+      </c>
+      <c r="GG57">
+        <v>13</v>
+      </c>
+      <c r="GI57">
+        <v>0</v>
+      </c>
+      <c r="GK57">
+        <v>13</v>
+      </c>
+      <c r="GM57">
+        <v>0</v>
+      </c>
+      <c r="GO57">
+        <v>13</v>
+      </c>
+      <c r="GQ57">
+        <v>0</v>
+      </c>
+      <c r="GS57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -51921,6 +57856,30 @@
       <c r="GC58">
         <v>50</v>
       </c>
+      <c r="GE58">
+        <v>28</v>
+      </c>
+      <c r="GG58">
+        <v>52</v>
+      </c>
+      <c r="GI58">
+        <v>28</v>
+      </c>
+      <c r="GK58">
+        <v>52</v>
+      </c>
+      <c r="GM58">
+        <v>28</v>
+      </c>
+      <c r="GO58">
+        <v>52</v>
+      </c>
+      <c r="GQ58">
+        <v>28</v>
+      </c>
+      <c r="GS58">
+        <v>52</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -52248,6 +58207,30 @@
       <c r="GC59">
         <v>13</v>
       </c>
+      <c r="GE59">
+        <v>0</v>
+      </c>
+      <c r="GG59">
+        <v>13</v>
+      </c>
+      <c r="GI59">
+        <v>0</v>
+      </c>
+      <c r="GK59">
+        <v>13</v>
+      </c>
+      <c r="GM59">
+        <v>0</v>
+      </c>
+      <c r="GO59">
+        <v>13</v>
+      </c>
+      <c r="GQ59">
+        <v>0</v>
+      </c>
+      <c r="GS59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -52575,6 +58558,30 @@
       <c r="GC60">
         <v>50</v>
       </c>
+      <c r="GE60">
+        <v>40</v>
+      </c>
+      <c r="GG60">
+        <v>52</v>
+      </c>
+      <c r="GI60">
+        <v>40</v>
+      </c>
+      <c r="GK60">
+        <v>52</v>
+      </c>
+      <c r="GM60">
+        <v>40</v>
+      </c>
+      <c r="GO60">
+        <v>52</v>
+      </c>
+      <c r="GQ60">
+        <v>40</v>
+      </c>
+      <c r="GS60">
+        <v>52</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -52900,6 +58907,30 @@
         <v>0</v>
       </c>
       <c r="GC61">
+        <v>13</v>
+      </c>
+      <c r="GE61">
+        <v>0</v>
+      </c>
+      <c r="GG61">
+        <v>13</v>
+      </c>
+      <c r="GI61">
+        <v>0</v>
+      </c>
+      <c r="GK61">
+        <v>13</v>
+      </c>
+      <c r="GM61">
+        <v>0</v>
+      </c>
+      <c r="GO61">
+        <v>13</v>
+      </c>
+      <c r="GQ61">
+        <v>0</v>
+      </c>
+      <c r="GS61">
         <v>13</v>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -6068,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1391"/>
+  <dimension ref="A1:I1552"/>
   <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.25"/>
@@ -35063,6 +35063,1938 @@
       <c r="B1391" t="inlineStr">
         <is>
           <t xml:space="preserve">E18E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E5</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EC</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10EC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10ED</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D4</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E0</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E6</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E2</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D7</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E7</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E3</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D8</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DD</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DE</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D0</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E1</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E8</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D3</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E4</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D2</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10F0</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10F0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EF</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10EF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DF</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D9</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DA</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D6</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EB</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EE</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10EE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EA</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10EA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E9</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D5</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D1</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DC</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DB</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055D</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055C</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0586</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0586</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0556</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0556</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0571</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0541</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0541</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_058A</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">058A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2014</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0589</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0589</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2026</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055E</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2024</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0587</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0587</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055B</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055A</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">055A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0585</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0585</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0555</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0555</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0567</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0567</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0537</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0537</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0572</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0572</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0542</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0542</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0573</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0573</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0543</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0543</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0583</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0583</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0553</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0553</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0562</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0562</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0532</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0532</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057D</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054D</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0574</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0574</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0544</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0544</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0578</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0578</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0548</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0548</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0582</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0582</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0552</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0552</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056F</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053F</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0568</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0568</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0538</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0538</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0569</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0569</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0539</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0539</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056E</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053E</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0581</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0551</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057B</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054B</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057E</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054E</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0563</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0563</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0533</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0533</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0565</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0565</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0535</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0535</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0561</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0561</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0531</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0531</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0576</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0576</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0546</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0546</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056B</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053B</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057F</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054F</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0570</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0570</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0540</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0540</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057A</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054A</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0580</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0580</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0550</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0550</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056A</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053A</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0564</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0564</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0534</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0534</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0579</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0579</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0549</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0549</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0575</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0575</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0545</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0545</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0566</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0566</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0536</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0536</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056C</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053C</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0584</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0584</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0554</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0554</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056D</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">056D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053D</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">053D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0577</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0577</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0547</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0547</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057C</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">057C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054C</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3105</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3105</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3106</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3106</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3107</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3107</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3108</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3108</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3109</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3109</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310A</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310B</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310C</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310D</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310E</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310F</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">310F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3110</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3110</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3111</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3112</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3113</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3113</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3114</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3114</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3115</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3115</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3116</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3116</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3117</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3118</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3118</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3119</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3119</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3127</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3127</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3128</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3128</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3129</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3129</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311A</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311B</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311C</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311D</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311E</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311F</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3120</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3120</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3121</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3122</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3123</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3123</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3124</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3124</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3125</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3125</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3126</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3126</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02C7</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CB</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CA</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02D9</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02D9</t>
         </is>
       </c>
     </row>
@@ -35085,7 +37017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:GS79"/>
+  <dimension ref="A1:HI79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -35482,6 +37414,26 @@
       <c r="GS1">
         <v>1097</v>
       </c>
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zh-TW</t>
+        </is>
+      </c>
+      <c r="GX1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ka-GE</t>
+        </is>
+      </c>
+      <c r="HB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hy-AM</t>
+        </is>
+      </c>
+      <c r="HF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id-ID</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -35822,6 +37774,36 @@
       <c r="GR2" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BCB</t>
+        </is>
+      </c>
+      <c r="GT2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3107</t>
+        </is>
+      </c>
+      <c r="GV2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3107</t>
+        </is>
+      </c>
+      <c r="GX2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D0</t>
+        </is>
+      </c>
+      <c r="GZ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D0</t>
+        </is>
+      </c>
+      <c r="HB2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057B</t>
+        </is>
+      </c>
+      <c r="HC2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054B</t>
         </is>
       </c>
     </row>
@@ -36137,6 +38119,36 @@
           <t xml:space="preserve">TAMIL_0BB5</t>
         </is>
       </c>
+      <c r="GT3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3116</t>
+        </is>
+      </c>
+      <c r="GV3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3116</t>
+        </is>
+      </c>
+      <c r="GX3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D1</t>
+        </is>
+      </c>
+      <c r="GZ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D1</t>
+        </is>
+      </c>
+      <c r="HB3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0566</t>
+        </is>
+      </c>
+      <c r="HC3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0536</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -36476,6 +38488,41 @@
           <t xml:space="preserve">TAMIL_0BAE</t>
         </is>
       </c>
+      <c r="GT4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310F</t>
+        </is>
+      </c>
+      <c r="GV4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310F</t>
+        </is>
+      </c>
+      <c r="GX4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EA</t>
+        </is>
+      </c>
+      <c r="GY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E9</t>
+        </is>
+      </c>
+      <c r="GZ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EA</t>
+        </is>
+      </c>
+      <c r="HB4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0579</t>
+        </is>
+      </c>
+      <c r="HC4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0549</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -36805,6 +38852,36 @@
           <t xml:space="preserve">TAML_DC_0BCD</t>
         </is>
       </c>
+      <c r="GT5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310E</t>
+        </is>
+      </c>
+      <c r="GV5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310E</t>
+        </is>
+      </c>
+      <c r="GX5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D3</t>
+        </is>
+      </c>
+      <c r="GZ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D3</t>
+        </is>
+      </c>
+      <c r="HB5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0563</t>
+        </is>
+      </c>
+      <c r="HC5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0533</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -37235,6 +39312,36 @@
       <c r="GR6" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BBE</t>
+        </is>
+      </c>
+      <c r="GT6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310D</t>
+        </is>
+      </c>
+      <c r="GV6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310D</t>
+        </is>
+      </c>
+      <c r="GX6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D4</t>
+        </is>
+      </c>
+      <c r="GZ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D4</t>
+        </is>
+      </c>
+      <c r="HB6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0562</t>
+        </is>
+      </c>
+      <c r="HC6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0532</t>
         </is>
       </c>
     </row>
@@ -37565,6 +39672,36 @@
           <t xml:space="preserve">TAML_DC_0BBF</t>
         </is>
       </c>
+      <c r="GT7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3111</t>
+        </is>
+      </c>
+      <c r="GV7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3111</t>
+        </is>
+      </c>
+      <c r="GX7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E4</t>
+        </is>
+      </c>
+      <c r="GZ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E4</t>
+        </is>
+      </c>
+      <c r="HB7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0565</t>
+        </is>
+      </c>
+      <c r="HC7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0535</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -37896,6 +40033,36 @@
           <t xml:space="preserve">TAML_DC_0BC1</t>
         </is>
       </c>
+      <c r="GT8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3115</t>
+        </is>
+      </c>
+      <c r="GV8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3115</t>
+        </is>
+      </c>
+      <c r="GX8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D2</t>
+        </is>
+      </c>
+      <c r="GZ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D2</t>
+        </is>
+      </c>
+      <c r="HB8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0561</t>
+        </is>
+      </c>
+      <c r="HC8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0531</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -38212,6 +40379,36 @@
           <t xml:space="preserve">TAMIL_0BAA</t>
         </is>
       </c>
+      <c r="GT9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3118</t>
+        </is>
+      </c>
+      <c r="GV9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3118</t>
+        </is>
+      </c>
+      <c r="GX9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10F0</t>
+        </is>
+      </c>
+      <c r="GZ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10F0</t>
+        </is>
+      </c>
+      <c r="HB9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0576</t>
+        </is>
+      </c>
+      <c r="HC9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0546</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -38531,6 +40728,36 @@
       <c r="GN10" t="inlineStr">
         <is>
           <t xml:space="preserve">TELUGU_0C17</t>
+        </is>
+      </c>
+      <c r="GT10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311B</t>
+        </is>
+      </c>
+      <c r="GV10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311B</t>
+        </is>
+      </c>
+      <c r="GX10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D8</t>
+        </is>
+      </c>
+      <c r="GZ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D8</t>
+        </is>
+      </c>
+      <c r="HB10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056F</t>
+        </is>
+      </c>
+      <c r="HC10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053F</t>
         </is>
       </c>
     </row>
@@ -38853,6 +41080,41 @@
           <t xml:space="preserve">TAMIL_0BB0</t>
         </is>
       </c>
+      <c r="GT11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3128</t>
+        </is>
+      </c>
+      <c r="GV11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3128</t>
+        </is>
+      </c>
+      <c r="GX11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EF</t>
+        </is>
+      </c>
+      <c r="GY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DF</t>
+        </is>
+      </c>
+      <c r="GZ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EF</t>
+        </is>
+      </c>
+      <c r="HB11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056B</t>
+        </is>
+      </c>
+      <c r="HC11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053B</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -39176,6 +41438,36 @@
           <t xml:space="preserve">TAMIL_0B95</t>
         </is>
       </c>
+      <c r="GT12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311C</t>
+        </is>
+      </c>
+      <c r="GV12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311C</t>
+        </is>
+      </c>
+      <c r="GX12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D9</t>
+        </is>
+      </c>
+      <c r="GZ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D9</t>
+        </is>
+      </c>
+      <c r="HB12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057F</t>
+        </is>
+      </c>
+      <c r="HC12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054F</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -39501,6 +41793,36 @@
           <t xml:space="preserve">TAMIL_0BA4</t>
         </is>
       </c>
+      <c r="GT13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3120</t>
+        </is>
+      </c>
+      <c r="GV13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3120</t>
+        </is>
+      </c>
+      <c r="GX13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DA</t>
+        </is>
+      </c>
+      <c r="GZ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DA</t>
+        </is>
+      </c>
+      <c r="HB13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0570</t>
+        </is>
+      </c>
+      <c r="HC13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0540</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -39850,6 +42172,36 @@
       <c r="GR14" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0BB8</t>
+        </is>
+      </c>
+      <c r="GT14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3129</t>
+        </is>
+      </c>
+      <c r="GV14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3129</t>
+        </is>
+      </c>
+      <c r="GX14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DB</t>
+        </is>
+      </c>
+      <c r="GZ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DB</t>
+        </is>
+      </c>
+      <c r="HB14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0584</t>
+        </is>
+      </c>
+      <c r="HC14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0554</t>
         </is>
       </c>
     </row>
@@ -40182,6 +42534,36 @@
           <t xml:space="preserve">TAMIL_0BB2</t>
         </is>
       </c>
+      <c r="GT15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3119</t>
+        </is>
+      </c>
+      <c r="GV15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3119</t>
+        </is>
+      </c>
+      <c r="GX15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DC</t>
+        </is>
+      </c>
+      <c r="GZ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DC</t>
+        </is>
+      </c>
+      <c r="HB15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056C</t>
+        </is>
+      </c>
+      <c r="HC15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053C</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -40492,6 +42874,36 @@
           <t xml:space="preserve">TELUGU_0C26</t>
         </is>
       </c>
+      <c r="GT16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311F</t>
+        </is>
+      </c>
+      <c r="GV16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311F</t>
+        </is>
+      </c>
+      <c r="GX16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DD</t>
+        </is>
+      </c>
+      <c r="GZ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DD</t>
+        </is>
+      </c>
+      <c r="HB16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0568</t>
+        </is>
+      </c>
+      <c r="HC16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0538</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -40812,6 +43224,36 @@
           <t xml:space="preserve">TAMIL_0B9C</t>
         </is>
       </c>
+      <c r="GT17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3123</t>
+        </is>
+      </c>
+      <c r="GV17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3123</t>
+        </is>
+      </c>
+      <c r="GX17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DE</t>
+        </is>
+      </c>
+      <c r="GZ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10DE</t>
+        </is>
+      </c>
+      <c r="HB17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0569</t>
+        </is>
+      </c>
+      <c r="HC17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0539</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -41174,6 +43616,36 @@
       <c r="GR18" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BCC</t>
+        </is>
+      </c>
+      <c r="GT18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3106</t>
+        </is>
+      </c>
+      <c r="GV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3106</t>
+        </is>
+      </c>
+      <c r="GX18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E5</t>
+        </is>
+      </c>
+      <c r="GZ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E5</t>
+        </is>
+      </c>
+      <c r="HB18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0573</t>
+        </is>
+      </c>
+      <c r="HC18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0543</t>
         </is>
       </c>
     </row>
@@ -41505,6 +43977,41 @@
           <t xml:space="preserve">TAML_DC_0BC0</t>
         </is>
       </c>
+      <c r="GT19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3110</t>
+        </is>
+      </c>
+      <c r="GV19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3110</t>
+        </is>
+      </c>
+      <c r="GX19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E0</t>
+        </is>
+      </c>
+      <c r="GY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E6</t>
+        </is>
+      </c>
+      <c r="GZ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E0</t>
+        </is>
+      </c>
+      <c r="HB19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057D</t>
+        </is>
+      </c>
+      <c r="HC19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054D</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -41840,6 +44347,41 @@
       <c r="GR20" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BC7</t>
+        </is>
+      </c>
+      <c r="GT20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310B</t>
+        </is>
+      </c>
+      <c r="GV20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310B</t>
+        </is>
+      </c>
+      <c r="GX20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E1</t>
+        </is>
+      </c>
+      <c r="GY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E8</t>
+        </is>
+      </c>
+      <c r="GZ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E1</t>
+        </is>
+      </c>
+      <c r="HB20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057E</t>
+        </is>
+      </c>
+      <c r="HC20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054E</t>
         </is>
       </c>
     </row>
@@ -42161,6 +44703,41 @@
           <t xml:space="preserve">TAML_DC_0BC2</t>
         </is>
       </c>
+      <c r="GT21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3114</t>
+        </is>
+      </c>
+      <c r="GV21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3114</t>
+        </is>
+      </c>
+      <c r="GX21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E2</t>
+        </is>
+      </c>
+      <c r="GY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D7</t>
+        </is>
+      </c>
+      <c r="GZ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E2</t>
+        </is>
+      </c>
+      <c r="HB21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0574</t>
+        </is>
+      </c>
+      <c r="HC21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0544</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -42495,6 +45072,36 @@
           <t xml:space="preserve">TAMIL_0BB9</t>
         </is>
       </c>
+      <c r="GT22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3127</t>
+        </is>
+      </c>
+      <c r="GV22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3127</t>
+        </is>
+      </c>
+      <c r="GX22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E3</t>
+        </is>
+      </c>
+      <c r="GZ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E3</t>
+        </is>
+      </c>
+      <c r="HB22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0582</t>
+        </is>
+      </c>
+      <c r="HC22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0552</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -42810,6 +45417,36 @@
           <t xml:space="preserve">TAMIL_0BA8</t>
         </is>
       </c>
+      <c r="GT23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3112</t>
+        </is>
+      </c>
+      <c r="GV23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3112</t>
+        </is>
+      </c>
+      <c r="GX23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D5</t>
+        </is>
+      </c>
+      <c r="GZ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D5</t>
+        </is>
+      </c>
+      <c r="HB23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0575</t>
+        </is>
+      </c>
+      <c r="HC23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0545</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -43160,6 +45797,41 @@
       <c r="GR24" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BC8</t>
+        </is>
+      </c>
+      <c r="GT24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310A</t>
+        </is>
+      </c>
+      <c r="GV24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310A</t>
+        </is>
+      </c>
+      <c r="GX24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EC</t>
+        </is>
+      </c>
+      <c r="GY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10ED</t>
+        </is>
+      </c>
+      <c r="GZ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EC</t>
+        </is>
+      </c>
+      <c r="HB24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0583</t>
+        </is>
+      </c>
+      <c r="HC24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0553</t>
         </is>
       </c>
     </row>
@@ -43477,6 +46149,36 @@
           <t xml:space="preserve">TAML_DC_0B82</t>
         </is>
       </c>
+      <c r="GT25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310C</t>
+        </is>
+      </c>
+      <c r="GV25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_310C</t>
+        </is>
+      </c>
+      <c r="GX25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EE</t>
+        </is>
+      </c>
+      <c r="GZ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EE</t>
+        </is>
+      </c>
+      <c r="HB25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0564</t>
+        </is>
+      </c>
+      <c r="HC25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0534</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -43831,6 +46533,36 @@
           <t xml:space="preserve">TELUGU_0C2C</t>
         </is>
       </c>
+      <c r="GT26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3117</t>
+        </is>
+      </c>
+      <c r="GV26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3117</t>
+        </is>
+      </c>
+      <c r="GX26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E7</t>
+        </is>
+      </c>
+      <c r="GZ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10E7</t>
+        </is>
+      </c>
+      <c r="HB26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0578</t>
+        </is>
+      </c>
+      <c r="HC26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0548</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -44204,6 +46936,41 @@
           <t xml:space="preserve">TAML_DC_0BC6</t>
         </is>
       </c>
+      <c r="GT27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3108</t>
+        </is>
+      </c>
+      <c r="GV27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3108</t>
+        </is>
+      </c>
+      <c r="GX27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D6</t>
+        </is>
+      </c>
+      <c r="GY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10EB</t>
+        </is>
+      </c>
+      <c r="GZ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEORGIAN_10D6</t>
+        </is>
+      </c>
+      <c r="HB27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056A</t>
+        </is>
+      </c>
+      <c r="HC27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053A</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -44752,6 +47519,26 @@
       <c r="GR28" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0BE7</t>
+        </is>
+      </c>
+      <c r="GT28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3105</t>
+        </is>
+      </c>
+      <c r="GV28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3105</t>
+        </is>
+      </c>
+      <c r="HB28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0586</t>
+        </is>
+      </c>
+      <c r="HC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0556</t>
         </is>
       </c>
     </row>
@@ -45325,6 +48112,26 @@
           <t xml:space="preserve">TAMIL_0BE8</t>
         </is>
       </c>
+      <c r="GT29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3109</t>
+        </is>
+      </c>
+      <c r="GV29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3109</t>
+        </is>
+      </c>
+      <c r="HB29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0571</t>
+        </is>
+      </c>
+      <c r="HC29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0541</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -45929,6 +48736,31 @@
           <t xml:space="preserve">TAMIL_0BE9</t>
         </is>
       </c>
+      <c r="GT30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02C7</t>
+        </is>
+      </c>
+      <c r="GV30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02C7</t>
+        </is>
+      </c>
+      <c r="HB30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_058A</t>
+        </is>
+      </c>
+      <c r="HC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2014</t>
+        </is>
+      </c>
+      <c r="HD30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_058A</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -46523,6 +49355,31 @@
           <t xml:space="preserve">TAMIL_0BEA</t>
         </is>
       </c>
+      <c r="GT31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CB</t>
+        </is>
+      </c>
+      <c r="GV31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CB</t>
+        </is>
+      </c>
+      <c r="HB31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="HC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="HD31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -47069,6 +49926,31 @@
           <t xml:space="preserve">TAMIL_0BEB</t>
         </is>
       </c>
+      <c r="GT32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3113</t>
+        </is>
+      </c>
+      <c r="GV32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3113</t>
+        </is>
+      </c>
+      <c r="HB32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0589</t>
+        </is>
+      </c>
+      <c r="HC32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2026</t>
+        </is>
+      </c>
+      <c r="HD32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0589</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -47645,6 +50527,31 @@
           <t xml:space="preserve">TAMIL_0BEC</t>
         </is>
       </c>
+      <c r="GT33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CA</t>
+        </is>
+      </c>
+      <c r="GV33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02CA</t>
+        </is>
+      </c>
+      <c r="HB33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055E</t>
+        </is>
+      </c>
+      <c r="HC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="HD33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055E</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -48208,6 +51115,31 @@
       <c r="GR34" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0BED</t>
+        </is>
+      </c>
+      <c r="GT34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02D9</t>
+        </is>
+      </c>
+      <c r="GV34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_02D9</t>
+        </is>
+      </c>
+      <c r="HB34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2024</t>
+        </is>
+      </c>
+      <c r="HC34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0587</t>
+        </is>
+      </c>
+      <c r="HD34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_2024</t>
         </is>
       </c>
     </row>
@@ -48775,6 +51707,31 @@
           <t xml:space="preserve">TAMIL_0BEE</t>
         </is>
       </c>
+      <c r="GT35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311A</t>
+        </is>
+      </c>
+      <c r="GV35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311A</t>
+        </is>
+      </c>
+      <c r="HB35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055B</t>
+        </is>
+      </c>
+      <c r="HC35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055A</t>
+        </is>
+      </c>
+      <c r="HD35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055B</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -49338,6 +52295,31 @@
           <t xml:space="preserve">TAMIL_0BEF</t>
         </is>
       </c>
+      <c r="GT36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311E</t>
+        </is>
+      </c>
+      <c r="GV36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311E</t>
+        </is>
+      </c>
+      <c r="HB36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="HC36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="HD36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -49939,6 +52921,26 @@
       <c r="GR37" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0BE6</t>
+        </is>
+      </c>
+      <c r="GT37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3122</t>
+        </is>
+      </c>
+      <c r="GV37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3122</t>
+        </is>
+      </c>
+      <c r="HB37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0585</t>
+        </is>
+      </c>
+      <c r="HC37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0555</t>
         </is>
       </c>
     </row>
@@ -51091,6 +54093,26 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
+      <c r="GT43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3126</t>
+        </is>
+      </c>
+      <c r="GV43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3126</t>
+        </is>
+      </c>
+      <c r="HB43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0567</t>
+        </is>
+      </c>
+      <c r="HC43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0537</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -51645,6 +54667,16 @@
           <t xml:space="preserve">TELU_DC_0C43</t>
         </is>
       </c>
+      <c r="HB44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0572</t>
+        </is>
+      </c>
+      <c r="HC44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0542</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -52186,6 +55218,16 @@
           <t xml:space="preserve">TELUGU_0C21</t>
         </is>
       </c>
+      <c r="HB45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056E</t>
+        </is>
+      </c>
+      <c r="HC45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053E</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -52743,6 +55785,16 @@
           <t xml:space="preserve">TAMIL_0B9E</t>
         </is>
       </c>
+      <c r="HB46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0581</t>
+        </is>
+      </c>
+      <c r="HC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0551</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -53208,6 +56260,21 @@
       <c r="GF47" t="inlineStr">
         <is>
           <t xml:space="preserve">THAI_0E03</t>
+        </is>
+      </c>
+      <c r="HB47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
+        </is>
+      </c>
+      <c r="HC47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_L</t>
+        </is>
+      </c>
+      <c r="HD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
         </is>
       </c>
     </row>
@@ -53515,6 +56582,21 @@
           <t xml:space="preserve">THAI_0E03</t>
         </is>
       </c>
+      <c r="HB48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
+        </is>
+      </c>
+      <c r="HC48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_L</t>
+        </is>
+      </c>
+      <c r="HD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -54028,6 +57110,26 @@
       <c r="GR49" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0B9A</t>
+        </is>
+      </c>
+      <c r="GT49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3124</t>
+        </is>
+      </c>
+      <c r="GV49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3124</t>
+        </is>
+      </c>
+      <c r="HB49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057A</t>
+        </is>
+      </c>
+      <c r="HC49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054A</t>
         </is>
       </c>
     </row>
@@ -54589,6 +57691,16 @@
           <t xml:space="preserve">TAMIL_0B9F</t>
         </is>
       </c>
+      <c r="HB50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0580</t>
+        </is>
+      </c>
+      <c r="HC50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0550</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -55099,6 +58211,21 @@
       <c r="GR51" t="inlineStr">
         <is>
           <t xml:space="preserve">TAML_DC_0BCA</t>
+        </is>
+      </c>
+      <c r="HB51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055D</t>
+        </is>
+      </c>
+      <c r="HC51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055C</t>
+        </is>
+      </c>
+      <c r="HD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_055D</t>
         </is>
       </c>
     </row>
@@ -55526,6 +58653,26 @@
           <t xml:space="preserve">,</t>
         </is>
       </c>
+      <c r="GT52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311D</t>
+        </is>
+      </c>
+      <c r="GV52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_311D</t>
+        </is>
+      </c>
+      <c r="HB52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_056D</t>
+        </is>
+      </c>
+      <c r="HC52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_053D</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -55930,6 +59077,26 @@
           <t xml:space="preserve">.</t>
         </is>
       </c>
+      <c r="GT53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3121</t>
+        </is>
+      </c>
+      <c r="GV53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3121</t>
+        </is>
+      </c>
+      <c r="HB53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0577</t>
+        </is>
+      </c>
+      <c r="HC53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_0547</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -56343,6 +59510,26 @@
       <c r="GR54" t="inlineStr">
         <is>
           <t xml:space="preserve">TAMIL_0BAF</t>
+        </is>
+      </c>
+      <c r="GT54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3125</t>
+        </is>
+      </c>
+      <c r="GV54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHUYIN_3125</t>
+        </is>
+      </c>
+      <c r="HB54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_057C</t>
+        </is>
+      </c>
+      <c r="HC54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_054C</t>
         </is>
       </c>
     </row>
@@ -56765,6 +59952,21 @@
           <t xml:space="preserve">DEGREE</t>
         </is>
       </c>
+      <c r="HB55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="HC55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARMENIAN_058A</t>
+        </is>
+      </c>
+      <c r="HD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -57147,6 +60349,30 @@
       <c r="GS56">
         <v>52</v>
       </c>
+      <c r="GU56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="GW56">
+        <v>50</v>
+      </c>
+      <c r="GY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HA56">
+        <v>50</v>
+      </c>
+      <c r="HC56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HE56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -57529,6 +60755,30 @@
       <c r="GS57">
         <v>13</v>
       </c>
+      <c r="GU57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="GW57">
+        <v>12</v>
+      </c>
+      <c r="GY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HA57">
+        <v>12</v>
+      </c>
+      <c r="HC57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HE57">
+        <v>12</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -57880,6 +61130,24 @@
       <c r="GS58">
         <v>52</v>
       </c>
+      <c r="GU58">
+        <v>27</v>
+      </c>
+      <c r="GW58">
+        <v>50</v>
+      </c>
+      <c r="GY58">
+        <v>27</v>
+      </c>
+      <c r="HA58">
+        <v>50</v>
+      </c>
+      <c r="HC58">
+        <v>27</v>
+      </c>
+      <c r="HE58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -58231,6 +61499,24 @@
       <c r="GS59">
         <v>13</v>
       </c>
+      <c r="GU59">
+        <v>0</v>
+      </c>
+      <c r="GW59">
+        <v>12</v>
+      </c>
+      <c r="GY59">
+        <v>0</v>
+      </c>
+      <c r="HA59">
+        <v>12</v>
+      </c>
+      <c r="HC59">
+        <v>0</v>
+      </c>
+      <c r="HE59">
+        <v>12</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -58582,6 +61868,24 @@
       <c r="GS60">
         <v>52</v>
       </c>
+      <c r="GU60">
+        <v>27</v>
+      </c>
+      <c r="GW60">
+        <v>50</v>
+      </c>
+      <c r="GY60">
+        <v>27</v>
+      </c>
+      <c r="HA60">
+        <v>50</v>
+      </c>
+      <c r="HC60">
+        <v>27</v>
+      </c>
+      <c r="HE60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -58932,6 +62236,24 @@
       </c>
       <c r="GS61">
         <v>13</v>
+      </c>
+      <c r="GU61">
+        <v>0</v>
+      </c>
+      <c r="GW61">
+        <v>12</v>
+      </c>
+      <c r="GY61">
+        <v>0</v>
+      </c>
+      <c r="HA61">
+        <v>12</v>
+      </c>
+      <c r="HC61">
+        <v>0</v>
+      </c>
+      <c r="HE61">
+        <v>12</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -6068,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1552"/>
+  <dimension ref="A1:I1563"/>
   <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.25"/>
@@ -36995,6 +36995,138 @@
       <c r="B1552" t="inlineStr">
         <is>
           <t xml:space="preserve">02D9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0259</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0259</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_018F</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01B0</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01B0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01AF</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01A1</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01A0</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0300</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0301</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0303</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0309</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0323</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E1A4</t>
         </is>
       </c>
     </row>
@@ -37017,7 +37149,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:HI79"/>
+  <dimension ref="A1:HU79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -37434,6 +37566,21 @@
           <t xml:space="preserve">id-ID</t>
         </is>
       </c>
+      <c r="HJ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">az-AZ</t>
+        </is>
+      </c>
+      <c r="HN1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is-IS</t>
+        </is>
+      </c>
+      <c r="HR1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vi-VN</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -40760,6 +40907,16 @@
           <t xml:space="preserve">ARMENIAN_053F</t>
         </is>
       </c>
+      <c r="HJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i</t>
+        </is>
+      </c>
+      <c r="HK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I_WITH_DOT</t>
+        </is>
+      </c>
     </row>
     <row r="11" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="93" t="s">
@@ -45834,6 +45991,16 @@
           <t xml:space="preserve">ARMENIAN_0553</t>
         </is>
       </c>
+      <c r="HJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_U_SMALL</t>
+        </is>
+      </c>
+      <c r="HK24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_U</t>
+        </is>
+      </c>
     </row>
     <row r="25" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="93" t="s">
@@ -47541,6 +47708,16 @@
           <t xml:space="preserve">ARMENIAN_0556</t>
         </is>
       </c>
+      <c r="HR28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0103</t>
+        </is>
+      </c>
+      <c r="HS28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0102</t>
+        </is>
+      </c>
     </row>
     <row r="29" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="93" t="s">
@@ -48132,6 +48309,38 @@
           <t xml:space="preserve">ARMENIAN_0541</t>
         </is>
       </c>
+      <c r="HJ29">
+        <v>2</v>
+      </c>
+      <c r="HK29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="HL29">
+        <v>2</v>
+      </c>
+      <c r="HN29">
+        <v>2</v>
+      </c>
+      <c r="HO29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="HP29">
+        <v>2</v>
+      </c>
+      <c r="HR29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00E2</t>
+        </is>
+      </c>
+      <c r="HS29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00C2</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -48761,6 +48970,27 @@
           <t xml:space="preserve">ARMENIAN_058A</t>
         </is>
       </c>
+      <c r="HJ30">
+        <v>3</v>
+      </c>
+      <c r="HK30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUMERO_SIGN</t>
+        </is>
+      </c>
+      <c r="HL30">
+        <v>3</v>
+      </c>
+      <c r="HR30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00EA</t>
+        </is>
+      </c>
+      <c r="HS30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00CA</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -49380,6 +49610,27 @@
           <t xml:space="preserve">COMMA</t>
         </is>
       </c>
+      <c r="HJ31">
+        <v>4</v>
+      </c>
+      <c r="HK31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="HL31">
+        <v>4</v>
+      </c>
+      <c r="HR31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F4</t>
+        </is>
+      </c>
+      <c r="HS31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00D4</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -49951,6 +50202,21 @@
           <t xml:space="preserve">ARMENIAN_0589</t>
         </is>
       </c>
+      <c r="HR32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0300</t>
+        </is>
+      </c>
+      <c r="HS32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="HT32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0300</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -50552,6 +50818,32 @@
           <t xml:space="preserve">ARMENIAN_055E</t>
         </is>
       </c>
+      <c r="HJ33">
+        <v>6</v>
+      </c>
+      <c r="HK33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="HL33">
+        <v>6</v>
+      </c>
+      <c r="HR33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0309</t>
+        </is>
+      </c>
+      <c r="HS33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="HT33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0309</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -51140,6 +51432,32 @@
       <c r="HD34" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_2024</t>
+        </is>
+      </c>
+      <c r="HJ34">
+        <v>7</v>
+      </c>
+      <c r="HK34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="HL34">
+        <v>7</v>
+      </c>
+      <c r="HR34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0303</t>
+        </is>
+      </c>
+      <c r="HS34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="HT34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0303</t>
         </is>
       </c>
     </row>
@@ -51732,6 +52050,21 @@
           <t xml:space="preserve">ARMENIAN_055B</t>
         </is>
       </c>
+      <c r="HR35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0301</t>
+        </is>
+      </c>
+      <c r="HS35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="HT35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0301</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -52320,6 +52653,21 @@
           <t xml:space="preserve">)</t>
         </is>
       </c>
+      <c r="HR36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0323</t>
+        </is>
+      </c>
+      <c r="HS36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="HT36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIET_DC_0323</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -52941,6 +53289,16 @@
       <c r="HC37" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0555</t>
+        </is>
+      </c>
+      <c r="HR37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0111</t>
+        </is>
+      </c>
+      <c r="HS37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0110</t>
         </is>
       </c>
     </row>
@@ -54113,6 +54471,16 @@
           <t xml:space="preserve">ARMENIAN_0537</t>
         </is>
       </c>
+      <c r="HN43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O_SMALL</t>
+        </is>
+      </c>
+      <c r="HO43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -54677,6 +55045,36 @@
           <t xml:space="preserve">ARMENIAN_0542</t>
         </is>
       </c>
+      <c r="HN44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="HO44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="HP44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="HR44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DONG_SIGN</t>
+        </is>
+      </c>
+      <c r="HS44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="HT44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DONG_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -55228,6 +55626,36 @@
           <t xml:space="preserve">ARMENIAN_053E</t>
         </is>
       </c>
+      <c r="HJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O_SMALL</t>
+        </is>
+      </c>
+      <c r="HK45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O</t>
+        </is>
+      </c>
+      <c r="HN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F0</t>
+        </is>
+      </c>
+      <c r="HO45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00D0</t>
+        </is>
+      </c>
+      <c r="HR45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01B0</t>
+        </is>
+      </c>
+      <c r="HS45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01AF</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -55795,6 +56223,41 @@
           <t xml:space="preserve">ARMENIAN_0551</t>
         </is>
       </c>
+      <c r="HJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_WITH_BREVE_SMALL</t>
+        </is>
+      </c>
+      <c r="HK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G_WITH_BREVE</t>
+        </is>
+      </c>
+      <c r="HN46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="HO46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="HP46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="HR46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01A1</t>
+        </is>
+      </c>
+      <c r="HS46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_01A0</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -56275,6 +56738,36 @@
       <c r="HD47" t="inlineStr">
         <is>
           <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
+        </is>
+      </c>
+      <c r="HJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="HK47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="HL47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="HN47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="HO47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="HP47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
         </is>
       </c>
     </row>
@@ -56597,6 +57090,36 @@
           <t xml:space="preserve">DBL_ANGLE_QMARK_R</t>
         </is>
       </c>
+      <c r="HJ48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="HK48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="HL48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="HN48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="HO48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="HP48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -57130,6 +57653,26 @@
       <c r="HC49" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_054A</t>
+        </is>
+      </c>
+      <c r="HJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I_DOTLESS_SMALL</t>
+        </is>
+      </c>
+      <c r="HK49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="HN49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LETTER_AE_SMALL</t>
+        </is>
+      </c>
+      <c r="HO49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00C6</t>
         </is>
       </c>
     </row>
@@ -57701,6 +58244,31 @@
           <t xml:space="preserve">ARMENIAN_0550</t>
         </is>
       </c>
+      <c r="HJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0259</t>
+        </is>
+      </c>
+      <c r="HK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_018F</t>
+        </is>
+      </c>
+      <c r="HN50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="HO50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="HP50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -58226,6 +58794,21 @@
       <c r="HD51" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_055D</t>
+        </is>
+      </c>
+      <c r="HN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_RING</t>
+        </is>
+      </c>
+      <c r="HO51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="HP51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_RING</t>
         </is>
       </c>
     </row>
@@ -58673,6 +59256,16 @@
           <t xml:space="preserve">ARMENIAN_053D</t>
         </is>
       </c>
+      <c r="HJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="HK52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C_WITH_CEDILLA</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -59097,6 +59690,16 @@
           <t xml:space="preserve">ARMENIAN_0547</t>
         </is>
       </c>
+      <c r="HJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="HK53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S_WITH_CEDILLA</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -59530,6 +60133,31 @@
       <c r="HC54" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_054C</t>
+        </is>
+      </c>
+      <c r="HJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="HK54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="HL54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="HN54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FE</t>
+        </is>
+      </c>
+      <c r="HO54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00DE</t>
         </is>
       </c>
     </row>
@@ -60373,6 +61001,30 @@
       <c r="HE56">
         <v>50</v>
       </c>
+      <c r="HK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HM56">
+        <v>50</v>
+      </c>
+      <c r="HO56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HQ56">
+        <v>50</v>
+      </c>
+      <c r="HS56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HU56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -60779,6 +61431,30 @@
       <c r="HE57">
         <v>12</v>
       </c>
+      <c r="HK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HM57">
+        <v>13</v>
+      </c>
+      <c r="HO57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HQ57">
+        <v>13</v>
+      </c>
+      <c r="HS57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="HU57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -61148,6 +61824,24 @@
       <c r="HE58">
         <v>50</v>
       </c>
+      <c r="HK58">
+        <v>28</v>
+      </c>
+      <c r="HM58">
+        <v>50</v>
+      </c>
+      <c r="HO58">
+        <v>28</v>
+      </c>
+      <c r="HQ58">
+        <v>50</v>
+      </c>
+      <c r="HS58">
+        <v>28</v>
+      </c>
+      <c r="HU58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -61517,6 +62211,24 @@
       <c r="HE59">
         <v>12</v>
       </c>
+      <c r="HK59">
+        <v>0</v>
+      </c>
+      <c r="HM59">
+        <v>13</v>
+      </c>
+      <c r="HO59">
+        <v>0</v>
+      </c>
+      <c r="HQ59">
+        <v>13</v>
+      </c>
+      <c r="HS59">
+        <v>0</v>
+      </c>
+      <c r="HU59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -61886,6 +62598,24 @@
       <c r="HE60">
         <v>50</v>
       </c>
+      <c r="HK60">
+        <v>28</v>
+      </c>
+      <c r="HM60">
+        <v>50</v>
+      </c>
+      <c r="HO60">
+        <v>28</v>
+      </c>
+      <c r="HQ60">
+        <v>50</v>
+      </c>
+      <c r="HS60">
+        <v>28</v>
+      </c>
+      <c r="HU60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -62254,6 +62984,24 @@
       </c>
       <c r="HE61">
         <v>12</v>
+      </c>
+      <c r="HK61">
+        <v>0</v>
+      </c>
+      <c r="HM61">
+        <v>13</v>
+      </c>
+      <c r="HO61">
+        <v>0</v>
+      </c>
+      <c r="HQ61">
+        <v>13</v>
+      </c>
+      <c r="HS61">
+        <v>0</v>
+      </c>
+      <c r="HU61">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -61415,6 +61415,9 @@
       <c r="GW57">
         <v>12</v>
       </c>
+      <c r="GX57">
+        <v>3</v>
+      </c>
       <c r="GY57" t="inlineStr">
         <is>
           <t xml:space="preserve">HIDE</t>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -61401,8 +61401,13 @@
       <c r="GO57">
         <v>13</v>
       </c>
-      <c r="GQ57">
-        <v>0</v>
+      <c r="GP57">
+        <v>3</v>
+      </c>
+      <c r="GQ57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
       </c>
       <c r="GS57">
         <v>13</v>
@@ -62190,6 +62195,9 @@
       <c r="GO59">
         <v>13</v>
       </c>
+      <c r="GP59">
+        <v>3</v>
+      </c>
       <c r="GQ59">
         <v>0</v>
       </c>
@@ -62963,6 +62971,9 @@
       </c>
       <c r="GO61">
         <v>13</v>
+      </c>
+      <c r="GP61">
+        <v>3</v>
       </c>
       <c r="GQ61">
         <v>0</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -47718,6 +47718,9 @@
           <t xml:space="preserve">LATIN_0102</t>
         </is>
       </c>
+      <c r="HU28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="93" t="s">
@@ -48341,6 +48344,9 @@
           <t xml:space="preserve">LATIN_00C2</t>
         </is>
       </c>
+      <c r="HU29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -48991,6 +48997,9 @@
           <t xml:space="preserve">LATIN_00CA</t>
         </is>
       </c>
+      <c r="HU30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -49631,6 +49640,9 @@
           <t xml:space="preserve">LATIN_00D4</t>
         </is>
       </c>
+      <c r="HU31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -50217,6 +50229,9 @@
           <t xml:space="preserve">VIET_DC_0300</t>
         </is>
       </c>
+      <c r="HU32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -50844,6 +50859,9 @@
           <t xml:space="preserve">VIET_DC_0309</t>
         </is>
       </c>
+      <c r="HU33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -51459,6 +51477,9 @@
         <is>
           <t xml:space="preserve">VIET_DC_0303</t>
         </is>
+      </c>
+      <c r="HU34">
+        <v>7</v>
       </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52065,6 +52086,9 @@
           <t xml:space="preserve">VIET_DC_0301</t>
         </is>
       </c>
+      <c r="HU35">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -52668,6 +52692,9 @@
           <t xml:space="preserve">VIET_DC_0323</t>
         </is>
       </c>
+      <c r="HU36">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -53299,6 +53326,11 @@
       <c r="HS37" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_0110</t>
+        </is>
+      </c>
+      <c r="HU37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
         </is>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -47658,6 +47658,9 @@
           <t xml:space="preserve">THAI_0E45</t>
         </is>
       </c>
+      <c r="GG28">
+        <v>1</v>
+      </c>
       <c r="GH28" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09E7</t>
@@ -48262,6 +48265,9 @@
           <t xml:space="preserve">/</t>
         </is>
       </c>
+      <c r="GG29">
+        <v>2</v>
+      </c>
       <c r="GH29" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09E8</t>
@@ -48906,6 +48912,9 @@
           <t xml:space="preserve">-</t>
         </is>
       </c>
+      <c r="GG30">
+        <v>3</v>
+      </c>
       <c r="GH30" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09E9</t>
@@ -49549,6 +49558,9 @@
           <t xml:space="preserve">THAI_0E20</t>
         </is>
       </c>
+      <c r="GG31">
+        <v>4</v>
+      </c>
       <c r="GH31" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09EA</t>
@@ -50144,6 +50156,9 @@
           <t xml:space="preserve">THAI_0E16</t>
         </is>
       </c>
+      <c r="GG32">
+        <v>5</v>
+      </c>
       <c r="GH32" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09EB</t>
@@ -50763,6 +50778,9 @@
           <t xml:space="preserve">THAI_DC_0E38</t>
         </is>
       </c>
+      <c r="GG33">
+        <v>6</v>
+      </c>
       <c r="GH33" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09EC</t>
@@ -51381,6 +51399,9 @@
         <is>
           <t xml:space="preserve">THAI_DC_0E36</t>
         </is>
+      </c>
+      <c r="GG34">
+        <v>7</v>
       </c>
       <c r="GH34" t="inlineStr">
         <is>
@@ -52001,6 +52022,9 @@
           <t xml:space="preserve">THAI_0E04</t>
         </is>
       </c>
+      <c r="GG35">
+        <v>8</v>
+      </c>
       <c r="GH35" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09EE</t>
@@ -52607,6 +52631,9 @@
           <t xml:space="preserve">THAI_0E15</t>
         </is>
       </c>
+      <c r="GG36">
+        <v>9</v>
+      </c>
       <c r="GH36" t="inlineStr">
         <is>
           <t xml:space="preserve">BENGALI_09EF</t>
@@ -53251,6 +53278,11 @@
       <c r="GF37" t="inlineStr">
         <is>
           <t xml:space="preserve">THAI_0E08</t>
+        </is>
+      </c>
+      <c r="GG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
         </is>
       </c>
       <c r="GH37" t="inlineStr">
@@ -61436,10 +61468,8 @@
       <c r="GP57">
         <v>3</v>
       </c>
-      <c r="GQ57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HIDE</t>
-        </is>
+      <c r="GQ57">
+        <v>0</v>
       </c>
       <c r="GS57">
         <v>13</v>
@@ -61462,6 +61492,9 @@
       </c>
       <c r="HA57">
         <v>12</v>
+      </c>
+      <c r="HB57">
+        <v>3</v>
       </c>
       <c r="HC57" t="inlineStr">
         <is>
@@ -62248,6 +62281,9 @@
       <c r="HA59">
         <v>12</v>
       </c>
+      <c r="HB59">
+        <v>3</v>
+      </c>
       <c r="HC59">
         <v>0</v>
       </c>
@@ -63024,6 +63060,9 @@
       </c>
       <c r="HA61">
         <v>12</v>
+      </c>
+      <c r="HB61">
+        <v>3</v>
       </c>
       <c r="HC61">
         <v>0</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -47711,6 +47711,9 @@
           <t xml:space="preserve">ARMENIAN_0556</t>
         </is>
       </c>
+      <c r="HE28">
+        <v>1</v>
+      </c>
       <c r="HR28" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_0103</t>
@@ -48318,6 +48321,9 @@
           <t xml:space="preserve">ARMENIAN_0541</t>
         </is>
       </c>
+      <c r="HE29">
+        <v>2</v>
+      </c>
       <c r="HJ29">
         <v>2</v>
       </c>
@@ -48985,6 +48991,9 @@
           <t xml:space="preserve">ARMENIAN_058A</t>
         </is>
       </c>
+      <c r="HE30">
+        <v>3</v>
+      </c>
       <c r="HJ30">
         <v>3</v>
       </c>
@@ -49631,6 +49640,9 @@
           <t xml:space="preserve">COMMA</t>
         </is>
       </c>
+      <c r="HE31">
+        <v>4</v>
+      </c>
       <c r="HJ31">
         <v>4</v>
       </c>
@@ -50229,6 +50241,9 @@
           <t xml:space="preserve">ARMENIAN_0589</t>
         </is>
       </c>
+      <c r="HE32">
+        <v>5</v>
+      </c>
       <c r="HR32" t="inlineStr">
         <is>
           <t xml:space="preserve">VIET_DC_0300</t>
@@ -50851,6 +50866,9 @@
           <t xml:space="preserve">ARMENIAN_055E</t>
         </is>
       </c>
+      <c r="HE33">
+        <v>6</v>
+      </c>
       <c r="HJ33">
         <v>6</v>
       </c>
@@ -51472,6 +51490,9 @@
         <is>
           <t xml:space="preserve">ARMENIAN_2024</t>
         </is>
+      </c>
+      <c r="HE34">
+        <v>7</v>
       </c>
       <c r="HJ34">
         <v>7</v>
@@ -52095,6 +52116,9 @@
           <t xml:space="preserve">ARMENIAN_055B</t>
         </is>
       </c>
+      <c r="HE35">
+        <v>8</v>
+      </c>
       <c r="HR35" t="inlineStr">
         <is>
           <t xml:space="preserve">VIET_DC_0301</t>
@@ -52704,6 +52728,9 @@
           <t xml:space="preserve">)</t>
         </is>
       </c>
+      <c r="HE36">
+        <v>9</v>
+      </c>
       <c r="HR36" t="inlineStr">
         <is>
           <t xml:space="preserve">VIET_DC_0323</t>
@@ -53348,6 +53375,11 @@
       <c r="HC37" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0555</t>
+        </is>
+      </c>
+      <c r="HE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
         </is>
       </c>
       <c r="HR37" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -37915,7 +37915,7 @@
       </c>
       <c r="GQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAMIL_0B93</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GR2" t="inlineStr">
@@ -43767,7 +43767,7 @@
       </c>
       <c r="GQ18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAMIL_0B94</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GR18" t="inlineStr">
@@ -58869,7 +58869,7 @@
       </c>
       <c r="GQ51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAMIL_0B92</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="GR51" t="inlineStr">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -37149,7 +37149,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:HU79"/>
+  <dimension ref="A1:HY79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -37581,6 +37581,14 @@
           <t xml:space="preserve">vi-VN</t>
         </is>
       </c>
+      <c r="HV1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zh-HK</t>
+        </is>
+      </c>
+      <c r="HY1">
+        <v>3076</v>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -37951,6 +37959,21 @@
       <c r="HC2" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_054B</t>
+        </is>
+      </c>
+      <c r="HV2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_SUN</t>
+        </is>
+      </c>
+      <c r="HW2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="HX2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_SUN</t>
         </is>
       </c>
     </row>
@@ -38296,6 +38319,21 @@
           <t xml:space="preserve">ARMENIAN_0536</t>
         </is>
       </c>
+      <c r="HV3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOON</t>
+        </is>
+      </c>
+      <c r="HW3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b</t>
+        </is>
+      </c>
+      <c r="HX3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOON</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -38670,6 +38708,21 @@
           <t xml:space="preserve">ARMENIAN_0549</t>
         </is>
       </c>
+      <c r="HV4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_GOLD</t>
+        </is>
+      </c>
+      <c r="HW4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c</t>
+        </is>
+      </c>
+      <c r="HX4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_GOLD</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -39029,6 +39082,21 @@
           <t xml:space="preserve">ARMENIAN_0533</t>
         </is>
       </c>
+      <c r="HV5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_TREE</t>
+        </is>
+      </c>
+      <c r="HW5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d</t>
+        </is>
+      </c>
+      <c r="HX5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_TREE</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -39489,6 +39557,21 @@
       <c r="HC6" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0532</t>
+        </is>
+      </c>
+      <c r="HV6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_WATER</t>
+        </is>
+      </c>
+      <c r="HW6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e</t>
+        </is>
+      </c>
+      <c r="HX6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_WATER</t>
         </is>
       </c>
     </row>
@@ -39849,6 +39932,21 @@
           <t xml:space="preserve">ARMENIAN_0535</t>
         </is>
       </c>
+      <c r="HV7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_FIRE</t>
+        </is>
+      </c>
+      <c r="HW7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f</t>
+        </is>
+      </c>
+      <c r="HX7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_FIRE</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -40210,6 +40308,21 @@
           <t xml:space="preserve">ARMENIAN_0531</t>
         </is>
       </c>
+      <c r="HV8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_EARTH</t>
+        </is>
+      </c>
+      <c r="HW8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g</t>
+        </is>
+      </c>
+      <c r="HX8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_EARTH</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -40556,6 +40669,21 @@
           <t xml:space="preserve">ARMENIAN_0546</t>
         </is>
       </c>
+      <c r="HV9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BAMBOO</t>
+        </is>
+      </c>
+      <c r="HW9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h</t>
+        </is>
+      </c>
+      <c r="HX9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BAMBOO</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -40915,6 +41043,21 @@
       <c r="HK10" t="inlineStr">
         <is>
           <t xml:space="preserve">I_WITH_DOT</t>
+        </is>
+      </c>
+      <c r="HV10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HALBERD</t>
+        </is>
+      </c>
+      <c r="HW10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i</t>
+        </is>
+      </c>
+      <c r="HX10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HALBERD</t>
         </is>
       </c>
     </row>
@@ -41272,6 +41415,21 @@
           <t xml:space="preserve">ARMENIAN_053B</t>
         </is>
       </c>
+      <c r="HV11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_TEN</t>
+        </is>
+      </c>
+      <c r="HW11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">j</t>
+        </is>
+      </c>
+      <c r="HX11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_TEN</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -41625,6 +41783,21 @@
           <t xml:space="preserve">ARMENIAN_054F</t>
         </is>
       </c>
+      <c r="HV12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BIG</t>
+        </is>
+      </c>
+      <c r="HW12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">k</t>
+        </is>
+      </c>
+      <c r="HX12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BIG</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -41980,6 +42153,21 @@
           <t xml:space="preserve">ARMENIAN_0540</t>
         </is>
       </c>
+      <c r="HV13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_4E2D</t>
+        </is>
+      </c>
+      <c r="HW13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">l</t>
+        </is>
+      </c>
+      <c r="HX13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_4E2D</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -42359,6 +42547,21 @@
       <c r="HC14" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0554</t>
+        </is>
+      </c>
+      <c r="HV14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_ONE</t>
+        </is>
+      </c>
+      <c r="HW14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="HX14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_ONE</t>
         </is>
       </c>
     </row>
@@ -42721,6 +42924,21 @@
           <t xml:space="preserve">ARMENIAN_053C</t>
         </is>
       </c>
+      <c r="HV15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BOW</t>
+        </is>
+      </c>
+      <c r="HW15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="HX15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_BOW</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -43061,6 +43279,21 @@
           <t xml:space="preserve">ARMENIAN_0538</t>
         </is>
       </c>
+      <c r="HV16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MAN</t>
+        </is>
+      </c>
+      <c r="HW16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">o</t>
+        </is>
+      </c>
+      <c r="HX16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MAN</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -43411,6 +43644,21 @@
           <t xml:space="preserve">ARMENIAN_0539</t>
         </is>
       </c>
+      <c r="HV17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HEART</t>
+        </is>
+      </c>
+      <c r="HW17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p</t>
+        </is>
+      </c>
+      <c r="HX17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HEART</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -43803,6 +44051,21 @@
       <c r="HC18" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0543</t>
+        </is>
+      </c>
+      <c r="HV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HAND</t>
+        </is>
+      </c>
+      <c r="HW18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="HX18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_HAND</t>
         </is>
       </c>
     </row>
@@ -44169,6 +44432,21 @@
           <t xml:space="preserve">ARMENIAN_054D</t>
         </is>
       </c>
+      <c r="HV19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOUTH</t>
+        </is>
+      </c>
+      <c r="HW19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">r</t>
+        </is>
+      </c>
+      <c r="HX19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOUTH</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -44539,6 +44817,21 @@
       <c r="HC20" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_054E</t>
+        </is>
+      </c>
+      <c r="HV20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_CORPSE</t>
+        </is>
+      </c>
+      <c r="HW20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="HX20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_CORPSE</t>
         </is>
       </c>
     </row>
@@ -44895,6 +45188,21 @@
           <t xml:space="preserve">ARMENIAN_0544</t>
         </is>
       </c>
+      <c r="HV21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_5EFF</t>
+        </is>
+      </c>
+      <c r="HW21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">t</t>
+        </is>
+      </c>
+      <c r="HX21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_5EFF</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -45259,6 +45567,21 @@
           <t xml:space="preserve">ARMENIAN_0552</t>
         </is>
       </c>
+      <c r="HV22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOUNTAIN</t>
+        </is>
+      </c>
+      <c r="HW22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u</t>
+        </is>
+      </c>
+      <c r="HX22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_MOUNTAIN</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -45604,6 +45927,21 @@
           <t xml:space="preserve">ARMENIAN_0545</t>
         </is>
       </c>
+      <c r="HV23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_WOMAN</t>
+        </is>
+      </c>
+      <c r="HW23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v</t>
+        </is>
+      </c>
+      <c r="HX23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_WOMAN</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -45999,6 +46337,21 @@
       <c r="HK24" t="inlineStr">
         <is>
           <t xml:space="preserve">UMLAUT_U</t>
+        </is>
+      </c>
+      <c r="HV24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_FIELD</t>
+        </is>
+      </c>
+      <c r="HW24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w</t>
+        </is>
+      </c>
+      <c r="HX24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_FIELD</t>
         </is>
       </c>
     </row>
@@ -46346,6 +46699,21 @@
           <t xml:space="preserve">ARMENIAN_0534</t>
         </is>
       </c>
+      <c r="HV25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_96E3</t>
+        </is>
+      </c>
+      <c r="HW25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="HX25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_96E3</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -46730,6 +47098,21 @@
           <t xml:space="preserve">ARMENIAN_0548</t>
         </is>
       </c>
+      <c r="HV26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_DIVINATION</t>
+        </is>
+      </c>
+      <c r="HW26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y</t>
+        </is>
+      </c>
+      <c r="HX26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_DIVINATION</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -47138,6 +47521,21 @@
           <t xml:space="preserve">ARMENIAN_053A</t>
         </is>
       </c>
+      <c r="HV27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
+      <c r="HW27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="HX27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -47725,6 +48123,17 @@
         </is>
       </c>
       <c r="HU28">
+        <v>1</v>
+      </c>
+      <c r="HV28">
+        <v>1</v>
+      </c>
+      <c r="HW28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="HX28">
         <v>1</v>
       </c>
     </row>
@@ -48359,6 +48768,17 @@
       <c r="HU29">
         <v>2</v>
       </c>
+      <c r="HV29">
+        <v>2</v>
+      </c>
+      <c r="HW29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDDLE_DOT</t>
+        </is>
+      </c>
+      <c r="HX29">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -49018,6 +49438,17 @@
       <c r="HU30">
         <v>3</v>
       </c>
+      <c r="HV30">
+        <v>3</v>
+      </c>
+      <c r="HW30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LANGLE_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX30">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -49667,6 +50098,17 @@
       <c r="HU31">
         <v>4</v>
       </c>
+      <c r="HV31">
+        <v>4</v>
+      </c>
+      <c r="HW31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YEN_SIGN</t>
+        </is>
+      </c>
+      <c r="HX31">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -50262,6 +50704,17 @@
       <c r="HU32">
         <v>5</v>
       </c>
+      <c r="HV32">
+        <v>5</v>
+      </c>
+      <c r="HW32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RANGLE_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX32">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -50898,6 +51351,17 @@
       <c r="HU33">
         <v>6</v>
       </c>
+      <c r="HV33">
+        <v>6</v>
+      </c>
+      <c r="HW33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LWCORNER_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX33">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -51521,6 +51985,17 @@
         </is>
       </c>
       <c r="HU34">
+        <v>7</v>
+      </c>
+      <c r="HV34">
+        <v>7</v>
+      </c>
+      <c r="HW34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RWCORNER_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX34">
         <v>7</v>
       </c>
     </row>
@@ -52137,6 +52612,17 @@
       <c r="HU35">
         <v>8</v>
       </c>
+      <c r="HV35">
+        <v>8</v>
+      </c>
+      <c r="HW35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u". . ."</t>
+        </is>
+      </c>
+      <c r="HX35">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -52749,6 +53235,17 @@
       <c r="HU36">
         <v>9</v>
       </c>
+      <c r="HV36">
+        <v>9</v>
+      </c>
+      <c r="HW36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="HX36">
+        <v>9</v>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -53396,6 +53893,17 @@
         <is>
           <t xml:space="preserve">ZERO</t>
         </is>
+      </c>
+      <c r="HV37">
+        <v>0</v>
+      </c>
+      <c r="HW37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="HX37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54577,6 +55085,21 @@
           <t xml:space="preserve">UMLAUT_O</t>
         </is>
       </c>
+      <c r="HV43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON_LEFT</t>
+        </is>
+      </c>
+      <c r="HW43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCORNER_BRKT</t>
+        </is>
+      </c>
+      <c r="HX43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON_LEFT</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -55171,6 +55694,21 @@
           <t xml:space="preserve">DONG_SIGN</t>
         </is>
       </c>
+      <c r="HV44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON_RIGHT</t>
+        </is>
+      </c>
+      <c r="HW44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RCORNER_BRKT</t>
+        </is>
+      </c>
+      <c r="HX44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ICON_RIGHT</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -55752,6 +56290,21 @@
           <t xml:space="preserve">LATIN_01AF</t>
         </is>
       </c>
+      <c r="HV45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="HW45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LLENTICULAR_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -56354,6 +56907,21 @@
           <t xml:space="preserve">LATIN_01A0</t>
         </is>
       </c>
+      <c r="HV46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="HW46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RLENTICULAR_BRACKET</t>
+        </is>
+      </c>
+      <c r="HX46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -56864,6 +57432,21 @@
       <c r="HP47" t="inlineStr">
         <is>
           <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="HV47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_IDEOG_COMMA</t>
+        </is>
+      </c>
+      <c r="HW47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_ONE</t>
+        </is>
+      </c>
+      <c r="HX47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_IDEOG_COMMA</t>
         </is>
       </c>
     </row>
@@ -57216,6 +57799,21 @@
           <t xml:space="preserve">+</t>
         </is>
       </c>
+      <c r="HV48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="HW48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="HX48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -57769,6 +58367,21 @@
       <c r="HO49" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_00C6</t>
+        </is>
+      </c>
+      <c r="HV49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="HW49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="HX49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
         </is>
       </c>
     </row>
@@ -58365,6 +58978,21 @@
           <t xml:space="preserve">ACUTE_ACCENT</t>
         </is>
       </c>
+      <c r="HV50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="HW50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="HX50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -58905,6 +59533,21 @@
       <c r="HP51" t="inlineStr">
         <is>
           <t xml:space="preserve">MOD_RING</t>
+        </is>
+      </c>
+      <c r="HV51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="HW51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="HX51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
         </is>
       </c>
     </row>
@@ -59362,6 +60005,21 @@
           <t xml:space="preserve">C_WITH_CEDILLA</t>
         </is>
       </c>
+      <c r="HV52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="HW52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LANGLE_BRACKET_DBL</t>
+        </is>
+      </c>
+      <c r="HX52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -59796,6 +60454,16 @@
           <t xml:space="preserve">S_WITH_CEDILLA</t>
         </is>
       </c>
+      <c r="HV53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_IDEOG_FSTOP</t>
+        </is>
+      </c>
+      <c r="HW53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RANGLE_BRACKET_DBL</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -60254,6 +60922,21 @@
       <c r="HO54" t="inlineStr">
         <is>
           <t xml:space="preserve">LATIN_00DE</t>
+        </is>
+      </c>
+      <c r="HV54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="HW54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="HX54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
         </is>
       </c>
     </row>
@@ -60691,6 +61374,21 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
+      <c r="HV55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_IDEOG_COMMA</t>
+        </is>
+      </c>
+      <c r="HW55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KANGXI_RADICAL_ONE</t>
+        </is>
+      </c>
+      <c r="HX55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_IDEOG_COMMA</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -61121,6 +61819,9 @@
       <c r="HU56">
         <v>50</v>
       </c>
+      <c r="HW56">
+        <v>42</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -61560,6 +62261,9 @@
       <c r="HU57">
         <v>13</v>
       </c>
+      <c r="HW57">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -61947,6 +62651,9 @@
       <c r="HU58">
         <v>50</v>
       </c>
+      <c r="HW58">
+        <v>34</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -62340,6 +63047,9 @@
       <c r="HU59">
         <v>13</v>
       </c>
+      <c r="HW59">
+        <v>10</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -62727,6 +63437,9 @@
       <c r="HU60">
         <v>50</v>
       </c>
+      <c r="HW60">
+        <v>34</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -63119,6 +63832,9 @@
       </c>
       <c r="HU61">
         <v>13</v>
+      </c>
+      <c r="HW61">
+        <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -6068,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1563"/>
+  <dimension ref="A1:I1564"/>
   <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.25"/>
@@ -37127,6 +37127,18 @@
       <c r="B1563" t="inlineStr">
         <is>
           <t xml:space="preserve">E1A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_91CD</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91CD</t>
         </is>
       </c>
     </row>
@@ -47240,14 +47252,18 @@
       <c r="BS27" s="110"/>
       <c r="BT27" s="110"/>
       <c r="BU27" s="110"/>
-      <c r="BV27" s="83" t="s">
-        <v>1220</v>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_91CD</t>
+        </is>
       </c>
       <c r="BW27" s="84" t="s">
         <v>1219</v>
       </c>
-      <c r="BX27" s="83" t="s">
-        <v>1219</v>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJK_91CD</t>
+        </is>
       </c>
       <c r="BY27" s="84"/>
       <c r="BZ27" s="111"/>
@@ -47523,7 +47539,7 @@
       </c>
       <c r="HV27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z</t>
+          <t xml:space="preserve">CJK_91CD</t>
         </is>
       </c>
       <c r="HW27" t="inlineStr">
@@ -47533,7 +47549,7 @@
       </c>
       <c r="HX27" t="inlineStr">
         <is>
-          <t xml:space="preserve">z</t>
+          <t xml:space="preserve">CJK_91CD</t>
         </is>
       </c>
     </row>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -37722,16 +37722,6 @@
       <c r="BS2" s="82"/>
       <c r="BT2" s="82"/>
       <c r="BU2" s="82"/>
-      <c r="BV2" s="83" t="s">
-        <v>767</v>
-      </c>
-      <c r="BW2" s="84" t="s">
-        <v>1130</v>
-      </c>
-      <c r="BX2" s="83" t="s">
-        <v>767</v>
-      </c>
-      <c r="BY2" s="83"/>
       <c r="BZ2" s="85"/>
       <c r="CA2" s="85"/>
       <c r="CB2" s="85"/>
@@ -38103,16 +38093,6 @@
       <c r="BS3" s="110"/>
       <c r="BT3" s="110"/>
       <c r="BU3" s="110"/>
-      <c r="BV3" s="83" t="s">
-        <v>769</v>
-      </c>
-      <c r="BW3" s="84" t="s">
-        <v>1135</v>
-      </c>
-      <c r="BX3" s="83" t="s">
-        <v>769</v>
-      </c>
-      <c r="BY3" s="84"/>
       <c r="BZ3" s="111"/>
       <c r="CA3" s="111"/>
       <c r="CB3" s="111"/>
@@ -38465,16 +38445,6 @@
       <c r="BU4" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="BV4" s="83" t="s">
-        <v>781</v>
-      </c>
-      <c r="BW4" s="84" t="s">
-        <v>1139</v>
-      </c>
-      <c r="BX4" s="83" t="s">
-        <v>781</v>
-      </c>
-      <c r="BY4" s="84"/>
       <c r="BZ4" s="111"/>
       <c r="CA4" s="111"/>
       <c r="CB4" s="125" t="s">
@@ -38856,16 +38826,6 @@
       <c r="BU5" s="110" t="s">
         <v>1146</v>
       </c>
-      <c r="BV5" s="83" t="s">
-        <v>771</v>
-      </c>
-      <c r="BW5" s="84" t="s">
-        <v>1143</v>
-      </c>
-      <c r="BX5" s="83" t="s">
-        <v>771</v>
-      </c>
-      <c r="BY5" s="84"/>
       <c r="BZ5" s="111"/>
       <c r="CA5" s="111"/>
       <c r="CB5" s="111"/>
@@ -39246,16 +39206,6 @@
       <c r="BU6" s="110" t="s">
         <v>682</v>
       </c>
-      <c r="BV6" s="83" t="s">
-        <v>773</v>
-      </c>
-      <c r="BW6" s="84" t="s">
-        <v>1148</v>
-      </c>
-      <c r="BX6" s="83" t="s">
-        <v>773</v>
-      </c>
-      <c r="BY6" s="84"/>
       <c r="BZ6" s="111"/>
       <c r="CA6" s="111"/>
       <c r="CB6" s="111" t="s">
@@ -39701,16 +39651,6 @@
       <c r="BS7" s="110"/>
       <c r="BT7" s="110"/>
       <c r="BU7" s="110"/>
-      <c r="BV7" s="83" t="s">
-        <v>775</v>
-      </c>
-      <c r="BW7" s="84" t="s">
-        <v>1152</v>
-      </c>
-      <c r="BX7" s="83" t="s">
-        <v>775</v>
-      </c>
-      <c r="BY7" s="84"/>
       <c r="BZ7" s="111"/>
       <c r="CA7" s="111"/>
       <c r="CB7" s="111"/>
@@ -40070,16 +40010,6 @@
       <c r="BS8" s="110"/>
       <c r="BT8" s="110"/>
       <c r="BU8" s="110"/>
-      <c r="BV8" s="83" t="s">
-        <v>749</v>
-      </c>
-      <c r="BW8" s="84" t="s">
-        <v>1156</v>
-      </c>
-      <c r="BX8" s="83" t="s">
-        <v>749</v>
-      </c>
-      <c r="BY8" s="84"/>
       <c r="BZ8" s="111"/>
       <c r="CA8" s="111"/>
       <c r="CB8" s="111"/>
@@ -40450,16 +40380,6 @@
       <c r="BS9" s="110"/>
       <c r="BT9" s="110"/>
       <c r="BU9" s="110"/>
-      <c r="BV9" s="83" t="s">
-        <v>779</v>
-      </c>
-      <c r="BW9" s="84" t="s">
-        <v>1159</v>
-      </c>
-      <c r="BX9" s="83" t="s">
-        <v>779</v>
-      </c>
-      <c r="BY9" s="84"/>
       <c r="BZ9" s="111"/>
       <c r="CA9" s="111"/>
       <c r="CB9" s="111"/>
@@ -40817,16 +40737,6 @@
       <c r="BS10" s="110"/>
       <c r="BT10" s="110"/>
       <c r="BU10" s="110"/>
-      <c r="BV10" s="83" t="s">
-        <v>763</v>
-      </c>
-      <c r="BW10" s="84" t="s">
-        <v>1162</v>
-      </c>
-      <c r="BX10" s="83" t="s">
-        <v>763</v>
-      </c>
-      <c r="BY10" s="84"/>
       <c r="BZ10" s="111"/>
       <c r="CA10" s="111"/>
       <c r="CB10" s="111"/>
@@ -41187,16 +41097,6 @@
       <c r="BS11" s="110"/>
       <c r="BT11" s="110"/>
       <c r="BU11" s="110"/>
-      <c r="BV11" s="83" t="s">
-        <v>743</v>
-      </c>
-      <c r="BW11" s="84" t="s">
-        <v>1165</v>
-      </c>
-      <c r="BX11" s="83" t="s">
-        <v>743</v>
-      </c>
-      <c r="BY11" s="84"/>
       <c r="BZ11" s="111"/>
       <c r="CA11" s="111"/>
       <c r="CB11" s="111"/>
@@ -41557,16 +41457,6 @@
       <c r="BS12" s="110"/>
       <c r="BT12" s="110"/>
       <c r="BU12" s="110"/>
-      <c r="BV12" s="83" t="s">
-        <v>751</v>
-      </c>
-      <c r="BW12" s="84" t="s">
-        <v>1168</v>
-      </c>
-      <c r="BX12" s="83" t="s">
-        <v>751</v>
-      </c>
-      <c r="BY12" s="84"/>
       <c r="BZ12" s="111"/>
       <c r="CA12" s="111"/>
       <c r="CB12" s="111"/>
@@ -41927,16 +41817,6 @@
       <c r="BU13" s="110" t="s">
         <v>1174</v>
       </c>
-      <c r="BV13" s="129" t="s">
-        <v>938</v>
-      </c>
-      <c r="BW13" s="84" t="s">
-        <v>1172</v>
-      </c>
-      <c r="BX13" s="129" t="s">
-        <v>938</v>
-      </c>
-      <c r="BY13" s="84"/>
       <c r="BZ13" s="111"/>
       <c r="CA13" s="111"/>
       <c r="CB13" s="111"/>
@@ -42303,16 +42183,6 @@
       <c r="BS14" s="110"/>
       <c r="BT14" s="110"/>
       <c r="BU14" s="110"/>
-      <c r="BV14" s="83" t="s">
-        <v>739</v>
-      </c>
-      <c r="BW14" s="84" t="s">
-        <v>1176</v>
-      </c>
-      <c r="BX14" s="83" t="s">
-        <v>739</v>
-      </c>
-      <c r="BY14" s="84"/>
       <c r="BZ14" s="111"/>
       <c r="CA14" s="111"/>
       <c r="CB14" s="111"/>
@@ -42693,16 +42563,6 @@
       <c r="BS15" s="110"/>
       <c r="BT15" s="110"/>
       <c r="BU15" s="110"/>
-      <c r="BV15" s="83" t="s">
-        <v>759</v>
-      </c>
-      <c r="BW15" s="84" t="s">
-        <v>1183</v>
-      </c>
-      <c r="BX15" s="83" t="s">
-        <v>759</v>
-      </c>
-      <c r="BY15" s="84"/>
       <c r="BZ15" s="111"/>
       <c r="CA15" s="111"/>
       <c r="CB15" s="111"/>
@@ -43068,16 +42928,6 @@
       <c r="BS16" s="110"/>
       <c r="BT16" s="110"/>
       <c r="BU16" s="110"/>
-      <c r="BV16" s="83" t="s">
-        <v>741</v>
-      </c>
-      <c r="BW16" s="84" t="s">
-        <v>1187</v>
-      </c>
-      <c r="BX16" s="83" t="s">
-        <v>741</v>
-      </c>
-      <c r="BY16" s="84"/>
       <c r="BZ16" s="111"/>
       <c r="CA16" s="111"/>
       <c r="CB16" s="111"/>
@@ -43425,16 +43275,6 @@
       <c r="BU17" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="BV17" s="83" t="s">
-        <v>761</v>
-      </c>
-      <c r="BW17" s="84" t="s">
-        <v>1190</v>
-      </c>
-      <c r="BX17" s="83" t="s">
-        <v>761</v>
-      </c>
-      <c r="BY17" s="84"/>
       <c r="BZ17" s="111"/>
       <c r="CA17" s="111"/>
       <c r="CB17" s="111"/>
@@ -43800,16 +43640,6 @@
       <c r="BS18" s="110"/>
       <c r="BT18" s="110"/>
       <c r="BU18" s="110"/>
-      <c r="BV18" s="83" t="s">
-        <v>765</v>
-      </c>
-      <c r="BW18" s="84" t="s">
-        <v>1132</v>
-      </c>
-      <c r="BX18" s="83" t="s">
-        <v>765</v>
-      </c>
-      <c r="BY18" s="84"/>
       <c r="BZ18" s="111"/>
       <c r="CA18" s="111"/>
       <c r="CB18" s="111"/>
@@ -44201,16 +44031,6 @@
       <c r="BS19" s="110"/>
       <c r="BT19" s="110"/>
       <c r="BU19" s="110"/>
-      <c r="BV19" s="83" t="s">
-        <v>747</v>
-      </c>
-      <c r="BW19" s="84" t="s">
-        <v>1201</v>
-      </c>
-      <c r="BX19" s="83" t="s">
-        <v>747</v>
-      </c>
-      <c r="BY19" s="84"/>
       <c r="BZ19" s="111"/>
       <c r="CA19" s="111"/>
       <c r="CB19" s="111"/>
@@ -44576,16 +44396,6 @@
       <c r="BU20" s="124" t="s">
         <v>135</v>
       </c>
-      <c r="BV20" s="83" t="s">
-        <v>755</v>
-      </c>
-      <c r="BW20" s="84" t="s">
-        <v>1205</v>
-      </c>
-      <c r="BX20" s="83" t="s">
-        <v>755</v>
-      </c>
-      <c r="BY20" s="84"/>
       <c r="BZ20" s="111"/>
       <c r="CA20" s="111"/>
       <c r="CB20" s="111"/>
@@ -44959,16 +44769,6 @@
       <c r="BS21" s="110"/>
       <c r="BT21" s="110"/>
       <c r="BU21" s="110"/>
-      <c r="BV21" s="129" t="s">
-        <v>941</v>
-      </c>
-      <c r="BW21" s="84" t="s">
-        <v>1209</v>
-      </c>
-      <c r="BX21" s="129" t="s">
-        <v>941</v>
-      </c>
-      <c r="BY21" s="84"/>
       <c r="BZ21" s="111"/>
       <c r="CA21" s="111"/>
       <c r="CB21" s="111"/>
@@ -45334,16 +45134,6 @@
       <c r="BS22" s="110"/>
       <c r="BT22" s="110"/>
       <c r="BU22" s="110"/>
-      <c r="BV22" s="83" t="s">
-        <v>757</v>
-      </c>
-      <c r="BW22" s="84" t="s">
-        <v>1211</v>
-      </c>
-      <c r="BX22" s="83" t="s">
-        <v>757</v>
-      </c>
-      <c r="BY22" s="84"/>
       <c r="BZ22" s="111"/>
       <c r="CA22" s="111"/>
       <c r="CB22" s="111"/>
@@ -45711,16 +45501,6 @@
       <c r="BS23" s="110"/>
       <c r="BT23" s="110"/>
       <c r="BU23" s="110"/>
-      <c r="BV23" s="83" t="s">
-        <v>753</v>
-      </c>
-      <c r="BW23" s="84" t="s">
-        <v>1214</v>
-      </c>
-      <c r="BX23" s="83" t="s">
-        <v>753</v>
-      </c>
-      <c r="BY23" s="84"/>
       <c r="BZ23" s="111"/>
       <c r="CA23" s="111"/>
       <c r="CB23" s="111"/>
@@ -46079,16 +45859,6 @@
       <c r="BS24" s="110"/>
       <c r="BT24" s="110"/>
       <c r="BU24" s="110"/>
-      <c r="BV24" s="83" t="s">
-        <v>777</v>
-      </c>
-      <c r="BW24" s="84" t="s">
-        <v>1217</v>
-      </c>
-      <c r="BX24" s="83" t="s">
-        <v>777</v>
-      </c>
-      <c r="BY24" s="84"/>
       <c r="BZ24" s="111"/>
       <c r="CA24" s="111"/>
       <c r="CB24" s="111"/>
@@ -46481,16 +46251,6 @@
       <c r="BS25" s="110"/>
       <c r="BT25" s="110"/>
       <c r="BU25" s="110"/>
-      <c r="BV25" s="129" t="s">
-        <v>944</v>
-      </c>
-      <c r="BW25" s="84" t="s">
-        <v>1226</v>
-      </c>
-      <c r="BX25" s="129" t="s">
-        <v>944</v>
-      </c>
-      <c r="BY25" s="84"/>
       <c r="BZ25" s="111"/>
       <c r="CA25" s="111"/>
       <c r="CB25" s="111"/>
@@ -46851,16 +46611,6 @@
       <c r="BS26" s="110"/>
       <c r="BT26" s="110"/>
       <c r="BU26" s="110"/>
-      <c r="BV26" s="83" t="s">
-        <v>745</v>
-      </c>
-      <c r="BW26" s="84" t="s">
-        <v>1230</v>
-      </c>
-      <c r="BX26" s="83" t="s">
-        <v>745</v>
-      </c>
-      <c r="BY26" s="84"/>
       <c r="BZ26" s="111"/>
       <c r="CA26" s="111"/>
       <c r="CB26" s="111"/>
@@ -47252,20 +47002,6 @@
       <c r="BS27" s="110"/>
       <c r="BT27" s="110"/>
       <c r="BU27" s="110"/>
-      <c r="BV27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CJK_91CD</t>
-        </is>
-      </c>
-      <c r="BW27" s="84" t="s">
-        <v>1219</v>
-      </c>
-      <c r="BX27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CJK_91CD</t>
-        </is>
-      </c>
-      <c r="BY27" s="84"/>
       <c r="BZ27" s="111"/>
       <c r="CA27" s="111"/>
       <c r="CB27" s="111"/>
@@ -47735,16 +47471,6 @@
       <c r="BU28" s="110" t="s">
         <v>198</v>
       </c>
-      <c r="BV28" s="83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW28" s="84" t="s">
-        <v>1236</v>
-      </c>
-      <c r="BX28" s="83" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY28" s="84"/>
       <c r="BZ28" s="111" t="n">
         <v>1</v>
       </c>
@@ -48343,16 +48069,6 @@
       <c r="BU29" s="110" t="s">
         <v>1241</v>
       </c>
-      <c r="BV29" s="83" t="n">
-        <v>2</v>
-      </c>
-      <c r="BW29" s="131" t="s">
-        <v>86</v>
-      </c>
-      <c r="BX29" s="83" t="n">
-        <v>2</v>
-      </c>
-      <c r="BY29" s="84"/>
       <c r="BZ29" s="111" t="n">
         <v>2</v>
       </c>
@@ -48988,16 +48704,6 @@
       <c r="BU30" s="110" t="s">
         <v>1245</v>
       </c>
-      <c r="BV30" s="83" t="n">
-        <v>3</v>
-      </c>
-      <c r="BW30" s="131" t="s">
-        <v>785</v>
-      </c>
-      <c r="BX30" s="83" t="n">
-        <v>3</v>
-      </c>
-      <c r="BY30" s="84"/>
       <c r="BZ30" s="111" t="n">
         <v>3</v>
       </c>
@@ -49658,16 +49364,6 @@
       <c r="BU31" s="110" t="s">
         <v>190</v>
       </c>
-      <c r="BV31" s="84" t="n">
-        <v>4</v>
-      </c>
-      <c r="BW31" s="131" t="s">
-        <v>53</v>
-      </c>
-      <c r="BX31" s="84" t="n">
-        <v>4</v>
-      </c>
-      <c r="BY31" s="84"/>
       <c r="BZ31" s="132" t="s">
         <v>1252</v>
       </c>
@@ -50318,16 +50014,6 @@
       <c r="BU32" s="110" t="s">
         <v>194</v>
       </c>
-      <c r="BV32" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="BW32" s="131" t="s">
-        <v>787</v>
-      </c>
-      <c r="BX32" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="BY32" s="84"/>
       <c r="BZ32" s="132" t="s">
         <v>1259</v>
       </c>
@@ -50920,16 +50606,6 @@
       <c r="BU33" s="124" t="s">
         <v>196</v>
       </c>
-      <c r="BV33" s="84" t="n">
-        <v>6</v>
-      </c>
-      <c r="BW33" s="131" t="s">
-        <v>797</v>
-      </c>
-      <c r="BX33" s="84" t="n">
-        <v>6</v>
-      </c>
-      <c r="BY33" s="84"/>
       <c r="BZ33" s="111" t="n">
         <v>6</v>
       </c>
@@ -51569,16 +51245,6 @@
       <c r="BU34" s="110" t="s">
         <v>1268</v>
       </c>
-      <c r="BV34" s="84" t="n">
-        <v>7</v>
-      </c>
-      <c r="BW34" s="131" t="s">
-        <v>799</v>
-      </c>
-      <c r="BX34" s="84" t="n">
-        <v>7</v>
-      </c>
-      <c r="BY34" s="84"/>
       <c r="BZ34" s="111" t="n">
         <v>7</v>
       </c>
@@ -52205,16 +51871,6 @@
       <c r="BU35" s="124" t="s">
         <v>192</v>
       </c>
-      <c r="BV35" s="84" t="n">
-        <v>8</v>
-      </c>
-      <c r="BW35" s="84" t="s">
-        <v>1273</v>
-      </c>
-      <c r="BX35" s="84" t="n">
-        <v>8</v>
-      </c>
-      <c r="BY35" s="84"/>
       <c r="BZ35" s="111" t="n">
         <v>8</v>
       </c>
@@ -52830,16 +52486,6 @@
       <c r="BU36" s="124" t="s">
         <v>80</v>
       </c>
-      <c r="BV36" s="84" t="n">
-        <v>9</v>
-      </c>
-      <c r="BW36" s="84" t="s">
-        <v>1257</v>
-      </c>
-      <c r="BX36" s="84" t="n">
-        <v>9</v>
-      </c>
-      <c r="BY36" s="84"/>
       <c r="BZ36" s="111" t="n">
         <v>9</v>
       </c>
@@ -53453,16 +53099,6 @@
       <c r="BU37" s="124" t="s">
         <v>200</v>
       </c>
-      <c r="BV37" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW37" s="84" t="s">
-        <v>1276</v>
-      </c>
-      <c r="BX37" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY37" s="84"/>
       <c r="BZ37" s="111" t="s">
         <v>12</v>
       </c>
@@ -54000,10 +53636,6 @@
       <c r="BS38" s="110"/>
       <c r="BT38" s="110"/>
       <c r="BU38" s="110"/>
-      <c r="BV38" s="84"/>
-      <c r="BW38" s="84"/>
-      <c r="BX38" s="84"/>
-      <c r="BY38" s="84"/>
       <c r="BZ38" s="111"/>
       <c r="CA38" s="111"/>
       <c r="CB38" s="111"/>
@@ -54115,10 +53747,6 @@
       <c r="BS39" s="110"/>
       <c r="BT39" s="110"/>
       <c r="BU39" s="110"/>
-      <c r="BV39" s="84"/>
-      <c r="BW39" s="84"/>
-      <c r="BX39" s="84"/>
-      <c r="BY39" s="84"/>
       <c r="BZ39" s="111"/>
       <c r="CA39" s="111"/>
       <c r="CB39" s="111"/>
@@ -54230,10 +53858,6 @@
       <c r="BS40" s="110"/>
       <c r="BT40" s="110"/>
       <c r="BU40" s="110"/>
-      <c r="BV40" s="84"/>
-      <c r="BW40" s="84"/>
-      <c r="BX40" s="84"/>
-      <c r="BY40" s="84"/>
       <c r="BZ40" s="111"/>
       <c r="CA40" s="111"/>
       <c r="CB40" s="111"/>
@@ -54345,10 +53969,6 @@
       <c r="BS41" s="110"/>
       <c r="BT41" s="110"/>
       <c r="BU41" s="110"/>
-      <c r="BV41" s="84"/>
-      <c r="BW41" s="84"/>
-      <c r="BX41" s="84"/>
-      <c r="BY41" s="84"/>
       <c r="BZ41" s="111"/>
       <c r="CA41" s="111"/>
       <c r="CB41" s="111"/>
@@ -54460,10 +54080,6 @@
       <c r="BS42" s="110"/>
       <c r="BT42" s="110"/>
       <c r="BU42" s="110"/>
-      <c r="BV42" s="84"/>
-      <c r="BW42" s="84"/>
-      <c r="BX42" s="84"/>
-      <c r="BY42" s="84"/>
       <c r="BZ42" s="111"/>
       <c r="CA42" s="111"/>
       <c r="CB42" s="111"/>
@@ -54659,16 +54275,6 @@
       <c r="BU43" s="124" t="s">
         <v>1291</v>
       </c>
-      <c r="BV43" s="84" t="s">
-        <v>22</v>
-      </c>
-      <c r="BW43" s="131" t="s">
-        <v>793</v>
-      </c>
-      <c r="BX43" s="84" t="s">
-        <v>22</v>
-      </c>
-      <c r="BY43" s="84"/>
       <c r="BZ43" s="111" t="s">
         <v>1173</v>
       </c>
@@ -55293,16 +54899,6 @@
       <c r="BU44" s="110" t="s">
         <v>1294</v>
       </c>
-      <c r="BV44" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="BW44" s="84" t="s">
-        <v>795</v>
-      </c>
-      <c r="BX44" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="BY44" s="84"/>
       <c r="BZ44" s="125" t="s">
         <v>72</v>
       </c>
@@ -55900,16 +55496,6 @@
       <c r="BU45" s="110" t="s">
         <v>1302</v>
       </c>
-      <c r="BV45" s="84" t="s">
-        <v>1154</v>
-      </c>
-      <c r="BW45" s="84" t="s">
-        <v>801</v>
-      </c>
-      <c r="BX45" s="84" t="s">
-        <v>1154</v>
-      </c>
-      <c r="BY45" s="84"/>
       <c r="BZ45" s="125" t="s">
         <v>59</v>
       </c>
@@ -56496,16 +56082,6 @@
       <c r="BU46" s="110" t="s">
         <v>1310</v>
       </c>
-      <c r="BV46" s="84" t="s">
-        <v>1145</v>
-      </c>
-      <c r="BW46" s="84" t="s">
-        <v>803</v>
-      </c>
-      <c r="BX46" s="84" t="s">
-        <v>1145</v>
-      </c>
-      <c r="BY46" s="131"/>
       <c r="BZ46" s="111" t="s">
         <v>1272</v>
       </c>
@@ -57109,16 +56685,6 @@
       <c r="BU47" s="124" t="s">
         <v>1320</v>
       </c>
-      <c r="BV47" s="84" t="s">
-        <v>783</v>
-      </c>
-      <c r="BW47" s="84" t="s">
-        <v>739</v>
-      </c>
-      <c r="BX47" s="84" t="s">
-        <v>783</v>
-      </c>
-      <c r="BY47" s="131"/>
       <c r="BZ47" s="111" t="s">
         <v>1181</v>
       </c>
@@ -57552,16 +57118,6 @@
       <c r="BS48" s="110"/>
       <c r="BT48" s="110"/>
       <c r="BU48" s="110"/>
-      <c r="BV48" s="84" t="s">
-        <v>1228</v>
-      </c>
-      <c r="BW48" s="84" t="s">
-        <v>1234</v>
-      </c>
-      <c r="BX48" s="84" t="s">
-        <v>1228</v>
-      </c>
-      <c r="BY48" s="84"/>
       <c r="BZ48" s="111"/>
       <c r="CA48" s="111"/>
       <c r="CB48" s="111"/>
@@ -57993,16 +57549,6 @@
       <c r="BU49" s="110" t="s">
         <v>1326</v>
       </c>
-      <c r="BV49" s="84" t="s">
-        <v>1197</v>
-      </c>
-      <c r="BW49" s="84" t="s">
-        <v>1198</v>
-      </c>
-      <c r="BX49" s="84" t="s">
-        <v>1197</v>
-      </c>
-      <c r="BY49" s="84"/>
       <c r="BZ49" s="111" t="s">
         <v>1237</v>
       </c>
@@ -58567,16 +58113,6 @@
       <c r="BU50" s="110" t="s">
         <v>1336</v>
       </c>
-      <c r="BV50" s="84" t="s">
-        <v>1222</v>
-      </c>
-      <c r="BW50" s="84" t="s">
-        <v>8</v>
-      </c>
-      <c r="BX50" s="84" t="s">
-        <v>1222</v>
-      </c>
-      <c r="BY50" s="84"/>
       <c r="BZ50" s="111" t="s">
         <v>1268</v>
       </c>
@@ -59184,16 +58720,6 @@
       <c r="BU51" s="110" t="s">
         <v>1344</v>
       </c>
-      <c r="BV51" s="84" t="s">
-        <v>18</v>
-      </c>
-      <c r="BW51" s="84" t="s">
-        <v>1234</v>
-      </c>
-      <c r="BX51" s="84" t="s">
-        <v>18</v>
-      </c>
-      <c r="BY51" s="131"/>
       <c r="BZ51" s="111" t="s">
         <v>1195</v>
       </c>
@@ -59733,16 +59259,6 @@
       <c r="BU52" s="110" t="s">
         <v>1347</v>
       </c>
-      <c r="BV52" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="BW52" s="84" t="s">
-        <v>789</v>
-      </c>
-      <c r="BX52" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="BY52" s="84"/>
       <c r="BZ52" s="111" t="s">
         <v>1179</v>
       </c>
@@ -60203,14 +59719,6 @@
       <c r="BU53" s="110" t="s">
         <v>1349</v>
       </c>
-      <c r="BV53" s="84" t="s">
-        <v>784</v>
-      </c>
-      <c r="BW53" s="84" t="s">
-        <v>791</v>
-      </c>
-      <c r="BX53" s="84"/>
-      <c r="BY53" s="84"/>
       <c r="BZ53" s="111" t="s">
         <v>1267</v>
       </c>
@@ -60655,16 +60163,6 @@
         <v>1173</v>
       </c>
       <c r="BU54" s="110"/>
-      <c r="BV54" s="84" t="s">
-        <v>1173</v>
-      </c>
-      <c r="BW54" s="84" t="s">
-        <v>1180</v>
-      </c>
-      <c r="BX54" s="84" t="s">
-        <v>1173</v>
-      </c>
-      <c r="BY54" s="84"/>
       <c r="BZ54" s="111" t="s">
         <v>1262</v>
       </c>
@@ -61082,16 +60580,6 @@
         <v>16</v>
       </c>
       <c r="BU55" s="162"/>
-      <c r="BV55" s="131" t="s">
-        <v>783</v>
-      </c>
-      <c r="BW55" s="131" t="s">
-        <v>739</v>
-      </c>
-      <c r="BX55" s="131" t="s">
-        <v>783</v>
-      </c>
-      <c r="BY55" s="163"/>
       <c r="BZ55" s="164" t="s">
         <v>1145</v>
       </c>
@@ -61548,12 +61036,6 @@
       <c r="BU56" s="162" t="n">
         <v>48</v>
       </c>
-      <c r="BV56" s="163"/>
-      <c r="BW56" s="163" t="n">
-        <v>42</v>
-      </c>
-      <c r="BX56" s="163"/>
-      <c r="BY56" s="163"/>
       <c r="BZ56" s="164"/>
       <c r="CA56" s="164" t="s">
         <v>1354</v>
@@ -61981,12 +61463,6 @@
       <c r="BU57" s="162" t="n">
         <v>12</v>
       </c>
-      <c r="BV57" s="163"/>
-      <c r="BW57" s="163" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX57" s="163"/>
-      <c r="BY57" s="163"/>
       <c r="BZ57" s="164"/>
       <c r="CA57" s="164" t="s">
         <v>1354</v>
@@ -62423,12 +61899,6 @@
       <c r="BU58" s="162" t="n">
         <v>50</v>
       </c>
-      <c r="BV58" s="163"/>
-      <c r="BW58" s="163" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX58" s="163"/>
-      <c r="BY58" s="163"/>
       <c r="BZ58" s="164"/>
       <c r="CA58" s="164" t="n">
         <v>28</v>
@@ -62813,12 +62283,6 @@
       <c r="BU59" s="162" t="n">
         <v>12</v>
       </c>
-      <c r="BV59" s="163"/>
-      <c r="BW59" s="163" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX59" s="163"/>
-      <c r="BY59" s="163"/>
       <c r="BZ59" s="164"/>
       <c r="CA59" s="164" t="n">
         <v>0</v>
@@ -63209,12 +62673,6 @@
       <c r="BU60" s="162" t="n">
         <v>48</v>
       </c>
-      <c r="BV60" s="163"/>
-      <c r="BW60" s="163" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX60" s="163"/>
-      <c r="BY60" s="163"/>
       <c r="BZ60" s="164"/>
       <c r="CA60" s="164" t="n">
         <v>28</v>
@@ -63599,12 +63057,6 @@
       <c r="BU61" s="162" t="n">
         <v>12</v>
       </c>
-      <c r="BV61" s="163"/>
-      <c r="BW61" s="163" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX61" s="163"/>
-      <c r="BY61" s="163"/>
       <c r="BZ61" s="164"/>
       <c r="CA61" s="164" t="n">
         <v>0</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -47841,6 +47841,9 @@
           <t xml:space="preserve">ZHUYIN_3105</t>
         </is>
       </c>
+      <c r="GW28">
+        <v>1</v>
+      </c>
       <c r="HB28" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0586</t>
@@ -48452,6 +48455,9 @@
           <t xml:space="preserve">ZHUYIN_3109</t>
         </is>
       </c>
+      <c r="GW29">
+        <v>2</v>
+      </c>
       <c r="HB29" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0571</t>
@@ -49118,6 +49124,9 @@
           <t xml:space="preserve">ZHUYIN_02C7</t>
         </is>
       </c>
+      <c r="GW30">
+        <v>3</v>
+      </c>
       <c r="HB30" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_058A</t>
@@ -49768,6 +49777,9 @@
           <t xml:space="preserve">ZHUYIN_02CB</t>
         </is>
       </c>
+      <c r="GW31">
+        <v>4</v>
+      </c>
       <c r="HB31" t="inlineStr">
         <is>
           <t xml:space="preserve">COMMA</t>
@@ -50370,6 +50382,9 @@
           <t xml:space="preserve">ZHUYIN_3113</t>
         </is>
       </c>
+      <c r="GW32">
+        <v>5</v>
+      </c>
       <c r="HB32" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_0589</t>
@@ -50996,6 +51011,9 @@
           <t xml:space="preserve">ZHUYIN_02CA</t>
         </is>
       </c>
+      <c r="GW33">
+        <v>6</v>
+      </c>
       <c r="HB33" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_055E</t>
@@ -51621,6 +51639,9 @@
         <is>
           <t xml:space="preserve">ZHUYIN_02D9</t>
         </is>
+      </c>
+      <c r="GW34">
+        <v>7</v>
       </c>
       <c r="HB34" t="inlineStr">
         <is>
@@ -52248,6 +52269,9 @@
           <t xml:space="preserve">ZHUYIN_311A</t>
         </is>
       </c>
+      <c r="GW35">
+        <v>8</v>
+      </c>
       <c r="HB35" t="inlineStr">
         <is>
           <t xml:space="preserve">ARMENIAN_055B</t>
@@ -52861,6 +52885,9 @@
           <t xml:space="preserve">ZHUYIN_311E</t>
         </is>
       </c>
+      <c r="GW36">
+        <v>9</v>
+      </c>
       <c r="HB36" t="inlineStr">
         <is>
           <t xml:space="preserve">)</t>
@@ -53514,6 +53541,11 @@
       <c r="GV37" t="inlineStr">
         <is>
           <t xml:space="preserve">ZHUYIN_3122</t>
+        </is>
+      </c>
+      <c r="GW37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
         </is>
       </c>
       <c r="HB37" t="inlineStr">
@@ -61036,6 +61068,11 @@
       <c r="BU56" s="162" t="n">
         <v>48</v>
       </c>
+      <c r="BW56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
       <c r="BZ56" s="164"/>
       <c r="CA56" s="164" t="s">
         <v>1354</v>
@@ -61292,6 +61329,11 @@
       </c>
       <c r="HE56">
         <v>50</v>
+      </c>
+      <c r="HG56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
       </c>
       <c r="HK56" t="inlineStr">
         <is>
@@ -61463,6 +61505,11 @@
       <c r="BU57" s="162" t="n">
         <v>12</v>
       </c>
+      <c r="BW57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
       <c r="BZ57" s="164"/>
       <c r="CA57" s="164" t="s">
         <v>1354</v>
@@ -61728,6 +61775,11 @@
       </c>
       <c r="HE57">
         <v>12</v>
+      </c>
+      <c r="HG57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
       </c>
       <c r="HK57" t="inlineStr">
         <is>
@@ -61899,6 +61951,9 @@
       <c r="BU58" s="162" t="n">
         <v>50</v>
       </c>
+      <c r="BW58">
+        <v>35</v>
+      </c>
       <c r="BZ58" s="164"/>
       <c r="CA58" s="164" t="n">
         <v>28</v>
@@ -62118,6 +62173,9 @@
       </c>
       <c r="HE58">
         <v>50</v>
+      </c>
+      <c r="HG58">
+        <v>35</v>
       </c>
       <c r="HK58">
         <v>28</v>
@@ -62283,6 +62341,9 @@
       <c r="BU59" s="162" t="n">
         <v>12</v>
       </c>
+      <c r="BW59">
+        <v>0</v>
+      </c>
       <c r="BZ59" s="164"/>
       <c r="CA59" s="164" t="n">
         <v>0</v>
@@ -62508,6 +62569,9 @@
       </c>
       <c r="HE59">
         <v>12</v>
+      </c>
+      <c r="HG59">
+        <v>0</v>
       </c>
       <c r="HK59">
         <v>0</v>
@@ -62673,6 +62737,9 @@
       <c r="BU60" s="162" t="n">
         <v>48</v>
       </c>
+      <c r="BW60">
+        <v>35</v>
+      </c>
       <c r="BZ60" s="164"/>
       <c r="CA60" s="164" t="n">
         <v>28</v>
@@ -62892,6 +62959,9 @@
       </c>
       <c r="HE60">
         <v>50</v>
+      </c>
+      <c r="HG60">
+        <v>35</v>
       </c>
       <c r="HK60">
         <v>28</v>
@@ -63057,6 +63127,9 @@
       <c r="BU61" s="162" t="n">
         <v>12</v>
       </c>
+      <c r="BW61">
+        <v>0</v>
+      </c>
       <c r="BZ61" s="164"/>
       <c r="CA61" s="164" t="n">
         <v>0</v>
@@ -63282,6 +63355,9 @@
       </c>
       <c r="HE61">
         <v>12</v>
+      </c>
+      <c r="HG61">
+        <v>0</v>
       </c>
       <c r="HK61">
         <v>0</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -61746,6 +61746,9 @@
       <c r="GS57">
         <v>13</v>
       </c>
+      <c r="GT57">
+        <v>3</v>
+      </c>
       <c r="GU57" t="inlineStr">
         <is>
           <t xml:space="preserve">HIDE</t>
@@ -62549,6 +62552,9 @@
       <c r="GS59">
         <v>13</v>
       </c>
+      <c r="GT59">
+        <v>3</v>
+      </c>
       <c r="GU59">
         <v>0</v>
       </c>
@@ -63334,6 +63340,9 @@
       </c>
       <c r="GS61">
         <v>13</v>
+      </c>
+      <c r="GT61">
+        <v>3</v>
       </c>
       <c r="GU61">
         <v>0</v>

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -6068,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1564"/>
+  <dimension ref="A1:I1636"/>
   <sheetFormatPr defaultColWidth="12.5234375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.25"/>
@@ -37139,6 +37139,870 @@
       <c r="B1564" t="inlineStr">
         <is>
           <t xml:space="preserve">91CD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2BB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAIRA_SIGN</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1E62</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1E62</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1E63</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1E63</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1EB8</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EB8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1EB9</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1EB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1ECC</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ECC</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1ECD</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1ECD</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH_V</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">695</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_VEH</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_V</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_OE</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_V</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AE</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1200</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1208</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1208</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1210</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1210</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1218</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1218</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1220</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1228</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1230</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1238</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1240</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1240</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1250</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1260</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1268</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1270</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1270</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1278</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1278</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1280</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1290</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1290</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1298</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1298</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A0</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A1</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A2</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A4</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A4</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A6</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A8</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12B8</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12C8</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12D0</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12D0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12D8</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12E0</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12E0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12E8</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12F0</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12F0</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12F8</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1300</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1300</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1308</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1308</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1318</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1318</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1320</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1328</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1330</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1330</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1338</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1338</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1340</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1340</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1348</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1348</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1350</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1350</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1361</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1362</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1362</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1363</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1364</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1365</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1365</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1366</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1366</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1367</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1367</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1369</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1369</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136A</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136B</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136B</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136C</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136C</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136D</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136E</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136E</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136F</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136F</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1370</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1370</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1371</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_137B</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137B</t>
         </is>
       </c>
     </row>
@@ -37161,7 +38025,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:HY79"/>
+  <dimension ref="A1:LM79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="21.56"/>
@@ -37601,6 +38465,121 @@
       <c r="HY1">
         <v>3076</v>
       </c>
+      <c r="HZ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-AU</t>
+        </is>
+      </c>
+      <c r="ID1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-NZ</t>
+        </is>
+      </c>
+      <c r="IH1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mi-NZ</t>
+        </is>
+      </c>
+      <c r="IL1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sm-WS</t>
+        </is>
+      </c>
+      <c r="IP1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fj-FJ</t>
+        </is>
+      </c>
+      <c r="IT1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tl-PH</t>
+        </is>
+      </c>
+      <c r="IX1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hw-US</t>
+        </is>
+      </c>
+      <c r="JB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-ZA</t>
+        </is>
+      </c>
+      <c r="JF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">af-ZA</t>
+        </is>
+      </c>
+      <c r="JJ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar-EG</t>
+        </is>
+      </c>
+      <c r="JN1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sw-KE</t>
+        </is>
+      </c>
+      <c r="JR1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">am-ET</t>
+        </is>
+      </c>
+      <c r="JV1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yo-NG</t>
+        </is>
+      </c>
+      <c r="JZ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-NG</t>
+        </is>
+      </c>
+      <c r="KD1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar-MA</t>
+        </is>
+      </c>
+      <c r="KH1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar-IQ</t>
+        </is>
+      </c>
+      <c r="KL1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ku-IQ</t>
+        </is>
+      </c>
+      <c r="KP1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms-MY</t>
+        </is>
+      </c>
+      <c r="KT1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uz-UZ</t>
+        </is>
+      </c>
+      <c r="KX1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-CA</t>
+        </is>
+      </c>
+      <c r="LB1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">es-AR</t>
+        </is>
+      </c>
+      <c r="LF1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en-PG</t>
+        </is>
+      </c>
+      <c r="LJ1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ty-PF</t>
+        </is>
+      </c>
     </row>
     <row r="2" s="92" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -37976,6 +38955,106 @@
       <c r="HX2" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_SUN</t>
+        </is>
+      </c>
+      <c r="IK2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0101</t>
+        </is>
+      </c>
+      <c r="IO2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0101</t>
+        </is>
+      </c>
+      <c r="JA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0101</t>
+        </is>
+      </c>
+      <c r="JI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_A_SMALL</t>
+        </is>
+      </c>
+      <c r="JJ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="JK2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="JL2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="JR2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A0</t>
+        </is>
+      </c>
+      <c r="JT2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A0</t>
+        </is>
+      </c>
+      <c r="KD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="KE2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KF2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="KH2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="KI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KJ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="KL2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="KM2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MADDA_A</t>
+        </is>
+      </c>
+      <c r="KN2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="LJ2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="LK2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Q</t>
         </is>
       </c>
     </row>
@@ -38326,6 +39405,61 @@
           <t xml:space="preserve">KANGXI_RADICAL_MOON</t>
         </is>
       </c>
+      <c r="JJ3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF</t>
+        </is>
+      </c>
+      <c r="JK3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF_MADDA</t>
+        </is>
+      </c>
+      <c r="JR3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1260</t>
+        </is>
+      </c>
+      <c r="JT3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1260</t>
+        </is>
+      </c>
+      <c r="KD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF</t>
+        </is>
+      </c>
+      <c r="KE3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF_MADDA</t>
+        </is>
+      </c>
+      <c r="KH3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF</t>
+        </is>
+      </c>
+      <c r="KI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_ALEF_MADDA</t>
+        </is>
+      </c>
+      <c r="KL3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="KM3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="KN3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
     </row>
     <row r="4" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="93" t="s">
@@ -38705,6 +39839,76 @@
           <t xml:space="preserve">KANGXI_RADICAL_GOLD</t>
         </is>
       </c>
+      <c r="JJ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="JK4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRA</t>
+        </is>
+      </c>
+      <c r="JL4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="JR4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1278</t>
+        </is>
+      </c>
+      <c r="JT4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1278</t>
+        </is>
+      </c>
+      <c r="KD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KE4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRA</t>
+        </is>
+      </c>
+      <c r="KF4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KH4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRA</t>
+        </is>
+      </c>
+      <c r="KJ4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KL4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KM4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TCHEH</t>
+        </is>
+      </c>
+      <c r="KN4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
     </row>
     <row r="5" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
@@ -39069,6 +40273,81 @@
           <t xml:space="preserve">KANGXI_RADICAL_TREE</t>
         </is>
       </c>
+      <c r="JJ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="JK5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="JL5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="JR5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12F0</t>
+        </is>
+      </c>
+      <c r="JS5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12F8</t>
+        </is>
+      </c>
+      <c r="JT5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12F0</t>
+        </is>
+      </c>
+      <c r="KD5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="KE5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="KF5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="KH5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="KI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="KJ5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH</t>
+        </is>
+      </c>
+      <c r="KL5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KM5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="KN5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
     </row>
     <row r="6" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="93" t="s">
@@ -39534,6 +40813,101 @@
       <c r="HX6" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_WATER</t>
+        </is>
+      </c>
+      <c r="IK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0113</t>
+        </is>
+      </c>
+      <c r="IO6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0113</t>
+        </is>
+      </c>
+      <c r="JA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0113</t>
+        </is>
+      </c>
+      <c r="JI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00EB</t>
+        </is>
+      </c>
+      <c r="JJ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="JK6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMA</t>
+        </is>
+      </c>
+      <c r="JL6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="JR6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A4</t>
+        </is>
+      </c>
+      <c r="JT6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A4</t>
+        </is>
+      </c>
+      <c r="KD6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="KE6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMA</t>
+        </is>
+      </c>
+      <c r="KF6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="KH6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="KI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMA</t>
+        </is>
+      </c>
+      <c r="KJ6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="KL6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AE</t>
+        </is>
+      </c>
+      <c r="KM6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KN6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AE</t>
+        </is>
+      </c>
+      <c r="LM6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
         </is>
       </c>
     </row>
@@ -39899,6 +41273,76 @@
           <t xml:space="preserve">KANGXI_RADICAL_FIRE</t>
         </is>
       </c>
+      <c r="JJ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="JK7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="JL7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="JR7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1348</t>
+        </is>
+      </c>
+      <c r="JT7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1348</t>
+        </is>
+      </c>
+      <c r="KD7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="KE7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="KF7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="KH7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="KI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="KJ7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_BEH</t>
+        </is>
+      </c>
+      <c r="KL7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="KM7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_B</t>
+        </is>
+      </c>
+      <c r="KN7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
     </row>
     <row r="8" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="93" t="s">
@@ -40265,6 +41709,51 @@
           <t xml:space="preserve">KANGXI_RADICAL_EARTH</t>
         </is>
       </c>
+      <c r="JJ8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="JR8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1308</t>
+        </is>
+      </c>
+      <c r="JS8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1318</t>
+        </is>
+      </c>
+      <c r="JT8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1308</t>
+        </is>
+      </c>
+      <c r="KD8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="KH8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="KL8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
+      <c r="KM8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="KN8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GAF</t>
+        </is>
+      </c>
     </row>
     <row r="9" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
@@ -40616,6 +42105,76 @@
           <t xml:space="preserve">KANGXI_RADICAL_BAMBOO</t>
         </is>
       </c>
+      <c r="JJ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="JK9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="JL9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="JR9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1200</t>
+        </is>
+      </c>
+      <c r="JS9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1210</t>
+        </is>
+      </c>
+      <c r="JT9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1200</t>
+        </is>
+      </c>
+      <c r="KD9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="KE9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KF9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="KH9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="KI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KJ9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF</t>
+        </is>
+      </c>
+      <c r="KL9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KN9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
     </row>
     <row r="10" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="93" t="s">
@@ -40980,6 +42539,96 @@
       <c r="HX10" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_HALBERD</t>
+        </is>
+      </c>
+      <c r="IK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012B</t>
+        </is>
+      </c>
+      <c r="IO10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012B</t>
+        </is>
+      </c>
+      <c r="JA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_012B</t>
+        </is>
+      </c>
+      <c r="JI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00EF</t>
+        </is>
+      </c>
+      <c r="JJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="JK10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVISION_SIGN</t>
+        </is>
+      </c>
+      <c r="JL10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="JR10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A2</t>
+        </is>
+      </c>
+      <c r="JT10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A2</t>
+        </is>
+      </c>
+      <c r="KD10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KE10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVISION_SIGN</t>
+        </is>
+      </c>
+      <c r="KF10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KH10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVISION_SIGN</t>
+        </is>
+      </c>
+      <c r="KJ10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HEH</t>
+        </is>
+      </c>
+      <c r="KL10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="KM10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="KN10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
         </is>
       </c>
     </row>
@@ -41342,6 +42991,76 @@
           <t xml:space="preserve">KANGXI_RADICAL_TEN</t>
         </is>
       </c>
+      <c r="JJ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="JK11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="JL11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="JR11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1300</t>
+        </is>
+      </c>
+      <c r="JT11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1300</t>
+        </is>
+      </c>
+      <c r="KD11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="KE11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="KF11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="KH11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="KI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="KJ11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="KL11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEH</t>
+        </is>
+      </c>
+      <c r="KM11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KN11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEH</t>
+        </is>
+      </c>
     </row>
     <row r="12" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="93" t="s">
@@ -41700,6 +43419,81 @@
           <t xml:space="preserve">KANGXI_RADICAL_BIG</t>
         </is>
       </c>
+      <c r="JJ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="JK12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="JL12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="JR12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A8</t>
+        </is>
+      </c>
+      <c r="JS12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12B8</t>
+        </is>
+      </c>
+      <c r="JT12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A8</t>
+        </is>
+      </c>
+      <c r="KD12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="KE12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="KF12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="KH12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="KI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="KJ12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="KL12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
+      <c r="KM12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="KN12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KEHEH</t>
+        </is>
+      </c>
     </row>
     <row r="13" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
@@ -42060,6 +43854,76 @@
           <t xml:space="preserve">CJK_4E2D</t>
         </is>
       </c>
+      <c r="JJ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="JK13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="JL13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="JR13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1208</t>
+        </is>
+      </c>
+      <c r="JT13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1208</t>
+        </is>
+      </c>
+      <c r="KD13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="KE13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="KF13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="KH13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="KI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="KJ13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="KL13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
+      <c r="KM13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM_V</t>
+        </is>
+      </c>
+      <c r="KN13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_LAM</t>
+        </is>
+      </c>
     </row>
     <row r="14" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="93" t="s">
@@ -42444,6 +44308,86 @@
       <c r="HX14" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_ONE</t>
+        </is>
+      </c>
+      <c r="JJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="JK14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="JL14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="JR14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1218</t>
+        </is>
+      </c>
+      <c r="JT14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1218</t>
+        </is>
+      </c>
+      <c r="KD14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KE14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="KF14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KH14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="KJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KL14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="KM14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="KN14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_MEEM</t>
+        </is>
+      </c>
+      <c r="LJ14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">,</t>
+        </is>
+      </c>
+      <c r="LK14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
         </is>
       </c>
     </row>
@@ -42811,6 +44755,81 @@
           <t xml:space="preserve">KANGXI_RADICAL_BOW</t>
         </is>
       </c>
+      <c r="JJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="JK15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MADDA_A</t>
+        </is>
+      </c>
+      <c r="JL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="JR15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1290</t>
+        </is>
+      </c>
+      <c r="JS15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1298</t>
+        </is>
+      </c>
+      <c r="JT15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1290</t>
+        </is>
+      </c>
+      <c r="KD15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="KE15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MADDA_A</t>
+        </is>
+      </c>
+      <c r="KF15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="KH15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="KI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MADDA_A</t>
+        </is>
+      </c>
+      <c r="KJ15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_MAKSURA</t>
+        </is>
+      </c>
+      <c r="KL15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
+      <c r="KM15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="KN15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_NOON</t>
+        </is>
+      </c>
     </row>
     <row r="16" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="93" t="s">
@@ -43156,6 +45175,96 @@
           <t xml:space="preserve">KANGXI_RADICAL_MAN</t>
         </is>
       </c>
+      <c r="IK16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_014D</t>
+        </is>
+      </c>
+      <c r="IO16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_014D</t>
+        </is>
+      </c>
+      <c r="JA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_014D</t>
+        </is>
+      </c>
+      <c r="JI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_O_SMALL</t>
+        </is>
+      </c>
+      <c r="JJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="JK16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUL_SIGN</t>
+        </is>
+      </c>
+      <c r="JL16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="JR16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A6</t>
+        </is>
+      </c>
+      <c r="JT16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A6</t>
+        </is>
+      </c>
+      <c r="KD16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="KE16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUL_SIGN</t>
+        </is>
+      </c>
+      <c r="KF16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="KH16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="KI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUL_SIGN</t>
+        </is>
+      </c>
+      <c r="KJ16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH_MARBUTA</t>
+        </is>
+      </c>
+      <c r="KL16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_OE</t>
+        </is>
+      </c>
+      <c r="KM16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KN16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_OE</t>
+        </is>
+      </c>
     </row>
     <row r="17" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
@@ -43511,6 +45620,86 @@
           <t xml:space="preserve">KANGXI_RADICAL_HEART</t>
         </is>
       </c>
+      <c r="JI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00F4</t>
+        </is>
+      </c>
+      <c r="JJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="JK17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="JL17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="JR17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1350</t>
+        </is>
+      </c>
+      <c r="JS17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1330</t>
+        </is>
+      </c>
+      <c r="JT17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1350</t>
+        </is>
+      </c>
+      <c r="KD17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="KE17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="KF17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="KH17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="KI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="KJ17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAH</t>
+        </is>
+      </c>
+      <c r="KL17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
+      <c r="KM17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THEH</t>
+        </is>
+      </c>
+      <c r="KN17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_PEH</t>
+        </is>
+      </c>
     </row>
     <row r="18" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="93" t="s">
@@ -43908,6 +46097,101 @@
       <c r="HX18" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_HAND</t>
+        </is>
+      </c>
+      <c r="JJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="JK18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHA</t>
+        </is>
+      </c>
+      <c r="JL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="JR18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1240</t>
+        </is>
+      </c>
+      <c r="JS18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1250</t>
+        </is>
+      </c>
+      <c r="JT18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1240</t>
+        </is>
+      </c>
+      <c r="JV18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1EB9</t>
+        </is>
+      </c>
+      <c r="JW18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1EB8</t>
+        </is>
+      </c>
+      <c r="JY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q</t>
+        </is>
+      </c>
+      <c r="KD18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="KE18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHA</t>
+        </is>
+      </c>
+      <c r="KF18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="KH18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="KI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHA</t>
+        </is>
+      </c>
+      <c r="KJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="KL18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="KN18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="LJ18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a</t>
+        </is>
+      </c>
+      <c r="LK18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
     </row>
@@ -44279,6 +46563,96 @@
           <t xml:space="preserve">KANGXI_RADICAL_MOUTH</t>
         </is>
       </c>
+      <c r="JI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00EA</t>
+        </is>
+      </c>
+      <c r="JJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="JK19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMATAN</t>
+        </is>
+      </c>
+      <c r="JL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="JM19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
+      <c r="JR19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1228</t>
+        </is>
+      </c>
+      <c r="JT19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1228</t>
+        </is>
+      </c>
+      <c r="KD19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="KE19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMATAN</t>
+        </is>
+      </c>
+      <c r="KF19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="KG19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
+      <c r="KH19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="KI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_DAMMATAN</t>
+        </is>
+      </c>
+      <c r="KJ19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QAF</t>
+        </is>
+      </c>
+      <c r="KK19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
+      <c r="KL19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="KM19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH_V</t>
+        </is>
+      </c>
+      <c r="KN19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
     </row>
     <row r="20" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="93" t="s">
@@ -44654,6 +47028,56 @@
       <c r="HX20" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_CORPSE</t>
+        </is>
+      </c>
+      <c r="JI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_0161</t>
+        </is>
+      </c>
+      <c r="JJ20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="JR20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1230</t>
+        </is>
+      </c>
+      <c r="JS20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1220</t>
+        </is>
+      </c>
+      <c r="JT20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1230</t>
+        </is>
+      </c>
+      <c r="KD20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="KH20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="KL20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
+        </is>
+      </c>
+      <c r="KM20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SHEEN</t>
+        </is>
+      </c>
+      <c r="KN20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEEN</t>
         </is>
       </c>
     </row>
@@ -45015,6 +47439,51 @@
           <t xml:space="preserve">CJK_5EFF</t>
         </is>
       </c>
+      <c r="JJ21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="JR21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1270</t>
+        </is>
+      </c>
+      <c r="JS21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1320</t>
+        </is>
+      </c>
+      <c r="JT21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1270</t>
+        </is>
+      </c>
+      <c r="KD21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="KH21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FEH</t>
+        </is>
+      </c>
+      <c r="KL21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
+      <c r="KM21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="KN21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TEH</t>
+        </is>
+      </c>
     </row>
     <row r="22" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="93" t="s">
@@ -45384,6 +47853,96 @@
           <t xml:space="preserve">KANGXI_RADICAL_MOUNTAIN</t>
         </is>
       </c>
+      <c r="IK22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016B</t>
+        </is>
+      </c>
+      <c r="IO22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016B</t>
+        </is>
+      </c>
+      <c r="JA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_016B</t>
+        </is>
+      </c>
+      <c r="JI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMLAUT_U_SMALL</t>
+        </is>
+      </c>
+      <c r="JJ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="JK22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="JL22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="JR22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A1</t>
+        </is>
+      </c>
+      <c r="JT22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A1</t>
+        </is>
+      </c>
+      <c r="KD22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="KE22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="KF22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="KH22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="KI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="KJ22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_AIN</t>
+        </is>
+      </c>
+      <c r="KL22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KM22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="KN22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
     </row>
     <row r="23" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="93" t="s">
@@ -45734,6 +48293,96 @@
           <t xml:space="preserve">KANGXI_RADICAL_WOMAN</t>
         </is>
       </c>
+      <c r="JJ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="JK23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRATAN</t>
+        </is>
+      </c>
+      <c r="JL23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="JR23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1238</t>
+        </is>
+      </c>
+      <c r="JS23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1268</t>
+        </is>
+      </c>
+      <c r="JT23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1238</t>
+        </is>
+      </c>
+      <c r="JV23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1E63</t>
+        </is>
+      </c>
+      <c r="JW23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1E62</t>
+        </is>
+      </c>
+      <c r="JY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v</t>
+        </is>
+      </c>
+      <c r="KD23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="KE23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRATAN</t>
+        </is>
+      </c>
+      <c r="KF23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="KH23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="KI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KASRATAN</t>
+        </is>
+      </c>
+      <c r="KJ23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_REH</t>
+        </is>
+      </c>
+      <c r="KL23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_VEH</t>
+        </is>
+      </c>
+      <c r="KM23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="KN23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_VEH</t>
+        </is>
+      </c>
     </row>
     <row r="24" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="93" t="s">
@@ -46134,6 +48783,81 @@
       <c r="HX24" t="inlineStr">
         <is>
           <t xml:space="preserve">KANGXI_RADICAL_FIELD</t>
+        </is>
+      </c>
+      <c r="JJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="JK24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHATAN</t>
+        </is>
+      </c>
+      <c r="JL24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="JR24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12C8</t>
+        </is>
+      </c>
+      <c r="JT24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12C8</t>
+        </is>
+      </c>
+      <c r="KD24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="KE24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHATAN</t>
+        </is>
+      </c>
+      <c r="KF24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="KH24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="KI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_FATHATAN</t>
+        </is>
+      </c>
+      <c r="KJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="KL24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KN24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="LJ24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z</t>
+        </is>
+      </c>
+      <c r="LK24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
         </is>
       </c>
     </row>
@@ -46486,6 +49210,96 @@
           <t xml:space="preserve">CJK_96E3</t>
         </is>
       </c>
+      <c r="JJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="JK25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SUKUN</t>
+        </is>
+      </c>
+      <c r="JL25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="JR25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A0</t>
+        </is>
+      </c>
+      <c r="JS25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12D0</t>
+        </is>
+      </c>
+      <c r="JT25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12A0</t>
+        </is>
+      </c>
+      <c r="JV25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1ECD</t>
+        </is>
+      </c>
+      <c r="JW25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_1ECC</t>
+        </is>
+      </c>
+      <c r="JY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+      <c r="KD25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="KE25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SUKUN</t>
+        </is>
+      </c>
+      <c r="KF25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="KH25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="KI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SUKUN</t>
+        </is>
+      </c>
+      <c r="KJ25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_HAMZA</t>
+        </is>
+      </c>
+      <c r="KL25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KHAH</t>
+        </is>
+      </c>
+      <c r="KM25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SAD</t>
+        </is>
+      </c>
+      <c r="KN25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KHAH</t>
+        </is>
+      </c>
     </row>
     <row r="26" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="93" t="s">
@@ -46875,6 +49689,81 @@
           <t xml:space="preserve">KANGXI_RADICAL_DIVINATION</t>
         </is>
       </c>
+      <c r="JI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LATIN_00FB</t>
+        </is>
+      </c>
+      <c r="JJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="JK26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_B</t>
+        </is>
+      </c>
+      <c r="JL26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="JR26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12E8</t>
+        </is>
+      </c>
+      <c r="JT26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12E8</t>
+        </is>
+      </c>
+      <c r="KD26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="KE26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_B</t>
+        </is>
+      </c>
+      <c r="KF26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="KH26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="KI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ALEF_HAMZA_B</t>
+        </is>
+      </c>
+      <c r="KJ26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_GHAIN</t>
+        </is>
+      </c>
+      <c r="KL26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
+      <c r="KM26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_V</t>
+        </is>
+      </c>
+      <c r="KN26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_FARSI_YEH</t>
+        </is>
+      </c>
     </row>
     <row r="27" s="116" customFormat="true" ht="15.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="93" t="s">
@@ -47288,6 +50177,91 @@
           <t xml:space="preserve">CJK_91CD</t>
         </is>
       </c>
+      <c r="JJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="JK27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="JL27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="JR27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12D8</t>
+        </is>
+      </c>
+      <c r="JS27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12E0</t>
+        </is>
+      </c>
+      <c r="JT27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_12D8</t>
+        </is>
+      </c>
+      <c r="KD27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KE27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="KF27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KH27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="KJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_YEH_HAMZA_A</t>
+        </is>
+      </c>
+      <c r="KL27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="KM27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAD</t>
+        </is>
+      </c>
+      <c r="KN27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="LJ27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">w</t>
+        </is>
+      </c>
+      <c r="LK27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">W</t>
+        </is>
+      </c>
     </row>
     <row r="28" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="93" t="s">
@@ -47879,6 +50853,110 @@
         </is>
       </c>
       <c r="HX28">
+        <v>1</v>
+      </c>
+      <c r="JJ28">
+        <v>1</v>
+      </c>
+      <c r="JK28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="JL28">
+        <v>1</v>
+      </c>
+      <c r="JM28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_1</t>
+        </is>
+      </c>
+      <c r="JR28">
+        <v>1</v>
+      </c>
+      <c r="JS28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="JT28">
+        <v>1</v>
+      </c>
+      <c r="JU28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1369</t>
+        </is>
+      </c>
+      <c r="KD28">
+        <v>1</v>
+      </c>
+      <c r="KE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="KF28">
+        <v>1</v>
+      </c>
+      <c r="KG28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_1</t>
+        </is>
+      </c>
+      <c r="KH28">
+        <v>1</v>
+      </c>
+      <c r="KI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="KJ28">
+        <v>1</v>
+      </c>
+      <c r="KK28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_1</t>
+        </is>
+      </c>
+      <c r="KL28">
+        <v>1</v>
+      </c>
+      <c r="KM28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="KN28">
+        <v>1</v>
+      </c>
+      <c r="KO28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_1</t>
+        </is>
+      </c>
+      <c r="LB28">
+        <v>1</v>
+      </c>
+      <c r="LC28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="LD28">
+        <v>1</v>
+      </c>
+      <c r="LE28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="LJ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="LK28">
         <v>1</v>
       </c>
     </row>
@@ -48517,6 +51595,104 @@
       <c r="HX29">
         <v>2</v>
       </c>
+      <c r="JI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YEN_SIGN</t>
+        </is>
+      </c>
+      <c r="JJ29">
+        <v>2</v>
+      </c>
+      <c r="JK29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="JL29">
+        <v>2</v>
+      </c>
+      <c r="JM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_2</t>
+        </is>
+      </c>
+      <c r="JR29">
+        <v>2</v>
+      </c>
+      <c r="JS29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="JT29">
+        <v>2</v>
+      </c>
+      <c r="JU29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136A</t>
+        </is>
+      </c>
+      <c r="KD29">
+        <v>2</v>
+      </c>
+      <c r="KE29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="KF29">
+        <v>2</v>
+      </c>
+      <c r="KG29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_2</t>
+        </is>
+      </c>
+      <c r="KH29">
+        <v>2</v>
+      </c>
+      <c r="KI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="KJ29">
+        <v>2</v>
+      </c>
+      <c r="KK29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_2</t>
+        </is>
+      </c>
+      <c r="KL29">
+        <v>2</v>
+      </c>
+      <c r="KM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
+      </c>
+      <c r="KN29">
+        <v>2</v>
+      </c>
+      <c r="KO29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_2</t>
+        </is>
+      </c>
+      <c r="LJ29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\f\f" E_WITH_ACUTE_SMALL</t>
+        </is>
+      </c>
+      <c r="LK29">
+        <v>2</v>
+      </c>
+      <c r="LM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
     </row>
     <row r="30" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="93" t="s">
@@ -49180,6 +52356,120 @@
       <c r="HX30">
         <v>3</v>
       </c>
+      <c r="JI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="JJ30">
+        <v>3</v>
+      </c>
+      <c r="JK30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="JL30">
+        <v>3</v>
+      </c>
+      <c r="JM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_3</t>
+        </is>
+      </c>
+      <c r="JR30">
+        <v>3</v>
+      </c>
+      <c r="JS30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="JT30">
+        <v>3</v>
+      </c>
+      <c r="JU30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136B</t>
+        </is>
+      </c>
+      <c r="KD30">
+        <v>3</v>
+      </c>
+      <c r="KE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="KF30">
+        <v>3</v>
+      </c>
+      <c r="KG30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_3</t>
+        </is>
+      </c>
+      <c r="KH30">
+        <v>3</v>
+      </c>
+      <c r="KI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="KJ30">
+        <v>3</v>
+      </c>
+      <c r="KK30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_3</t>
+        </is>
+      </c>
+      <c r="KL30">
+        <v>3</v>
+      </c>
+      <c r="KM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="KN30">
+        <v>3</v>
+      </c>
+      <c r="KO30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_3</t>
+        </is>
+      </c>
+      <c r="LB30">
+        <v>3</v>
+      </c>
+      <c r="LC30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="LD30">
+        <v>3</v>
+      </c>
+      <c r="LE30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDDLE_DOT</t>
+        </is>
+      </c>
+      <c r="LJ30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="LK30">
+        <v>3</v>
+      </c>
+      <c r="LM30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
     </row>
     <row r="31" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="93" t="s">
@@ -49833,6 +53123,135 @@
       <c r="HX31">
         <v>4</v>
       </c>
+      <c r="JJ31">
+        <v>4</v>
+      </c>
+      <c r="JK31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="JL31">
+        <v>4</v>
+      </c>
+      <c r="JM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_4</t>
+        </is>
+      </c>
+      <c r="JR31">
+        <v>4</v>
+      </c>
+      <c r="JS31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="JT31">
+        <v>4</v>
+      </c>
+      <c r="JU31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136C</t>
+        </is>
+      </c>
+      <c r="JW31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAIRA_SIGN</t>
+        </is>
+      </c>
+      <c r="JY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="KA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAIRA_SIGN</t>
+        </is>
+      </c>
+      <c r="KC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="KD31">
+        <v>4</v>
+      </c>
+      <c r="KE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="KF31">
+        <v>4</v>
+      </c>
+      <c r="KG31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_4</t>
+        </is>
+      </c>
+      <c r="KH31">
+        <v>4</v>
+      </c>
+      <c r="KI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="KJ31">
+        <v>4</v>
+      </c>
+      <c r="KK31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_4</t>
+        </is>
+      </c>
+      <c r="KL31">
+        <v>4</v>
+      </c>
+      <c r="KM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="KN31">
+        <v>4</v>
+      </c>
+      <c r="KO31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_4</t>
+        </is>
+      </c>
+      <c r="LB31">
+        <v>4</v>
+      </c>
+      <c r="LC31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="LD31">
+        <v>4</v>
+      </c>
+      <c r="LE31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="LJ31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="LK31">
+        <v>4</v>
+      </c>
+      <c r="LM31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
     </row>
     <row r="32" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="93" t="s">
@@ -50432,6 +53851,104 @@
       <c r="HX32">
         <v>5</v>
       </c>
+      <c r="JI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EURO_SIGN</t>
+        </is>
+      </c>
+      <c r="JJ32">
+        <v>5</v>
+      </c>
+      <c r="JK32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="JL32">
+        <v>5</v>
+      </c>
+      <c r="JM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_5</t>
+        </is>
+      </c>
+      <c r="JR32">
+        <v>5</v>
+      </c>
+      <c r="JS32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="JT32">
+        <v>5</v>
+      </c>
+      <c r="JU32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136D</t>
+        </is>
+      </c>
+      <c r="KD32">
+        <v>5</v>
+      </c>
+      <c r="KE32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="KF32">
+        <v>5</v>
+      </c>
+      <c r="KG32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_5</t>
+        </is>
+      </c>
+      <c r="KH32">
+        <v>5</v>
+      </c>
+      <c r="KI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="KJ32">
+        <v>5</v>
+      </c>
+      <c r="KK32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_5</t>
+        </is>
+      </c>
+      <c r="KL32">
+        <v>5</v>
+      </c>
+      <c r="KM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="KN32">
+        <v>5</v>
+      </c>
+      <c r="KO32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_5</t>
+        </is>
+      </c>
+      <c r="LJ32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="LK32">
+        <v>5</v>
+      </c>
+      <c r="LM32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
     </row>
     <row r="33" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="93" t="s">
@@ -51072,6 +54589,120 @@
       <c r="HX33">
         <v>6</v>
       </c>
+      <c r="JI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="JJ33">
+        <v>6</v>
+      </c>
+      <c r="JK33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="JL33">
+        <v>6</v>
+      </c>
+      <c r="JM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_6</t>
+        </is>
+      </c>
+      <c r="JR33">
+        <v>6</v>
+      </c>
+      <c r="JS33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="JT33">
+        <v>6</v>
+      </c>
+      <c r="JU33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136E</t>
+        </is>
+      </c>
+      <c r="KD33">
+        <v>6</v>
+      </c>
+      <c r="KE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="KF33">
+        <v>6</v>
+      </c>
+      <c r="KG33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_6</t>
+        </is>
+      </c>
+      <c r="KH33">
+        <v>6</v>
+      </c>
+      <c r="KI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="KJ33">
+        <v>6</v>
+      </c>
+      <c r="KK33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_6</t>
+        </is>
+      </c>
+      <c r="KL33">
+        <v>6</v>
+      </c>
+      <c r="KM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="KN33">
+        <v>6</v>
+      </c>
+      <c r="KO33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_6</t>
+        </is>
+      </c>
+      <c r="LB33">
+        <v>6</v>
+      </c>
+      <c r="LC33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="LD33">
+        <v>6</v>
+      </c>
+      <c r="LE33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="LJ33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="LK33">
+        <v>6</v>
+      </c>
+      <c r="LM33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
     </row>
     <row r="34" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="93" t="s">
@@ -51700,6 +55331,99 @@
       </c>
       <c r="HX34">
         <v>7</v>
+      </c>
+      <c r="JJ34">
+        <v>7</v>
+      </c>
+      <c r="JK34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="JL34">
+        <v>7</v>
+      </c>
+      <c r="JM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_7</t>
+        </is>
+      </c>
+      <c r="JR34">
+        <v>7</v>
+      </c>
+      <c r="JS34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="JT34">
+        <v>7</v>
+      </c>
+      <c r="JU34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_136F</t>
+        </is>
+      </c>
+      <c r="KD34">
+        <v>7</v>
+      </c>
+      <c r="KE34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="KF34">
+        <v>7</v>
+      </c>
+      <c r="KG34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_7</t>
+        </is>
+      </c>
+      <c r="KH34">
+        <v>7</v>
+      </c>
+      <c r="KI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="KJ34">
+        <v>7</v>
+      </c>
+      <c r="KK34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_7</t>
+        </is>
+      </c>
+      <c r="KL34">
+        <v>7</v>
+      </c>
+      <c r="KM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&amp;</t>
+        </is>
+      </c>
+      <c r="KN34">
+        <v>7</v>
+      </c>
+      <c r="KO34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_7</t>
+        </is>
+      </c>
+      <c r="LJ34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\f\f" E_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="LK34">
+        <v>7</v>
+      </c>
+      <c r="LM34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
       </c>
     </row>
     <row r="35" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52319,6 +56043,99 @@
       <c r="HX35">
         <v>8</v>
       </c>
+      <c r="JJ35">
+        <v>8</v>
+      </c>
+      <c r="JK35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="JL35">
+        <v>8</v>
+      </c>
+      <c r="JM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_8</t>
+        </is>
+      </c>
+      <c r="JR35">
+        <v>8</v>
+      </c>
+      <c r="JS35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="JT35">
+        <v>8</v>
+      </c>
+      <c r="JU35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1370</t>
+        </is>
+      </c>
+      <c r="KD35">
+        <v>8</v>
+      </c>
+      <c r="KE35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="KF35">
+        <v>8</v>
+      </c>
+      <c r="KG35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_8</t>
+        </is>
+      </c>
+      <c r="KH35">
+        <v>8</v>
+      </c>
+      <c r="KI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="KJ35">
+        <v>8</v>
+      </c>
+      <c r="KK35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_8</t>
+        </is>
+      </c>
+      <c r="KL35">
+        <v>8</v>
+      </c>
+      <c r="KM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="KN35">
+        <v>8</v>
+      </c>
+      <c r="KO35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_8</t>
+        </is>
+      </c>
+      <c r="LJ35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">_</t>
+        </is>
+      </c>
+      <c r="LK35">
+        <v>8</v>
+      </c>
+      <c r="LM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
     </row>
     <row r="36" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="93" t="s">
@@ -52935,6 +56752,99 @@
       <c r="HX36">
         <v>9</v>
       </c>
+      <c r="JJ36">
+        <v>9</v>
+      </c>
+      <c r="JK36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="JL36">
+        <v>9</v>
+      </c>
+      <c r="JM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_9</t>
+        </is>
+      </c>
+      <c r="JR36">
+        <v>9</v>
+      </c>
+      <c r="JS36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="JT36">
+        <v>9</v>
+      </c>
+      <c r="JU36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1371</t>
+        </is>
+      </c>
+      <c r="KD36">
+        <v>9</v>
+      </c>
+      <c r="KE36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="KF36">
+        <v>9</v>
+      </c>
+      <c r="KG36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_9</t>
+        </is>
+      </c>
+      <c r="KH36">
+        <v>9</v>
+      </c>
+      <c r="KI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="KJ36">
+        <v>9</v>
+      </c>
+      <c r="KK36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_9</t>
+        </is>
+      </c>
+      <c r="KL36">
+        <v>9</v>
+      </c>
+      <c r="KM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="KN36">
+        <v>9</v>
+      </c>
+      <c r="KO36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_9</t>
+        </is>
+      </c>
+      <c r="LJ36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\f\f" C_WITH_CEDILLA_SMALL</t>
+        </is>
+      </c>
+      <c r="LK36">
+        <v>9</v>
+      </c>
+      <c r="LM36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
     </row>
     <row r="37" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="93" t="s">
@@ -53588,6 +57498,121 @@
       </c>
       <c r="HX37">
         <v>0</v>
+      </c>
+      <c r="JJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="JK37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="JL37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="JM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_0</t>
+        </is>
+      </c>
+      <c r="JR37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="JS37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="JT37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="JU37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_137B</t>
+        </is>
+      </c>
+      <c r="KD37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KE37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="KF37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KG37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_0</t>
+        </is>
+      </c>
+      <c r="KH37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KI37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="KJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KK37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_0</t>
+        </is>
+      </c>
+      <c r="KL37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(</t>
+        </is>
+      </c>
+      <c r="KN37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="KO37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_INDIC_0</t>
+        </is>
+      </c>
+      <c r="LJ37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\f\f" A_WITH_GRAVE_SMALL</t>
+        </is>
+      </c>
+      <c r="LK37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZERO</t>
+        </is>
+      </c>
+      <c r="LM37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@</t>
+        </is>
       </c>
     </row>
     <row r="38" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54754,6 +58779,56 @@
           <t xml:space="preserve">ICON_LEFT</t>
         </is>
       </c>
+      <c r="KL43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="KM43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TATWEEL</t>
+        </is>
+      </c>
+      <c r="KN43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="LB43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="LC43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="LD43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="LE43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="LJ43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">)</t>
+        </is>
+      </c>
+      <c r="LK43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="LM43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
     </row>
     <row r="44" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="93" t="s">
@@ -55353,6 +59428,36 @@
           <t xml:space="preserve">ICON_RIGHT</t>
         </is>
       </c>
+      <c r="LB44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_QMARK</t>
+        </is>
+      </c>
+      <c r="LC44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_EMARK</t>
+        </is>
+      </c>
+      <c r="LD44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INVERTED_QMARK</t>
+        </is>
+      </c>
+      <c r="LJ44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EQUALS</t>
+        </is>
+      </c>
+      <c r="LK44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="LM44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
     </row>
     <row r="45" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="93" t="s">
@@ -55939,6 +60044,91 @@
           <t xml:space="preserve">[</t>
         </is>
       </c>
+      <c r="JJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="JK45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="JL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KE45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="KF45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KH45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KI45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="KJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_JEEM</t>
+        </is>
+      </c>
+      <c r="KL45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="KM45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="KN45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="LB45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="LC45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="LD45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="LJ45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="LK45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
     </row>
     <row r="46" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="93" t="s">
@@ -56546,6 +60736,101 @@
           <t xml:space="preserve">]</t>
         </is>
       </c>
+      <c r="JJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="JK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="JL46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="KF46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KH46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KI46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="KJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_DAL</t>
+        </is>
+      </c>
+      <c r="KL46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="KM46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="KN46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="LB46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="LC46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="LD46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+</t>
+        </is>
+      </c>
+      <c r="LE46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="LJ46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">$</t>
+        </is>
+      </c>
+      <c r="LK46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POUND_SIGN</t>
+        </is>
+      </c>
+      <c r="LM46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENCY_SIGN</t>
+        </is>
+      </c>
     </row>
     <row r="47" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="93" t="s">
@@ -57061,6 +61346,81 @@
       <c r="HX47" t="inlineStr">
         <is>
           <t xml:space="preserve">CJK_IDEOG_COMMA</t>
+        </is>
+      </c>
+      <c r="JJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="JK47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SHADDA</t>
+        </is>
+      </c>
+      <c r="JL47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="KD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="KE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SHADDA</t>
+        </is>
+      </c>
+      <c r="KF47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="KH47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="KI47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" ARABIC_SHADDA</t>
+        </is>
+      </c>
+      <c r="KJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_THAL</t>
+        </is>
+      </c>
+      <c r="LB47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="LC47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="LD47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="LE47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="LJ47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="LK47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICRO_SIGN</t>
         </is>
       </c>
     </row>
@@ -57418,6 +61778,26 @@
           <t xml:space="preserve">#</t>
         </is>
       </c>
+      <c r="LB48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="LC48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">]</t>
+        </is>
+      </c>
+      <c r="LD48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">}</t>
+        </is>
+      </c>
+      <c r="LE48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
     </row>
     <row r="49" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="93" t="s">
@@ -57976,6 +62356,111 @@
       <c r="HX49" t="inlineStr">
         <is>
           <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="JI49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIAERESIS</t>
+        </is>
+      </c>
+      <c r="JJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="JK49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="JL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="JR49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1362</t>
+        </is>
+      </c>
+      <c r="JS49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1361</t>
+        </is>
+      </c>
+      <c r="JT49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1362</t>
+        </is>
+      </c>
+      <c r="KD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="KE49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="KF49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="KH49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="KI49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="KJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_KAF</t>
+        </is>
+      </c>
+      <c r="KL49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="KM49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="KN49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_SEMICOLON</t>
+        </is>
+      </c>
+      <c r="LB49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE_SMALL</t>
+        </is>
+      </c>
+      <c r="LC49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE</t>
+        </is>
+      </c>
+      <c r="LD49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N_WITH_TILDE_SMALL</t>
+        </is>
+      </c>
+      <c r="LJ49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="LK49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
     </row>
@@ -58577,6 +63062,141 @@
           <t xml:space="preserve">'</t>
         </is>
       </c>
+      <c r="IO50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="IX50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="IY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="IZ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="JA50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
+        </is>
+      </c>
+      <c r="JI50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACUTE_ACCENT</t>
+        </is>
+      </c>
+      <c r="JJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="JK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="JL50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="JR50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1366</t>
+        </is>
+      </c>
+      <c r="JS50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1365</t>
+        </is>
+      </c>
+      <c r="JT50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1366</t>
+        </is>
+      </c>
+      <c r="KD50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="KE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="KF50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="KH50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="KI50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="KJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_TAH</t>
+        </is>
+      </c>
+      <c r="KT50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="KU50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUOTE</t>
+        </is>
+      </c>
+      <c r="KV50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKINA</t>
+        </is>
+      </c>
+      <c r="LB50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="LC50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[</t>
+        </is>
+      </c>
+      <c r="LD50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{</t>
+        </is>
+      </c>
+      <c r="LE50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^</t>
+        </is>
+      </c>
+      <c r="LJ50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U_WITH_GRAVE</t>
+        </is>
+      </c>
+      <c r="LK50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
     </row>
     <row r="51" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="93" t="s">
@@ -59122,6 +63742,101 @@
       <c r="HX51" t="inlineStr">
         <is>
           <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="JI51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
+      <c r="JJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="JK51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="JL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KE51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="KF51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KH51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KI51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="KJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KM51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEVISION_SIGN</t>
+        </is>
+      </c>
+      <c r="KO51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~</t>
+        </is>
+      </c>
+      <c r="LB51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="LC51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DEGREE</t>
+        </is>
+      </c>
+      <c r="LD51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="LE51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT_SIGN</t>
+        </is>
+      </c>
+      <c r="LJ51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" SUPER_SCRIPT_2</t>
+        </is>
+      </c>
+      <c r="LK51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPACE</t>
+        </is>
+      </c>
+      <c r="LL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u"\v" SUPER_SCRIPT_2</t>
         </is>
       </c>
     </row>
@@ -59584,6 +64299,86 @@
           <t xml:space="preserve">COMMA</t>
         </is>
       </c>
+      <c r="JJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="JK52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="JL52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="JR52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1363</t>
+        </is>
+      </c>
+      <c r="JT52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1363</t>
+        </is>
+      </c>
+      <c r="KD52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KE52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="KF52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KH52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KI52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMMA</t>
+        </is>
+      </c>
+      <c r="KJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_WAW</t>
+        </is>
+      </c>
+      <c r="KL52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="KM52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="KN52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_COMMA</t>
+        </is>
+      </c>
+      <c r="LJ52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">;</t>
+        </is>
+      </c>
+      <c r="LK52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
     </row>
     <row r="53" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="93" t="s">
@@ -60020,6 +64815,81 @@
           <t xml:space="preserve">RANGLE_BRACKET_DBL</t>
         </is>
       </c>
+      <c r="JI53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOD_DOT_ACCENT</t>
+        </is>
+      </c>
+      <c r="JJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="JK53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="JL53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="JR53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1364</t>
+        </is>
+      </c>
+      <c r="JT53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1364</t>
+        </is>
+      </c>
+      <c r="KD53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="KE53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="KF53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="KH53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="KI53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="KJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAIN</t>
+        </is>
+      </c>
+      <c r="KM53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="LJ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">:</t>
+        </is>
+      </c>
+      <c r="LK53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
     </row>
     <row r="54" s="116" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="93" t="s">
@@ -60483,6 +65353,86 @@
       <c r="HX54" t="inlineStr">
         <is>
           <t xml:space="preserve">/</t>
+        </is>
+      </c>
+      <c r="JJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="JK54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QMARK</t>
+        </is>
+      </c>
+      <c r="JL54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="JR54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1367</t>
+        </is>
+      </c>
+      <c r="JS54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="JT54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETHIOPIC_1367</t>
+        </is>
+      </c>
+      <c r="KD54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="KE54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QMARK</t>
+        </is>
+      </c>
+      <c r="KF54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="KH54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="KI54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QMARK</t>
+        </is>
+      </c>
+      <c r="KJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_ZAH</t>
+        </is>
+      </c>
+      <c r="KM54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARABIC_QMARK</t>
+        </is>
+      </c>
+      <c r="KO54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
+      <c r="LJ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!</t>
+        </is>
+      </c>
+      <c r="LK54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SECTION</t>
         </is>
       </c>
     </row>
@@ -60925,6 +65875,86 @@
           <t xml:space="preserve">CJK_IDEOG_COMMA</t>
         </is>
       </c>
+      <c r="JJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="JK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="JL55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KE55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="KF55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KH55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="KI55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
+      <c r="KJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="LB55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="LC55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="LD55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="LE55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BACKSLASH</t>
+        </is>
+      </c>
+      <c r="LJ55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="LK55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;</t>
+        </is>
+      </c>
+      <c r="LM55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|</t>
+        </is>
+      </c>
     </row>
     <row r="56" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="141" t="s">
@@ -61362,6 +66392,153 @@
       <c r="HW56">
         <v>42</v>
       </c>
+      <c r="IA56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IE56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="II56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IK56">
+        <v>50</v>
+      </c>
+      <c r="IM56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IO56">
+        <v>50</v>
+      </c>
+      <c r="IQ56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IU56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JA56">
+        <v>50</v>
+      </c>
+      <c r="JC56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JG56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JI56">
+        <v>50</v>
+      </c>
+      <c r="JK56">
+        <v>42</v>
+      </c>
+      <c r="JM56">
+        <v>52</v>
+      </c>
+      <c r="JO56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JS56">
+        <v>42</v>
+      </c>
+      <c r="JU56">
+        <v>52</v>
+      </c>
+      <c r="JW56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JY56">
+        <v>50</v>
+      </c>
+      <c r="KA56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KC56">
+        <v>50</v>
+      </c>
+      <c r="KE56">
+        <v>42</v>
+      </c>
+      <c r="KG56">
+        <v>52</v>
+      </c>
+      <c r="KI56">
+        <v>42</v>
+      </c>
+      <c r="KK56">
+        <v>52</v>
+      </c>
+      <c r="KM56">
+        <v>42</v>
+      </c>
+      <c r="KO56">
+        <v>52</v>
+      </c>
+      <c r="KQ56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KU56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KW56">
+        <v>50</v>
+      </c>
+      <c r="KY56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LC56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LE56">
+        <v>50</v>
+      </c>
+      <c r="LG56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LK56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LM56">
+        <v>50</v>
+      </c>
     </row>
     <row r="57" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="141" t="s">
@@ -61811,6 +66988,153 @@
       <c r="HW57">
         <v>10</v>
       </c>
+      <c r="IA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IE57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="II57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IK57">
+        <v>13</v>
+      </c>
+      <c r="IM57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IO57">
+        <v>13</v>
+      </c>
+      <c r="IQ57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IU57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="IY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JA57">
+        <v>13</v>
+      </c>
+      <c r="JC57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JG57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JI57">
+        <v>13</v>
+      </c>
+      <c r="JK57">
+        <v>0</v>
+      </c>
+      <c r="JM57">
+        <v>13</v>
+      </c>
+      <c r="JO57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JS57">
+        <v>0</v>
+      </c>
+      <c r="JU57">
+        <v>13</v>
+      </c>
+      <c r="JW57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="JY57">
+        <v>13</v>
+      </c>
+      <c r="KA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KC57">
+        <v>13</v>
+      </c>
+      <c r="KE57">
+        <v>0</v>
+      </c>
+      <c r="KG57">
+        <v>13</v>
+      </c>
+      <c r="KI57">
+        <v>0</v>
+      </c>
+      <c r="KK57">
+        <v>13</v>
+      </c>
+      <c r="KM57">
+        <v>0</v>
+      </c>
+      <c r="KO57">
+        <v>13</v>
+      </c>
+      <c r="KQ57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KU57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="KW57">
+        <v>13</v>
+      </c>
+      <c r="KY57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LC57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LE57">
+        <v>13</v>
+      </c>
+      <c r="LG57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LK57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDE</t>
+        </is>
+      </c>
+      <c r="LM57">
+        <v>13</v>
+      </c>
     </row>
     <row r="58" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="141" t="s">
@@ -62201,6 +67525,117 @@
       <c r="HW58">
         <v>34</v>
       </c>
+      <c r="IA58">
+        <v>35</v>
+      </c>
+      <c r="IE58">
+        <v>35</v>
+      </c>
+      <c r="II58">
+        <v>28</v>
+      </c>
+      <c r="IK58">
+        <v>50</v>
+      </c>
+      <c r="IM58">
+        <v>28</v>
+      </c>
+      <c r="IO58">
+        <v>50</v>
+      </c>
+      <c r="IQ58">
+        <v>35</v>
+      </c>
+      <c r="IU58">
+        <v>35</v>
+      </c>
+      <c r="IY58">
+        <v>28</v>
+      </c>
+      <c r="JA58">
+        <v>50</v>
+      </c>
+      <c r="JC58">
+        <v>35</v>
+      </c>
+      <c r="JG58">
+        <v>28</v>
+      </c>
+      <c r="JI58">
+        <v>50</v>
+      </c>
+      <c r="JK58">
+        <v>27</v>
+      </c>
+      <c r="JM58">
+        <v>52</v>
+      </c>
+      <c r="JO58">
+        <v>35</v>
+      </c>
+      <c r="JS58">
+        <v>27</v>
+      </c>
+      <c r="JU58">
+        <v>52</v>
+      </c>
+      <c r="JW58">
+        <v>28</v>
+      </c>
+      <c r="JY58">
+        <v>50</v>
+      </c>
+      <c r="KA58">
+        <v>28</v>
+      </c>
+      <c r="KC58">
+        <v>50</v>
+      </c>
+      <c r="KE58">
+        <v>27</v>
+      </c>
+      <c r="KG58">
+        <v>52</v>
+      </c>
+      <c r="KI58">
+        <v>27</v>
+      </c>
+      <c r="KK58">
+        <v>52</v>
+      </c>
+      <c r="KM58">
+        <v>27</v>
+      </c>
+      <c r="KO58">
+        <v>52</v>
+      </c>
+      <c r="KQ58">
+        <v>35</v>
+      </c>
+      <c r="KU58">
+        <v>28</v>
+      </c>
+      <c r="KW58">
+        <v>50</v>
+      </c>
+      <c r="KY58">
+        <v>35</v>
+      </c>
+      <c r="LC58">
+        <v>28</v>
+      </c>
+      <c r="LE58">
+        <v>50</v>
+      </c>
+      <c r="LG58">
+        <v>35</v>
+      </c>
+      <c r="LK58">
+        <v>28</v>
+      </c>
+      <c r="LM58">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="141" t="s">
@@ -62600,6 +68035,117 @@
       <c r="HW59">
         <v>10</v>
       </c>
+      <c r="IA59">
+        <v>0</v>
+      </c>
+      <c r="IE59">
+        <v>0</v>
+      </c>
+      <c r="II59">
+        <v>0</v>
+      </c>
+      <c r="IK59">
+        <v>13</v>
+      </c>
+      <c r="IM59">
+        <v>0</v>
+      </c>
+      <c r="IO59">
+        <v>13</v>
+      </c>
+      <c r="IQ59">
+        <v>0</v>
+      </c>
+      <c r="IU59">
+        <v>0</v>
+      </c>
+      <c r="IY59">
+        <v>0</v>
+      </c>
+      <c r="JA59">
+        <v>13</v>
+      </c>
+      <c r="JC59">
+        <v>0</v>
+      </c>
+      <c r="JG59">
+        <v>0</v>
+      </c>
+      <c r="JI59">
+        <v>13</v>
+      </c>
+      <c r="JK59">
+        <v>0</v>
+      </c>
+      <c r="JM59">
+        <v>13</v>
+      </c>
+      <c r="JO59">
+        <v>0</v>
+      </c>
+      <c r="JS59">
+        <v>0</v>
+      </c>
+      <c r="JU59">
+        <v>13</v>
+      </c>
+      <c r="JW59">
+        <v>0</v>
+      </c>
+      <c r="JY59">
+        <v>13</v>
+      </c>
+      <c r="KA59">
+        <v>0</v>
+      </c>
+      <c r="KC59">
+        <v>13</v>
+      </c>
+      <c r="KE59">
+        <v>0</v>
+      </c>
+      <c r="KG59">
+        <v>13</v>
+      </c>
+      <c r="KI59">
+        <v>0</v>
+      </c>
+      <c r="KK59">
+        <v>13</v>
+      </c>
+      <c r="KM59">
+        <v>0</v>
+      </c>
+      <c r="KO59">
+        <v>13</v>
+      </c>
+      <c r="KQ59">
+        <v>0</v>
+      </c>
+      <c r="KU59">
+        <v>0</v>
+      </c>
+      <c r="KW59">
+        <v>13</v>
+      </c>
+      <c r="KY59">
+        <v>0</v>
+      </c>
+      <c r="LC59">
+        <v>0</v>
+      </c>
+      <c r="LE59">
+        <v>13</v>
+      </c>
+      <c r="LG59">
+        <v>0</v>
+      </c>
+      <c r="LK59">
+        <v>0</v>
+      </c>
+      <c r="LM59">
+        <v>13</v>
+      </c>
     </row>
     <row r="60" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="141" t="s">
@@ -62990,6 +68536,117 @@
       <c r="HW60">
         <v>34</v>
       </c>
+      <c r="IA60">
+        <v>35</v>
+      </c>
+      <c r="IE60">
+        <v>35</v>
+      </c>
+      <c r="II60">
+        <v>28</v>
+      </c>
+      <c r="IK60">
+        <v>50</v>
+      </c>
+      <c r="IM60">
+        <v>28</v>
+      </c>
+      <c r="IO60">
+        <v>50</v>
+      </c>
+      <c r="IQ60">
+        <v>35</v>
+      </c>
+      <c r="IU60">
+        <v>35</v>
+      </c>
+      <c r="IY60">
+        <v>28</v>
+      </c>
+      <c r="JA60">
+        <v>50</v>
+      </c>
+      <c r="JC60">
+        <v>35</v>
+      </c>
+      <c r="JG60">
+        <v>28</v>
+      </c>
+      <c r="JI60">
+        <v>50</v>
+      </c>
+      <c r="JK60">
+        <v>42</v>
+      </c>
+      <c r="JM60">
+        <v>52</v>
+      </c>
+      <c r="JO60">
+        <v>35</v>
+      </c>
+      <c r="JS60">
+        <v>42</v>
+      </c>
+      <c r="JU60">
+        <v>52</v>
+      </c>
+      <c r="JW60">
+        <v>28</v>
+      </c>
+      <c r="JY60">
+        <v>50</v>
+      </c>
+      <c r="KA60">
+        <v>28</v>
+      </c>
+      <c r="KC60">
+        <v>50</v>
+      </c>
+      <c r="KE60">
+        <v>42</v>
+      </c>
+      <c r="KG60">
+        <v>52</v>
+      </c>
+      <c r="KI60">
+        <v>42</v>
+      </c>
+      <c r="KK60">
+        <v>52</v>
+      </c>
+      <c r="KM60">
+        <v>42</v>
+      </c>
+      <c r="KO60">
+        <v>52</v>
+      </c>
+      <c r="KQ60">
+        <v>35</v>
+      </c>
+      <c r="KU60">
+        <v>28</v>
+      </c>
+      <c r="KW60">
+        <v>50</v>
+      </c>
+      <c r="KY60">
+        <v>35</v>
+      </c>
+      <c r="LC60">
+        <v>28</v>
+      </c>
+      <c r="LE60">
+        <v>50</v>
+      </c>
+      <c r="LG60">
+        <v>35</v>
+      </c>
+      <c r="LK60">
+        <v>28</v>
+      </c>
+      <c r="LM60">
+        <v>50</v>
+      </c>
     </row>
     <row r="61" s="172" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="141" t="s">
@@ -63388,6 +69045,117 @@
       </c>
       <c r="HW61">
         <v>10</v>
+      </c>
+      <c r="IA61">
+        <v>0</v>
+      </c>
+      <c r="IE61">
+        <v>0</v>
+      </c>
+      <c r="II61">
+        <v>0</v>
+      </c>
+      <c r="IK61">
+        <v>13</v>
+      </c>
+      <c r="IM61">
+        <v>0</v>
+      </c>
+      <c r="IO61">
+        <v>13</v>
+      </c>
+      <c r="IQ61">
+        <v>0</v>
+      </c>
+      <c r="IU61">
+        <v>0</v>
+      </c>
+      <c r="IY61">
+        <v>0</v>
+      </c>
+      <c r="JA61">
+        <v>13</v>
+      </c>
+      <c r="JC61">
+        <v>0</v>
+      </c>
+      <c r="JG61">
+        <v>0</v>
+      </c>
+      <c r="JI61">
+        <v>13</v>
+      </c>
+      <c r="JK61">
+        <v>0</v>
+      </c>
+      <c r="JM61">
+        <v>13</v>
+      </c>
+      <c r="JO61">
+        <v>0</v>
+      </c>
+      <c r="JS61">
+        <v>0</v>
+      </c>
+      <c r="JU61">
+        <v>13</v>
+      </c>
+      <c r="JW61">
+        <v>0</v>
+      </c>
+      <c r="JY61">
+        <v>13</v>
+      </c>
+      <c r="KA61">
+        <v>0</v>
+      </c>
+      <c r="KC61">
+        <v>13</v>
+      </c>
+      <c r="KE61">
+        <v>0</v>
+      </c>
+      <c r="KG61">
+        <v>13</v>
+      </c>
+      <c r="KI61">
+        <v>0</v>
+      </c>
+      <c r="KK61">
+        <v>13</v>
+      </c>
+      <c r="KM61">
+        <v>0</v>
+      </c>
+      <c r="KO61">
+        <v>13</v>
+      </c>
+      <c r="KQ61">
+        <v>0</v>
+      </c>
+      <c r="KU61">
+        <v>0</v>
+      </c>
+      <c r="KW61">
+        <v>13</v>
+      </c>
+      <c r="KY61">
+        <v>0</v>
+      </c>
+      <c r="LC61">
+        <v>0</v>
+      </c>
+      <c r="LE61">
+        <v>13</v>
+      </c>
+      <c r="LG61">
+        <v>0</v>
+      </c>
+      <c r="LK61">
+        <v>0</v>
+      </c>
+      <c r="LM61">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/keyboards/handwired/polykybd/lang/lang_lut.xlsx
+++ b/keyboards/handwired/polykybd/lang/lang_lut.xlsx
@@ -53155,20 +53155,32 @@
           <t xml:space="preserve">ETHIOPIC_136C</t>
         </is>
       </c>
+      <c r="JV31">
+        <v>4</v>
+      </c>
       <c r="JW31" t="inlineStr">
         <is>
           <t xml:space="preserve">NAIRA_SIGN</t>
         </is>
       </c>
+      <c r="JX31">
+        <v>4</v>
+      </c>
       <c r="JY31" t="inlineStr">
         <is>
           <t xml:space="preserve">$</t>
         </is>
       </c>
+      <c r="JZ31">
+        <v>4</v>
+      </c>
       <c r="KA31" t="inlineStr">
         <is>
           <t xml:space="preserve">NAIRA_SIGN</t>
         </is>
+      </c>
+      <c r="KB31">
+        <v>4</v>
       </c>
       <c r="KC31" t="inlineStr">
         <is>
@@ -63794,9 +63806,19 @@
           <t xml:space="preserve">&gt;</t>
         </is>
       </c>
+      <c r="KL51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
+        </is>
+      </c>
       <c r="KM51" t="inlineStr">
         <is>
           <t xml:space="preserve">DEVISION_SIGN</t>
+        </is>
+      </c>
+      <c r="KN51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRAVE_ACCENT</t>
         </is>
       </c>
       <c r="KO51" t="inlineStr">
@@ -64875,9 +64897,24 @@
           <t xml:space="preserve">ARABIC_ZAIN</t>
         </is>
       </c>
+      <c r="KL53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
       <c r="KM53" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;</t>
+        </is>
+      </c>
+      <c r="KN53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.</t>
+        </is>
+      </c>
+      <c r="KO53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'</t>
         </is>
       </c>
       <c r="LJ53" t="inlineStr">
@@ -65415,14 +65452,24 @@
           <t xml:space="preserve">ARABIC_ZAH</t>
         </is>
       </c>
+      <c r="KL54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
       <c r="KM54" t="inlineStr">
         <is>
           <t xml:space="preserve">ARABIC_QMARK</t>
         </is>
       </c>
+      <c r="KN54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/</t>
+        </is>
+      </c>
       <c r="KO54" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="LJ54" t="inlineStr">
@@ -67004,7 +67051,7 @@
         </is>
       </c>
       <c r="IK57">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="IM57" t="inlineStr">
         <is>
@@ -67012,7 +67059,7 @@
         </is>
       </c>
       <c r="IO57">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="IQ57" t="inlineStr">
         <is>
@@ -67030,7 +67077,7 @@
         </is>
       </c>
       <c r="JA57">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="JC57" t="inlineStr">
         <is>
@@ -67043,7 +67090,7 @@
         </is>
       </c>
       <c r="JI57">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="JK57">
         <v>0</v>
